--- a/spreadsheets/Games.xlsx
+++ b/spreadsheets/Games.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\ucer0.github.io\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476BEF1E-2F0A-44D9-8995-77307386D8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8879D598-26AD-4B66-9BCA-B7D185243A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30780" yWindow="315" windowWidth="24390" windowHeight="11685" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2019" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="2023" sheetId="8" r:id="rId5"/>
     <sheet name="2024" sheetId="9" r:id="rId6"/>
     <sheet name="2025" sheetId="10" r:id="rId7"/>
+    <sheet name="2026" sheetId="11" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="665">
   <si>
     <t>Nier: Automata</t>
   </si>
@@ -2655,6 +2656,89 @@
   </si>
   <si>
     <t xml:space="preserve"> DTS (26h 26m), Nepheshel (15h 45m)</t>
+  </si>
+  <si>
+    <t>Koudelka</t>
+  </si>
+  <si>
+    <t>Saya no Uta</t>
+  </si>
+  <si>
+    <t>Pipistrello and the Cursed Yoyo</t>
+  </si>
+  <si>
+    <t>R.E.P.O</t>
+  </si>
+  <si>
+    <t>The Séance of Blake Manor</t>
+  </si>
+  <si>
+    <t>1-ene.-25</t>
+  </si>
+  <si>
+    <t>29-dic.-25</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nepheshel (14h 36m), Blake Manor (18h 10m), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Ubuntu"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pipistrello (beaten in 18h 27m with 96'9%)</t>
+    </r>
+  </si>
+  <si>
+    <t>Ys I Chronicles+</t>
+  </si>
+  <si>
+    <t>Ys II Chronicles+</t>
+  </si>
+  <si>
+    <t>3-ene.</t>
+  </si>
+  <si>
+    <t>Ys: The Oath in Felghana</t>
+  </si>
+  <si>
+    <t>6-ene.</t>
+  </si>
+  <si>
+    <t>Xanadu Next</t>
+  </si>
+  <si>
+    <t>13-ene.</t>
+  </si>
+  <si>
+    <t>25-ene.</t>
+  </si>
+  <si>
+    <t>Trails to Azure</t>
+  </si>
+  <si>
+    <t>Blake Manor (1h 10m), TtA (15h 54m)</t>
+  </si>
+  <si>
+    <t>Picross e4</t>
+  </si>
+  <si>
+    <t>10-feb.</t>
+  </si>
+  <si>
+    <t>TtA (56h 00m)</t>
+  </si>
+  <si>
+    <t>Devil Summoner: Soul Hackers</t>
+  </si>
+  <si>
+    <t>Tiling Forest - Tiling Town Demo -</t>
+  </si>
+  <si>
+    <t>28-feb.</t>
   </si>
 </sst>
 </file>
@@ -3591,6 +3675,24 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3621,9 +3723,6 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
@@ -3642,22 +3741,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5286,7 +5370,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>4</c:v>
@@ -5352,7 +5436,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>1</c:v>
@@ -5364,7 +5448,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>1</c:v>
@@ -5673,6 +5757,9 @@
                 <c:pt idx="10">
                   <c:v>2.6361111111111115</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.8902777777777775</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5792,12 +5879,951 @@
                 <c:pt idx="10">
                   <c:v>0.92152777777777772</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.26180555555555557</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-0C72-471C-B3C1-0C4DEDA3923A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="50"/>
+        <c:overlap val="100"/>
+        <c:axId val="-1526709120"/>
+        <c:axId val="-1526714016"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="-1526709120"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+            <a:headEnd type="none" w="sm" len="sm"/>
+            <a:tailEnd type="none" w="sm" len="sm"/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Ubuntu" panose="020B0504030602030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="-1526714016"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="-1526714016"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="[h]&quot;h&quot;" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Ubuntu" panose="020B0504030602030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="-1526709120"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="0.5"/>
+        <c:minorUnit val="0.5"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln cap="sq">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Ubuntu" panose="020B0504030602030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="accent5">
+        <a:lumMod val="60000"/>
+        <a:lumOff val="40000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="800" b="1">
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="Ubuntu" panose="020B0504030602030204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES"/>
+              <a:t>JUEGOS POR AÑO DE SALIDA</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-ES"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'2026'!$Q$117:$Q$149</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1993</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'2026'!$R$117:$R$149</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C14A-4468-9D15-1465369B0D7F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="444"/>
+        <c:overlap val="-90"/>
+        <c:axId val="-1526708032"/>
+        <c:axId val="-1526704224"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="-1526708032"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="-1526704224"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="-1526704224"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="-1526708032"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="6.5891758143229659E-2"/>
+          <c:y val="3.1746031746031744E-2"/>
+          <c:w val="0.91079821426834318"/>
+          <c:h val="0.81548389784610253"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'2026'!$Q$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SOLO</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="75000"/>
+                <a:alpha val="90000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'2026'!$P$22:$P$33</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Ene</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Abr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Ago</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Oct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Dic</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'2026'!$Q$22:$Q$33</c:f>
+              <c:numCache>
+                <c:formatCode>[h]"h"\ mm"m"</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>2.7666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.5451388888888893</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BC4C-410D-BBF5-59735C36BF8D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'2026'!$R$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ONLINE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+                <a:alpha val="90000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'2026'!$P$22:$P$33</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Ene</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Abr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Ago</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Oct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Dic</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'2026'!$R$22:$R$33</c:f>
+              <c:numCache>
+                <c:formatCode>[h]"h"\ mm"m"</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.18472222222222223</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17986111111111111</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-BC4C-410D-BBF5-59735C36BF8D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10024,6 +11050,83 @@
 </file>
 
 <file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent4"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
   <a:schemeClr val="accent6"/>
   <a:schemeClr val="accent5"/>
@@ -11950,6 +13053,1081 @@
 </file>
 
 <file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="305">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+        <a:headEnd type="none" w="sm" len="sm"/>
+        <a:tailEnd type="none" w="sm" len="sm"/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="bg1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="70000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="70000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="46000">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+              <a:alpha val="0"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="5000"/>
+                <a:lumOff val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="5000"/>
+                <a:lumOff val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+        <a:headEnd type="none" w="sm" len="sm"/>
+        <a:tailEnd type="none" w="sm" len="sm"/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="50" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="202">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="305">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -17234,6 +19412,87 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>209547</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>542924</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{057FC130-E159-4049-ACC3-84749B9D6257}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB350200-3D7F-4705-9E9D-9B5B65E54B46}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
@@ -17545,17 +19804,17 @@
     </row>
     <row r="2" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="170">
+      <c r="B2" s="176">
         <v>2019</v>
       </c>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
+      <c r="C2" s="177"/>
+      <c r="D2" s="177"/>
       <c r="E2" s="67"/>
-      <c r="F2" s="176" t="s">
+      <c r="F2" s="182" t="s">
         <v>261</v>
       </c>
-      <c r="G2" s="176"/>
-      <c r="H2" s="176"/>
+      <c r="G2" s="182"/>
+      <c r="H2" s="182"/>
       <c r="I2" s="35"/>
       <c r="J2" s="35"/>
       <c r="K2" s="35"/>
@@ -17586,18 +19845,18 @@
         <v>77</v>
       </c>
       <c r="E3" s="68"/>
-      <c r="F3" s="176"/>
-      <c r="G3" s="176"/>
-      <c r="H3" s="176"/>
+      <c r="F3" s="182"/>
+      <c r="G3" s="182"/>
+      <c r="H3" s="182"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
       <c r="M3" s="6"/>
       <c r="N3" s="29"/>
-      <c r="O3" s="175"/>
-      <c r="P3" s="175"/>
-      <c r="Q3" s="175"/>
+      <c r="O3" s="181"/>
+      <c r="P3" s="181"/>
+      <c r="Q3" s="181"/>
       <c r="R3" s="6"/>
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
@@ -17619,18 +19878,18 @@
         <v>2004</v>
       </c>
       <c r="E4" s="26"/>
-      <c r="F4" s="176"/>
-      <c r="G4" s="176"/>
-      <c r="H4" s="176"/>
+      <c r="F4" s="182"/>
+      <c r="G4" s="182"/>
+      <c r="H4" s="182"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="30"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
       <c r="N4" s="7"/>
-      <c r="O4" s="175"/>
-      <c r="P4" s="175"/>
-      <c r="Q4" s="175"/>
+      <c r="O4" s="181"/>
+      <c r="P4" s="181"/>
+      <c r="Q4" s="181"/>
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
       <c r="T4" s="6"/>
@@ -17652,18 +19911,18 @@
         <v>2017</v>
       </c>
       <c r="E5" s="26"/>
-      <c r="F5" s="176"/>
-      <c r="G5" s="176"/>
-      <c r="H5" s="176"/>
+      <c r="F5" s="182"/>
+      <c r="G5" s="182"/>
+      <c r="H5" s="182"/>
       <c r="I5" s="6"/>
       <c r="J5" s="30"/>
       <c r="K5" s="30"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="7"/>
-      <c r="O5" s="175"/>
-      <c r="P5" s="175"/>
-      <c r="Q5" s="175"/>
+      <c r="O5" s="181"/>
+      <c r="P5" s="181"/>
+      <c r="Q5" s="181"/>
       <c r="R5" s="6"/>
       <c r="S5" s="6"/>
       <c r="T5" s="6"/>
@@ -17685,18 +19944,18 @@
         <v>2017</v>
       </c>
       <c r="E6" s="26"/>
-      <c r="F6" s="176"/>
-      <c r="G6" s="176"/>
-      <c r="H6" s="176"/>
+      <c r="F6" s="182"/>
+      <c r="G6" s="182"/>
+      <c r="H6" s="182"/>
       <c r="I6" s="6"/>
       <c r="J6" s="30"/>
       <c r="K6" s="30"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
       <c r="N6" s="7"/>
-      <c r="O6" s="175"/>
-      <c r="P6" s="175"/>
-      <c r="Q6" s="175"/>
+      <c r="O6" s="181"/>
+      <c r="P6" s="181"/>
+      <c r="Q6" s="181"/>
       <c r="R6" s="6"/>
       <c r="S6" s="6"/>
       <c r="T6" s="6"/>
@@ -17718,18 +19977,18 @@
         <v>2017</v>
       </c>
       <c r="E7" s="26"/>
-      <c r="F7" s="176"/>
-      <c r="G7" s="176"/>
-      <c r="H7" s="176"/>
+      <c r="F7" s="182"/>
+      <c r="G7" s="182"/>
+      <c r="H7" s="182"/>
       <c r="I7" s="6"/>
       <c r="J7" s="30"/>
       <c r="K7" s="30"/>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="7"/>
-      <c r="O7" s="175"/>
-      <c r="P7" s="175"/>
-      <c r="Q7" s="175"/>
+      <c r="O7" s="181"/>
+      <c r="P7" s="181"/>
+      <c r="Q7" s="181"/>
       <c r="R7" s="6"/>
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
@@ -17751,18 +20010,18 @@
         <v>2017</v>
       </c>
       <c r="E8" s="26"/>
-      <c r="F8" s="176"/>
-      <c r="G8" s="176"/>
-      <c r="H8" s="176"/>
+      <c r="F8" s="182"/>
+      <c r="G8" s="182"/>
+      <c r="H8" s="182"/>
       <c r="I8" s="6"/>
       <c r="J8" s="30"/>
       <c r="K8" s="30"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="7"/>
-      <c r="O8" s="175"/>
-      <c r="P8" s="175"/>
-      <c r="Q8" s="175"/>
+      <c r="O8" s="181"/>
+      <c r="P8" s="181"/>
+      <c r="Q8" s="181"/>
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
@@ -17784,18 +20043,18 @@
         <v>2016</v>
       </c>
       <c r="E9" s="26"/>
-      <c r="F9" s="176"/>
-      <c r="G9" s="176"/>
-      <c r="H9" s="176"/>
+      <c r="F9" s="182"/>
+      <c r="G9" s="182"/>
+      <c r="H9" s="182"/>
       <c r="I9" s="6"/>
       <c r="J9" s="30"/>
       <c r="K9" s="30"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="7"/>
-      <c r="O9" s="175"/>
-      <c r="P9" s="175"/>
-      <c r="Q9" s="175"/>
+      <c r="O9" s="181"/>
+      <c r="P9" s="181"/>
+      <c r="Q9" s="181"/>
       <c r="R9" s="6"/>
       <c r="S9" s="6"/>
       <c r="T9" s="6"/>
@@ -17817,18 +20076,18 @@
         <v>2017</v>
       </c>
       <c r="E10" s="26"/>
-      <c r="F10" s="176"/>
-      <c r="G10" s="176"/>
-      <c r="H10" s="176"/>
+      <c r="F10" s="182"/>
+      <c r="G10" s="182"/>
+      <c r="H10" s="182"/>
       <c r="I10" s="6"/>
       <c r="J10" s="30"/>
       <c r="K10" s="30"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
       <c r="N10" s="7"/>
-      <c r="O10" s="175"/>
-      <c r="P10" s="175"/>
-      <c r="Q10" s="175"/>
+      <c r="O10" s="181"/>
+      <c r="P10" s="181"/>
+      <c r="Q10" s="181"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
       <c r="T10" s="6"/>
@@ -17850,18 +20109,18 @@
         <v>2016</v>
       </c>
       <c r="E11" s="26"/>
-      <c r="F11" s="176"/>
-      <c r="G11" s="176"/>
-      <c r="H11" s="176"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="182"/>
+      <c r="H11" s="182"/>
       <c r="I11" s="6"/>
       <c r="J11" s="30"/>
       <c r="K11" s="30"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="7"/>
-      <c r="O11" s="175"/>
-      <c r="P11" s="175"/>
-      <c r="Q11" s="175"/>
+      <c r="O11" s="181"/>
+      <c r="P11" s="181"/>
+      <c r="Q11" s="181"/>
       <c r="R11" s="6"/>
       <c r="S11" s="6"/>
       <c r="T11" s="6"/>
@@ -17883,18 +20142,18 @@
         <v>2017</v>
       </c>
       <c r="E12" s="26"/>
-      <c r="F12" s="176"/>
-      <c r="G12" s="176"/>
-      <c r="H12" s="176"/>
+      <c r="F12" s="182"/>
+      <c r="G12" s="182"/>
+      <c r="H12" s="182"/>
       <c r="I12" s="6"/>
       <c r="J12" s="30"/>
       <c r="K12" s="30"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="7"/>
-      <c r="O12" s="175"/>
-      <c r="P12" s="175"/>
-      <c r="Q12" s="175"/>
+      <c r="O12" s="181"/>
+      <c r="P12" s="181"/>
+      <c r="Q12" s="181"/>
       <c r="R12" s="6"/>
       <c r="S12" s="6"/>
       <c r="T12" s="6"/>
@@ -17916,18 +20175,18 @@
         <v>2009</v>
       </c>
       <c r="E13" s="26"/>
-      <c r="F13" s="176"/>
-      <c r="G13" s="176"/>
-      <c r="H13" s="176"/>
+      <c r="F13" s="182"/>
+      <c r="G13" s="182"/>
+      <c r="H13" s="182"/>
       <c r="I13" s="6"/>
       <c r="J13" s="30"/>
       <c r="K13" s="30"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="7"/>
-      <c r="O13" s="175"/>
-      <c r="P13" s="175"/>
-      <c r="Q13" s="175"/>
+      <c r="O13" s="181"/>
+      <c r="P13" s="181"/>
+      <c r="Q13" s="181"/>
       <c r="R13" s="6"/>
       <c r="S13" s="6"/>
       <c r="T13" s="6"/>
@@ -17949,18 +20208,18 @@
         <v>2019</v>
       </c>
       <c r="E14" s="26"/>
-      <c r="F14" s="176"/>
-      <c r="G14" s="176"/>
-      <c r="H14" s="176"/>
+      <c r="F14" s="182"/>
+      <c r="G14" s="182"/>
+      <c r="H14" s="182"/>
       <c r="I14" s="6"/>
       <c r="J14" s="30"/>
       <c r="K14" s="30"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="7"/>
-      <c r="O14" s="175"/>
-      <c r="P14" s="175"/>
-      <c r="Q14" s="175"/>
+      <c r="O14" s="181"/>
+      <c r="P14" s="181"/>
+      <c r="Q14" s="181"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
       <c r="T14" s="6"/>
@@ -17982,18 +20241,18 @@
         <v>2019</v>
       </c>
       <c r="E15" s="26"/>
-      <c r="F15" s="176"/>
-      <c r="G15" s="176"/>
-      <c r="H15" s="176"/>
+      <c r="F15" s="182"/>
+      <c r="G15" s="182"/>
+      <c r="H15" s="182"/>
       <c r="I15" s="6"/>
       <c r="J15" s="30"/>
       <c r="K15" s="30"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="7"/>
-      <c r="O15" s="175"/>
-      <c r="P15" s="175"/>
-      <c r="Q15" s="175"/>
+      <c r="O15" s="181"/>
+      <c r="P15" s="181"/>
+      <c r="Q15" s="181"/>
       <c r="R15" s="6"/>
       <c r="S15" s="6"/>
       <c r="T15" s="6"/>
@@ -18018,9 +20277,9 @@
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
-      <c r="O16" s="175"/>
-      <c r="P16" s="175"/>
-      <c r="Q16" s="175"/>
+      <c r="O16" s="181"/>
+      <c r="P16" s="181"/>
+      <c r="Q16" s="181"/>
       <c r="S16" s="6"/>
       <c r="T16" s="6"/>
       <c r="U16" s="6"/>
@@ -18031,9 +20290,9 @@
     </row>
     <row r="17" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="23"/>
-      <c r="B17" s="172"/>
-      <c r="C17" s="172"/>
-      <c r="D17" s="172"/>
+      <c r="B17" s="178"/>
+      <c r="C17" s="178"/>
+      <c r="D17" s="178"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="7"/>
@@ -18058,9 +20317,9 @@
     </row>
     <row r="18" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="23"/>
-      <c r="B18" s="172"/>
-      <c r="C18" s="172"/>
-      <c r="D18" s="172"/>
+      <c r="B18" s="178"/>
+      <c r="C18" s="178"/>
+      <c r="D18" s="178"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="7"/>
@@ -18070,8 +20329,8 @@
       <c r="K18" s="30"/>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
-      <c r="N18" s="173"/>
-      <c r="O18" s="174"/>
+      <c r="N18" s="179"/>
+      <c r="O18" s="180"/>
       <c r="P18" s="6"/>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
@@ -18085,9 +20344,9 @@
     </row>
     <row r="19" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="23"/>
-      <c r="B19" s="172"/>
-      <c r="C19" s="172"/>
-      <c r="D19" s="172"/>
+      <c r="B19" s="178"/>
+      <c r="C19" s="178"/>
+      <c r="D19" s="178"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="7"/>
@@ -18097,8 +20356,8 @@
       <c r="K19" s="30"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
-      <c r="N19" s="174"/>
-      <c r="O19" s="174"/>
+      <c r="N19" s="180"/>
+      <c r="O19" s="180"/>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
       <c r="R19" s="6"/>
@@ -18124,8 +20383,8 @@
       <c r="K20" s="30"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
-      <c r="N20" s="174"/>
-      <c r="O20" s="174"/>
+      <c r="N20" s="180"/>
+      <c r="O20" s="180"/>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
@@ -18151,8 +20410,8 @@
       <c r="K21" s="30"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
-      <c r="N21" s="174"/>
-      <c r="O21" s="174"/>
+      <c r="N21" s="180"/>
+      <c r="O21" s="180"/>
       <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
       <c r="R21" s="6"/>
@@ -18178,8 +20437,8 @@
       <c r="K22" s="30"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
-      <c r="N22" s="174"/>
-      <c r="O22" s="174"/>
+      <c r="N22" s="180"/>
+      <c r="O22" s="180"/>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
@@ -19358,8 +21617,8 @@
         <v>11</v>
       </c>
       <c r="I17" s="6"/>
-      <c r="J17" s="178"/>
-      <c r="K17" s="179"/>
+      <c r="J17" s="184"/>
+      <c r="K17" s="185"/>
       <c r="L17" s="6"/>
       <c r="M17" s="39"/>
       <c r="N17" s="39"/>
@@ -19397,8 +21656,8 @@
         <v>1</v>
       </c>
       <c r="I18" s="6"/>
-      <c r="J18" s="177"/>
-      <c r="K18" s="177"/>
+      <c r="J18" s="183"/>
+      <c r="K18" s="183"/>
       <c r="L18" s="6"/>
       <c r="M18" s="39"/>
       <c r="N18" s="39"/>
@@ -23449,7 +25708,7 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="3.140625" style="40" customWidth="1"/>
-    <col min="3" max="3" width="30" style="40" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" style="40" customWidth="1"/>
     <col min="4" max="4" width="7.140625" style="40" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" style="161" customWidth="1"/>
     <col min="6" max="7" width="12.85546875" style="40" customWidth="1"/>
@@ -23618,7 +25877,7 @@
         <v>4.197916666666667</v>
       </c>
       <c r="I3" s="6"/>
-      <c r="J3" s="184" t="s">
+      <c r="J3" s="189" t="s">
         <v>118</v>
       </c>
       <c r="K3" s="80" t="s">
@@ -23692,7 +25951,7 @@
         <v>0.30138888888888887</v>
       </c>
       <c r="I4" s="6"/>
-      <c r="J4" s="185"/>
+      <c r="J4" s="190"/>
       <c r="K4" s="54" t="s">
         <v>127</v>
       </c>
@@ -23764,7 +26023,7 @@
         <v>0.2076388888888889</v>
       </c>
       <c r="I5" s="6"/>
-      <c r="J5" s="185"/>
+      <c r="J5" s="190"/>
       <c r="K5" s="73" t="s">
         <v>132</v>
       </c>
@@ -23836,7 +26095,7 @@
         <v>1.2437499999999999</v>
       </c>
       <c r="I6" s="6"/>
-      <c r="J6" s="185"/>
+      <c r="J6" s="190"/>
       <c r="K6" s="54" t="s">
         <v>129</v>
       </c>
@@ -23908,7 +26167,7 @@
         <v>0.27916666666666667</v>
       </c>
       <c r="I7" s="6"/>
-      <c r="J7" s="185"/>
+      <c r="J7" s="190"/>
       <c r="K7" s="73" t="s">
         <v>136</v>
       </c>
@@ -23980,7 +26239,7 @@
         <v>6.1111111111111116E-2</v>
       </c>
       <c r="I8" s="6"/>
-      <c r="J8" s="185"/>
+      <c r="J8" s="190"/>
       <c r="K8" s="54" t="s">
         <v>137</v>
       </c>
@@ -24052,7 +26311,7 @@
         <v>0.11180555555555556</v>
       </c>
       <c r="I9" s="6"/>
-      <c r="J9" s="184" t="s">
+      <c r="J9" s="189" t="s">
         <v>119</v>
       </c>
       <c r="K9" s="71" t="s">
@@ -24126,7 +26385,7 @@
         <v>0.19027777777777777</v>
       </c>
       <c r="I10" s="6"/>
-      <c r="J10" s="185"/>
+      <c r="J10" s="190"/>
       <c r="K10" s="54" t="s">
         <v>127</v>
       </c>
@@ -24198,7 +26457,7 @@
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="I11" s="6"/>
-      <c r="J11" s="185"/>
+      <c r="J11" s="190"/>
       <c r="K11" s="73" t="s">
         <v>132</v>
       </c>
@@ -24270,7 +26529,7 @@
         <v>1.7097222222222221</v>
       </c>
       <c r="I12" s="6"/>
-      <c r="J12" s="185"/>
+      <c r="J12" s="190"/>
       <c r="K12" s="54" t="s">
         <v>129</v>
       </c>
@@ -24342,7 +26601,7 @@
         <v>0.15972222222222224</v>
       </c>
       <c r="I13" s="6"/>
-      <c r="J13" s="185"/>
+      <c r="J13" s="190"/>
       <c r="K13" s="73" t="s">
         <v>141</v>
       </c>
@@ -24414,7 +26673,7 @@
         <v>0.14722222222222223</v>
       </c>
       <c r="I14" s="6"/>
-      <c r="J14" s="184" t="s">
+      <c r="J14" s="189" t="s">
         <v>120</v>
       </c>
       <c r="K14" s="10" t="s">
@@ -24488,7 +26747,7 @@
         <v>0.59652777777777777</v>
       </c>
       <c r="I15" s="6"/>
-      <c r="J15" s="185"/>
+      <c r="J15" s="190"/>
       <c r="K15" s="73" t="s">
         <v>127</v>
       </c>
@@ -24560,7 +26819,7 @@
         <v>13</v>
       </c>
       <c r="I16" s="6"/>
-      <c r="J16" s="185"/>
+      <c r="J16" s="190"/>
       <c r="K16" s="54" t="s">
         <v>132</v>
       </c>
@@ -24632,7 +26891,7 @@
         <v>13</v>
       </c>
       <c r="I17" s="6"/>
-      <c r="J17" s="185"/>
+      <c r="J17" s="190"/>
       <c r="K17" s="73" t="s">
         <v>129</v>
       </c>
@@ -24704,7 +26963,7 @@
         <v>0.24583333333333335</v>
       </c>
       <c r="I18" s="6"/>
-      <c r="J18" s="185"/>
+      <c r="J18" s="190"/>
       <c r="K18" s="54" t="s">
         <v>144</v>
       </c>
@@ -24776,7 +27035,7 @@
         <v>0.49513888888888885</v>
       </c>
       <c r="I19" s="6"/>
-      <c r="J19" s="186"/>
+      <c r="J19" s="191"/>
       <c r="K19" s="76" t="s">
         <v>150</v>
       </c>
@@ -24848,7 +27107,7 @@
         <v>0.20972222222222223</v>
       </c>
       <c r="I20" s="6"/>
-      <c r="J20" s="184" t="s">
+      <c r="J20" s="189" t="s">
         <v>143</v>
       </c>
       <c r="K20" s="10" t="s">
@@ -24922,7 +27181,7 @@
         <v>0.25486111111111109</v>
       </c>
       <c r="I21" s="6"/>
-      <c r="J21" s="186"/>
+      <c r="J21" s="191"/>
       <c r="K21" s="76" t="s">
         <v>141</v>
       </c>
@@ -25004,7 +27263,7 @@
         <v>0.26666666666666666</v>
       </c>
       <c r="I22" s="6"/>
-      <c r="J22" s="185" t="s">
+      <c r="J22" s="190" t="s">
         <v>161</v>
       </c>
       <c r="K22" s="54" t="s">
@@ -25090,7 +27349,7 @@
         <v>0.26944444444444443</v>
       </c>
       <c r="I23" s="6"/>
-      <c r="J23" s="185"/>
+      <c r="J23" s="190"/>
       <c r="K23" s="80" t="s">
         <v>169</v>
       </c>
@@ -25174,7 +27433,7 @@
         <v>0.3263888888888889</v>
       </c>
       <c r="I24" s="39"/>
-      <c r="J24" s="185"/>
+      <c r="J24" s="190"/>
       <c r="K24" s="54" t="s">
         <v>163</v>
       </c>
@@ -25258,7 +27517,7 @@
         <v>0.32847222222222222</v>
       </c>
       <c r="I25" s="39"/>
-      <c r="J25" s="185"/>
+      <c r="J25" s="190"/>
       <c r="K25" s="73" t="s">
         <v>141</v>
       </c>
@@ -25342,7 +27601,7 @@
         <v>0.67013888888888884</v>
       </c>
       <c r="I26" s="39"/>
-      <c r="J26" s="186"/>
+      <c r="J26" s="191"/>
       <c r="K26" s="11" t="s">
         <v>162</v>
       </c>
@@ -25426,7 +27685,7 @@
         <v>0.11180555555555556</v>
       </c>
       <c r="I27" s="39"/>
-      <c r="J27" s="184" t="s">
+      <c r="J27" s="189" t="s">
         <v>171</v>
       </c>
       <c r="K27" s="73" t="s">
@@ -25512,7 +27771,7 @@
         <v>0.22291666666666665</v>
       </c>
       <c r="I28" s="39"/>
-      <c r="J28" s="185"/>
+      <c r="J28" s="190"/>
       <c r="K28" s="101" t="s">
         <v>163</v>
       </c>
@@ -25596,7 +27855,7 @@
         <v>0.13194444444444445</v>
       </c>
       <c r="I29" s="39"/>
-      <c r="J29" s="185"/>
+      <c r="J29" s="190"/>
       <c r="K29" s="73" t="s">
         <v>29</v>
       </c>
@@ -25680,7 +27939,7 @@
         <v>13</v>
       </c>
       <c r="I30" s="39"/>
-      <c r="J30" s="185"/>
+      <c r="J30" s="190"/>
       <c r="K30" s="101" t="s">
         <v>136</v>
       </c>
@@ -25764,7 +28023,7 @@
         <v>0.43888888888888888</v>
       </c>
       <c r="I31" s="39"/>
-      <c r="J31" s="186"/>
+      <c r="J31" s="191"/>
       <c r="K31" s="73" t="s">
         <v>141</v>
       </c>
@@ -25848,7 +28107,7 @@
         <v>0.42083333333333334</v>
       </c>
       <c r="I32" s="39"/>
-      <c r="J32" s="184" t="s">
+      <c r="J32" s="189" t="s">
         <v>184</v>
       </c>
       <c r="K32" s="107" t="s">
@@ -25934,7 +28193,7 @@
         <v>2.7097222222222221</v>
       </c>
       <c r="I33" s="39"/>
-      <c r="J33" s="185"/>
+      <c r="J33" s="190"/>
       <c r="K33" s="73" t="s">
         <v>179</v>
       </c>
@@ -26020,7 +28279,7 @@
         <v>13</v>
       </c>
       <c r="I34" s="39"/>
-      <c r="J34" s="185"/>
+      <c r="J34" s="190"/>
       <c r="K34" s="54" t="s">
         <v>199</v>
       </c>
@@ -26103,7 +28362,7 @@
         <v>0.11041666666666666</v>
       </c>
       <c r="I35" s="39"/>
-      <c r="J35" s="185"/>
+      <c r="J35" s="190"/>
       <c r="K35" s="80" t="s">
         <v>198</v>
       </c>
@@ -26175,7 +28434,7 @@
         <v>0.37083333333333335</v>
       </c>
       <c r="I36" s="39"/>
-      <c r="J36" s="185"/>
+      <c r="J36" s="190"/>
       <c r="K36" s="54" t="s">
         <v>141</v>
       </c>
@@ -26183,9 +28442,9 @@
         <v>4.5138888888888888E-2</v>
       </c>
       <c r="M36" s="39"/>
-      <c r="N36" s="180"/>
-      <c r="O36" s="180"/>
-      <c r="P36" s="180"/>
+      <c r="N36" s="172"/>
+      <c r="O36" s="172"/>
+      <c r="P36" s="172"/>
       <c r="Q36" s="111"/>
       <c r="R36" s="16"/>
       <c r="S36" s="16"/>
@@ -26247,7 +28506,7 @@
         <v>0.80694444444444446</v>
       </c>
       <c r="I37" s="39"/>
-      <c r="J37" s="185"/>
+      <c r="J37" s="190"/>
       <c r="K37" s="80" t="s">
         <v>196</v>
       </c>
@@ -26255,9 +28514,9 @@
         <v>7.7777777777777779E-2</v>
       </c>
       <c r="M37" s="39"/>
-      <c r="N37" s="180"/>
-      <c r="O37" s="180"/>
-      <c r="P37" s="180"/>
+      <c r="N37" s="172"/>
+      <c r="O37" s="172"/>
+      <c r="P37" s="172"/>
       <c r="Q37" s="111"/>
       <c r="R37" s="16"/>
       <c r="S37" s="16"/>
@@ -26319,7 +28578,7 @@
         <v>9.1666666666666674E-2</v>
       </c>
       <c r="I38" s="39"/>
-      <c r="J38" s="186"/>
+      <c r="J38" s="191"/>
       <c r="K38" s="11" t="s">
         <v>202</v>
       </c>
@@ -26327,9 +28586,9 @@
         <v>9.1666666666666674E-2</v>
       </c>
       <c r="M38" s="39"/>
-      <c r="N38" s="180"/>
-      <c r="O38" s="180"/>
-      <c r="P38" s="180"/>
+      <c r="N38" s="172"/>
+      <c r="O38" s="172"/>
+      <c r="P38" s="172"/>
       <c r="Q38" s="111"/>
       <c r="R38" s="16"/>
       <c r="S38" s="16"/>
@@ -26377,7 +28636,7 @@
       <c r="G39" s="30"/>
       <c r="H39" s="61"/>
       <c r="I39" s="39"/>
-      <c r="J39" s="184" t="s">
+      <c r="J39" s="189" t="s">
         <v>209</v>
       </c>
       <c r="K39" s="116" t="s">
@@ -26387,9 +28646,9 @@
         <v>0.14583333333333334</v>
       </c>
       <c r="M39" s="39"/>
-      <c r="N39" s="180"/>
-      <c r="O39" s="180"/>
-      <c r="P39" s="180"/>
+      <c r="N39" s="172"/>
+      <c r="O39" s="172"/>
+      <c r="P39" s="172"/>
       <c r="Q39" s="124"/>
       <c r="R39" s="16"/>
       <c r="S39" s="16"/>
@@ -26437,7 +28696,7 @@
       <c r="G40" s="39"/>
       <c r="H40" s="62"/>
       <c r="I40" s="39"/>
-      <c r="J40" s="185"/>
+      <c r="J40" s="190"/>
       <c r="K40" s="113" t="s">
         <v>210</v>
       </c>
@@ -26445,9 +28704,9 @@
         <v>0.3666666666666667</v>
       </c>
       <c r="M40" s="39"/>
-      <c r="N40" s="180"/>
-      <c r="O40" s="180"/>
-      <c r="P40" s="180"/>
+      <c r="N40" s="172"/>
+      <c r="O40" s="172"/>
+      <c r="P40" s="172"/>
       <c r="Q40" s="124"/>
       <c r="R40" s="16"/>
       <c r="S40" s="16"/>
@@ -26494,7 +28753,7 @@
       <c r="G41" s="30"/>
       <c r="H41" s="61"/>
       <c r="I41" s="39"/>
-      <c r="J41" s="185"/>
+      <c r="J41" s="190"/>
       <c r="K41" s="112" t="s">
         <v>179</v>
       </c>
@@ -26502,9 +28761,9 @@
         <v>0.53333333333333333</v>
       </c>
       <c r="M41" s="39"/>
-      <c r="N41" s="180"/>
-      <c r="O41" s="180"/>
-      <c r="P41" s="180"/>
+      <c r="N41" s="172"/>
+      <c r="O41" s="172"/>
+      <c r="P41" s="172"/>
       <c r="Q41" s="124"/>
       <c r="R41" s="16"/>
       <c r="S41" s="16"/>
@@ -26552,7 +28811,7 @@
       <c r="G42" s="30"/>
       <c r="H42" s="61"/>
       <c r="I42" s="39"/>
-      <c r="J42" s="185"/>
+      <c r="J42" s="190"/>
       <c r="K42" s="114" t="s">
         <v>136</v>
       </c>
@@ -26610,7 +28869,7 @@
       <c r="G43" s="39"/>
       <c r="H43" s="62"/>
       <c r="I43" s="39"/>
-      <c r="J43" s="185"/>
+      <c r="J43" s="190"/>
       <c r="K43" s="112" t="s">
         <v>212</v>
       </c>
@@ -26668,7 +28927,7 @@
       <c r="G44" s="39"/>
       <c r="H44" s="62"/>
       <c r="I44" s="39"/>
-      <c r="J44" s="185"/>
+      <c r="J44" s="190"/>
       <c r="K44" s="113" t="s">
         <v>213</v>
       </c>
@@ -26726,7 +28985,7 @@
       <c r="G45" s="39"/>
       <c r="H45" s="62"/>
       <c r="I45" s="39"/>
-      <c r="J45" s="186"/>
+      <c r="J45" s="191"/>
       <c r="K45" s="115" t="s">
         <v>141</v>
       </c>
@@ -26784,7 +29043,7 @@
       <c r="G46" s="39"/>
       <c r="H46" s="62"/>
       <c r="I46" s="39"/>
-      <c r="J46" s="181" t="s">
+      <c r="J46" s="186" t="s">
         <v>217</v>
       </c>
       <c r="K46" s="119" t="s">
@@ -26844,7 +29103,7 @@
       <c r="G47" s="39"/>
       <c r="H47" s="62"/>
       <c r="I47" s="39"/>
-      <c r="J47" s="182"/>
+      <c r="J47" s="187"/>
       <c r="K47" s="80" t="s">
         <v>179</v>
       </c>
@@ -26902,7 +29161,7 @@
       <c r="G48" s="39"/>
       <c r="H48" s="62"/>
       <c r="I48" s="39"/>
-      <c r="J48" s="182"/>
+      <c r="J48" s="187"/>
       <c r="K48" s="101" t="s">
         <v>136</v>
       </c>
@@ -26960,7 +29219,7 @@
       <c r="G49" s="39"/>
       <c r="H49" s="62"/>
       <c r="I49" s="39"/>
-      <c r="J49" s="183"/>
+      <c r="J49" s="188"/>
       <c r="K49" s="120" t="s">
         <v>213</v>
       </c>
@@ -27018,7 +29277,7 @@
       <c r="G50" s="39"/>
       <c r="H50" s="39"/>
       <c r="I50" s="39"/>
-      <c r="J50" s="181" t="s">
+      <c r="J50" s="186" t="s">
         <v>232</v>
       </c>
       <c r="K50" s="121" t="s">
@@ -27078,7 +29337,7 @@
       <c r="G51" s="39"/>
       <c r="H51" s="39"/>
       <c r="I51" s="39"/>
-      <c r="J51" s="182"/>
+      <c r="J51" s="187"/>
       <c r="K51" s="122" t="s">
         <v>179</v>
       </c>
@@ -27136,7 +29395,7 @@
       <c r="G52" s="39"/>
       <c r="H52" s="39"/>
       <c r="I52" s="39"/>
-      <c r="J52" s="182"/>
+      <c r="J52" s="187"/>
       <c r="K52" s="114" t="s">
         <v>235</v>
       </c>
@@ -27194,7 +29453,7 @@
       <c r="G53" s="39"/>
       <c r="H53" s="39"/>
       <c r="I53" s="39"/>
-      <c r="J53" s="183"/>
+      <c r="J53" s="188"/>
       <c r="K53" s="115" t="s">
         <v>211</v>
       </c>
@@ -27252,7 +29511,7 @@
       <c r="G54" s="39"/>
       <c r="H54" s="39"/>
       <c r="I54" s="39"/>
-      <c r="J54" s="181" t="s">
+      <c r="J54" s="186" t="s">
         <v>243</v>
       </c>
       <c r="K54" s="121" t="s">
@@ -27312,7 +29571,7 @@
       <c r="G55" s="39"/>
       <c r="H55" s="39"/>
       <c r="I55" s="39"/>
-      <c r="J55" s="182"/>
+      <c r="J55" s="187"/>
       <c r="K55" s="122" t="s">
         <v>242</v>
       </c>
@@ -27370,7 +29629,7 @@
       <c r="G56" s="39"/>
       <c r="H56" s="39"/>
       <c r="I56" s="39"/>
-      <c r="J56" s="182"/>
+      <c r="J56" s="187"/>
       <c r="K56" s="114" t="s">
         <v>29</v>
       </c>
@@ -27428,7 +29687,7 @@
       <c r="G57" s="39"/>
       <c r="H57" s="39"/>
       <c r="I57" s="39"/>
-      <c r="J57" s="183"/>
+      <c r="J57" s="188"/>
       <c r="K57" s="115" t="s">
         <v>199</v>
       </c>
@@ -27486,7 +29745,7 @@
       <c r="G58" s="39"/>
       <c r="H58" s="39"/>
       <c r="I58" s="39"/>
-      <c r="J58" s="181" t="s">
+      <c r="J58" s="186" t="s">
         <v>246</v>
       </c>
       <c r="K58" s="121" t="s">
@@ -27546,7 +29805,7 @@
       <c r="G59" s="39"/>
       <c r="H59" s="39"/>
       <c r="I59" s="39"/>
-      <c r="J59" s="182"/>
+      <c r="J59" s="187"/>
       <c r="K59" s="122" t="s">
         <v>235</v>
       </c>
@@ -27604,7 +29863,7 @@
       <c r="G60" s="39"/>
       <c r="H60" s="39"/>
       <c r="I60" s="39"/>
-      <c r="J60" s="182"/>
+      <c r="J60" s="187"/>
       <c r="K60" s="114" t="s">
         <v>242</v>
       </c>
@@ -27662,7 +29921,7 @@
       <c r="G61" s="39"/>
       <c r="H61" s="39"/>
       <c r="I61" s="39"/>
-      <c r="J61" s="182"/>
+      <c r="J61" s="187"/>
       <c r="K61" s="122" t="s">
         <v>245</v>
       </c>
@@ -27720,7 +29979,7 @@
       <c r="G62" s="39"/>
       <c r="H62" s="39"/>
       <c r="I62" s="39"/>
-      <c r="J62" s="182"/>
+      <c r="J62" s="187"/>
       <c r="K62" s="114" t="s">
         <v>29</v>
       </c>
@@ -27778,7 +30037,7 @@
       <c r="G63" s="39"/>
       <c r="H63" s="39"/>
       <c r="I63" s="39"/>
-      <c r="J63" s="183"/>
+      <c r="J63" s="188"/>
       <c r="K63" s="115" t="s">
         <v>199</v>
       </c>
@@ -33562,7 +35821,7 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="3.140625" style="130" customWidth="1"/>
-    <col min="3" max="3" width="35.7109375" style="130" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" style="130" customWidth="1"/>
     <col min="4" max="4" width="7.140625" style="130" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" style="159" customWidth="1"/>
     <col min="6" max="7" width="12.85546875" style="130" customWidth="1"/>
@@ -33631,15 +35890,15 @@
         <v>20</v>
       </c>
       <c r="I2" s="6"/>
-      <c r="J2" s="188" t="s">
+      <c r="J2" s="170" t="s">
         <v>284</v>
       </c>
-      <c r="K2" s="190"/>
+      <c r="K2" s="192"/>
       <c r="L2" s="136"/>
-      <c r="M2" s="190" t="s">
+      <c r="M2" s="192" t="s">
         <v>285</v>
       </c>
-      <c r="N2" s="189"/>
+      <c r="N2" s="171"/>
       <c r="O2" s="39"/>
       <c r="P2" s="39"/>
       <c r="Q2" s="39"/>
@@ -33939,15 +36198,15 @@
         <v>0.20416666666666669</v>
       </c>
       <c r="I9" s="6"/>
-      <c r="J9" s="188" t="s">
+      <c r="J9" s="170" t="s">
         <v>286</v>
       </c>
-      <c r="K9" s="190"/>
+      <c r="K9" s="192"/>
       <c r="L9" s="136"/>
-      <c r="M9" s="190" t="s">
+      <c r="M9" s="192" t="s">
         <v>287</v>
       </c>
-      <c r="N9" s="189"/>
+      <c r="N9" s="171"/>
       <c r="O9" s="39"/>
       <c r="P9" s="39"/>
       <c r="Q9" s="39"/>
@@ -34154,15 +36413,15 @@
         <v>0.15208333333333332</v>
       </c>
       <c r="I14" s="6"/>
-      <c r="J14" s="188" t="s">
+      <c r="J14" s="170" t="s">
         <v>288</v>
       </c>
-      <c r="K14" s="189"/>
+      <c r="K14" s="171"/>
       <c r="L14" s="136"/>
-      <c r="M14" s="188" t="s">
+      <c r="M14" s="170" t="s">
         <v>289</v>
       </c>
-      <c r="N14" s="189"/>
+      <c r="N14" s="171"/>
       <c r="O14" s="39"/>
       <c r="P14" s="39"/>
       <c r="Q14" s="39"/>
@@ -34466,15 +36725,15 @@
         <v>0.35138888888888892</v>
       </c>
       <c r="I21" s="6"/>
-      <c r="J21" s="188" t="s">
+      <c r="J21" s="170" t="s">
         <v>290</v>
       </c>
-      <c r="K21" s="189"/>
+      <c r="K21" s="171"/>
       <c r="L21" s="136"/>
-      <c r="M21" s="188" t="s">
+      <c r="M21" s="170" t="s">
         <v>291</v>
       </c>
-      <c r="N21" s="189"/>
+      <c r="N21" s="171"/>
       <c r="O21" s="39"/>
       <c r="P21" s="89" t="s">
         <v>31</v>
@@ -34856,15 +37115,15 @@
         <v>0.11805555555555557</v>
       </c>
       <c r="I28" s="39"/>
-      <c r="J28" s="188" t="s">
+      <c r="J28" s="170" t="s">
         <v>292</v>
       </c>
-      <c r="K28" s="189"/>
+      <c r="K28" s="171"/>
       <c r="L28" s="136"/>
-      <c r="M28" s="188" t="s">
+      <c r="M28" s="170" t="s">
         <v>293</v>
       </c>
-      <c r="N28" s="189"/>
+      <c r="N28" s="171"/>
       <c r="O28" s="39"/>
       <c r="P28" s="93" t="s">
         <v>38</v>
@@ -35211,15 +37470,15 @@
       <c r="G35" s="30"/>
       <c r="H35" s="61"/>
       <c r="I35" s="39"/>
-      <c r="J35" s="188" t="s">
+      <c r="J35" s="170" t="s">
         <v>294</v>
       </c>
-      <c r="K35" s="189"/>
+      <c r="K35" s="171"/>
       <c r="L35" s="136"/>
-      <c r="M35" s="188" t="s">
+      <c r="M35" s="170" t="s">
         <v>295</v>
       </c>
-      <c r="N35" s="189"/>
+      <c r="N35" s="171"/>
       <c r="O35" s="39"/>
       <c r="P35" s="39"/>
       <c r="Q35" s="39"/>
@@ -35254,9 +37513,9 @@
         <v>4.9305555555555554E-2</v>
       </c>
       <c r="O36" s="39"/>
-      <c r="P36" s="180"/>
-      <c r="Q36" s="180"/>
-      <c r="R36" s="180"/>
+      <c r="P36" s="172"/>
+      <c r="Q36" s="172"/>
+      <c r="R36" s="172"/>
       <c r="S36" s="111"/>
       <c r="T36" s="16"/>
       <c r="U36" s="16"/>
@@ -35287,9 +37546,9 @@
         <v>0.18472222222222223</v>
       </c>
       <c r="O37" s="39"/>
-      <c r="P37" s="187"/>
-      <c r="Q37" s="187"/>
-      <c r="R37" s="187"/>
+      <c r="P37" s="175"/>
+      <c r="Q37" s="175"/>
+      <c r="R37" s="175"/>
       <c r="S37" s="111"/>
       <c r="T37" s="16"/>
       <c r="U37" s="16"/>
@@ -35320,9 +37579,9 @@
         <v>0.21249999999999999</v>
       </c>
       <c r="O38" s="39"/>
-      <c r="P38" s="180"/>
-      <c r="Q38" s="180"/>
-      <c r="R38" s="180"/>
+      <c r="P38" s="172"/>
+      <c r="Q38" s="172"/>
+      <c r="R38" s="172"/>
       <c r="S38" s="111"/>
       <c r="T38" s="16"/>
       <c r="U38" s="16"/>
@@ -35353,9 +37612,9 @@
         <v>0.26527777777777778</v>
       </c>
       <c r="O39" s="39"/>
-      <c r="P39" s="180"/>
-      <c r="Q39" s="180"/>
-      <c r="R39" s="180"/>
+      <c r="P39" s="172"/>
+      <c r="Q39" s="172"/>
+      <c r="R39" s="172"/>
       <c r="S39" s="124"/>
       <c r="T39" s="16"/>
       <c r="U39" s="16"/>
@@ -35386,9 +37645,9 @@
         <v>0.75347222222222221</v>
       </c>
       <c r="O40" s="39"/>
-      <c r="P40" s="180"/>
-      <c r="Q40" s="180"/>
-      <c r="R40" s="180"/>
+      <c r="P40" s="172"/>
+      <c r="Q40" s="172"/>
+      <c r="R40" s="172"/>
       <c r="S40" s="124"/>
       <c r="T40" s="16"/>
       <c r="U40" s="16"/>
@@ -35414,9 +37673,9 @@
         <v>1.0513888888888889</v>
       </c>
       <c r="O41" s="39"/>
-      <c r="P41" s="180"/>
-      <c r="Q41" s="180"/>
-      <c r="R41" s="180"/>
+      <c r="P41" s="172"/>
+      <c r="Q41" s="172"/>
+      <c r="R41" s="172"/>
       <c r="S41" s="124"/>
       <c r="T41" s="16"/>
       <c r="U41" s="16"/>
@@ -38416,11 +40675,11 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="3.140625" style="130" customWidth="1"/>
-    <col min="3" max="3" width="35.7109375" style="130" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" style="130" customWidth="1"/>
     <col min="4" max="4" width="7.140625" style="130" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" style="156" customWidth="1"/>
     <col min="6" max="7" width="12.85546875" style="130" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" style="130" customWidth="1"/>
+    <col min="8" max="8" width="10" style="130" customWidth="1"/>
     <col min="9" max="9" width="3.140625" style="130" customWidth="1"/>
     <col min="10" max="10" width="30" style="130" customWidth="1"/>
     <col min="11" max="11" width="9.28515625" style="130" customWidth="1"/>
@@ -38486,15 +40745,15 @@
         <v>20</v>
       </c>
       <c r="I2" s="6"/>
-      <c r="J2" s="188" t="s">
+      <c r="J2" s="170" t="s">
         <v>284</v>
       </c>
-      <c r="K2" s="190"/>
+      <c r="K2" s="192"/>
       <c r="L2" s="136"/>
-      <c r="M2" s="190" t="s">
+      <c r="M2" s="192" t="s">
         <v>285</v>
       </c>
-      <c r="N2" s="189"/>
+      <c r="N2" s="171"/>
       <c r="O2" s="39"/>
       <c r="P2" s="39"/>
       <c r="Q2" s="39"/>
@@ -38824,15 +41083,15 @@
         <v>1.1847222222222222</v>
       </c>
       <c r="I10" s="6"/>
-      <c r="J10" s="188" t="s">
+      <c r="J10" s="170" t="s">
         <v>286</v>
       </c>
-      <c r="K10" s="189"/>
+      <c r="K10" s="171"/>
       <c r="L10" s="136"/>
-      <c r="M10" s="188" t="s">
+      <c r="M10" s="170" t="s">
         <v>287</v>
       </c>
-      <c r="N10" s="189"/>
+      <c r="N10" s="171"/>
       <c r="O10" s="39"/>
       <c r="P10" s="39"/>
       <c r="Q10" s="39"/>
@@ -39129,15 +41388,15 @@
         <v>6.063194444444445</v>
       </c>
       <c r="I17" s="6"/>
-      <c r="J17" s="188" t="s">
+      <c r="J17" s="170" t="s">
         <v>288</v>
       </c>
-      <c r="K17" s="189"/>
+      <c r="K17" s="171"/>
       <c r="L17" s="136"/>
-      <c r="M17" s="188" t="s">
+      <c r="M17" s="170" t="s">
         <v>289</v>
       </c>
-      <c r="N17" s="189"/>
+      <c r="N17" s="171"/>
       <c r="O17" s="39"/>
       <c r="P17" s="39"/>
       <c r="Q17" s="39"/>
@@ -39359,15 +41618,15 @@
         <v>0.50555555555555554</v>
       </c>
       <c r="I22" s="6"/>
-      <c r="J22" s="188" t="s">
+      <c r="J22" s="170" t="s">
         <v>290</v>
       </c>
-      <c r="K22" s="189"/>
+      <c r="K22" s="171"/>
       <c r="L22" s="136"/>
-      <c r="M22" s="188" t="s">
+      <c r="M22" s="170" t="s">
         <v>291</v>
       </c>
-      <c r="N22" s="189"/>
+      <c r="N22" s="171"/>
       <c r="O22" s="39"/>
       <c r="P22" s="63" t="s">
         <v>32</v>
@@ -39718,15 +41977,15 @@
         <v>2.6388888888888889E-2</v>
       </c>
       <c r="I28" s="39"/>
-      <c r="J28" s="188" t="s">
+      <c r="J28" s="170" t="s">
         <v>292</v>
       </c>
-      <c r="K28" s="189"/>
+      <c r="K28" s="171"/>
       <c r="L28" s="136"/>
-      <c r="M28" s="188" t="s">
+      <c r="M28" s="170" t="s">
         <v>293</v>
       </c>
-      <c r="N28" s="189"/>
+      <c r="N28" s="171"/>
       <c r="O28" s="39"/>
       <c r="P28" s="93" t="s">
         <v>38</v>
@@ -40092,15 +42351,15 @@
         <v>0.14722222222222223</v>
       </c>
       <c r="I34" s="39"/>
-      <c r="J34" s="188" t="s">
+      <c r="J34" s="170" t="s">
         <v>294</v>
       </c>
-      <c r="K34" s="189"/>
+      <c r="K34" s="171"/>
       <c r="L34" s="136"/>
-      <c r="M34" s="188" t="s">
+      <c r="M34" s="170" t="s">
         <v>295</v>
       </c>
-      <c r="N34" s="189"/>
+      <c r="N34" s="171"/>
       <c r="O34" s="39"/>
       <c r="P34" s="125" t="s">
         <v>77</v>
@@ -40207,9 +42466,9 @@
         <v>0.36944444444444446</v>
       </c>
       <c r="O36" s="39"/>
-      <c r="P36" s="180"/>
-      <c r="Q36" s="180"/>
-      <c r="R36" s="180"/>
+      <c r="P36" s="172"/>
+      <c r="Q36" s="172"/>
+      <c r="R36" s="172"/>
       <c r="S36" s="111"/>
       <c r="T36" s="16"/>
       <c r="U36" s="16"/>
@@ -40254,9 +42513,9 @@
         <v>7.9166666666666663E-2</v>
       </c>
       <c r="O37" s="39"/>
-      <c r="P37" s="187"/>
-      <c r="Q37" s="180"/>
-      <c r="R37" s="180"/>
+      <c r="P37" s="175"/>
+      <c r="Q37" s="172"/>
+      <c r="R37" s="172"/>
       <c r="S37" s="111"/>
       <c r="T37" s="16"/>
       <c r="U37" s="16"/>
@@ -40288,9 +42547,9 @@
       </c>
       <c r="I38" s="39"/>
       <c r="O38" s="39"/>
-      <c r="P38" s="180"/>
-      <c r="Q38" s="180"/>
-      <c r="R38" s="180"/>
+      <c r="P38" s="172"/>
+      <c r="Q38" s="172"/>
+      <c r="R38" s="172"/>
       <c r="S38" s="111"/>
       <c r="T38" s="16"/>
       <c r="U38" s="16"/>
@@ -40308,9 +42567,9 @@
       <c r="H39" s="138"/>
       <c r="I39" s="39"/>
       <c r="O39" s="39"/>
-      <c r="P39" s="180"/>
-      <c r="Q39" s="180"/>
-      <c r="R39" s="180"/>
+      <c r="P39" s="172"/>
+      <c r="Q39" s="172"/>
+      <c r="R39" s="172"/>
       <c r="S39" s="124"/>
       <c r="T39" s="16"/>
       <c r="U39" s="16"/>
@@ -40328,9 +42587,9 @@
       <c r="H40" s="61"/>
       <c r="I40" s="39"/>
       <c r="O40" s="39"/>
-      <c r="P40" s="180"/>
-      <c r="Q40" s="180"/>
-      <c r="R40" s="180"/>
+      <c r="P40" s="172"/>
+      <c r="Q40" s="172"/>
+      <c r="R40" s="172"/>
       <c r="S40" s="124"/>
       <c r="T40" s="16"/>
       <c r="U40" s="16"/>
@@ -40348,9 +42607,9 @@
       <c r="H41" s="61"/>
       <c r="I41" s="39"/>
       <c r="O41" s="39"/>
-      <c r="P41" s="180"/>
-      <c r="Q41" s="180"/>
-      <c r="R41" s="180"/>
+      <c r="P41" s="172"/>
+      <c r="Q41" s="172"/>
+      <c r="R41" s="172"/>
       <c r="S41" s="124"/>
       <c r="T41" s="16"/>
       <c r="U41" s="16"/>
@@ -43342,7 +45601,7 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="3.140625" style="130" customWidth="1"/>
-    <col min="3" max="3" width="37.140625" style="130" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" style="130" customWidth="1"/>
     <col min="4" max="4" width="7.140625" style="130" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" style="156" customWidth="1"/>
     <col min="6" max="7" width="12.85546875" style="130" customWidth="1"/>
@@ -43413,15 +45672,15 @@
         <v>20</v>
       </c>
       <c r="I2" s="6"/>
-      <c r="J2" s="188" t="s">
+      <c r="J2" s="170" t="s">
         <v>284</v>
       </c>
-      <c r="K2" s="189"/>
+      <c r="K2" s="171"/>
       <c r="L2" s="136"/>
-      <c r="M2" s="188" t="s">
+      <c r="M2" s="170" t="s">
         <v>285</v>
       </c>
-      <c r="N2" s="189"/>
+      <c r="N2" s="171"/>
       <c r="O2" s="39"/>
       <c r="P2" s="39"/>
       <c r="Q2" s="39"/>
@@ -43627,15 +45886,15 @@
         <v>0.33749999999999997</v>
       </c>
       <c r="I7" s="6"/>
-      <c r="J7" s="188" t="s">
+      <c r="J7" s="170" t="s">
         <v>286</v>
       </c>
-      <c r="K7" s="189"/>
+      <c r="K7" s="171"/>
       <c r="L7" s="136"/>
-      <c r="M7" s="188" t="s">
+      <c r="M7" s="170" t="s">
         <v>287</v>
       </c>
-      <c r="N7" s="189"/>
+      <c r="N7" s="171"/>
       <c r="O7" s="39"/>
       <c r="P7" s="39"/>
       <c r="Q7" s="39"/>
@@ -43842,15 +46101,15 @@
         <v>0.48819444444444443</v>
       </c>
       <c r="I12" s="6"/>
-      <c r="J12" s="188" t="s">
+      <c r="J12" s="170" t="s">
         <v>288</v>
       </c>
-      <c r="K12" s="189"/>
+      <c r="K12" s="171"/>
       <c r="L12" s="136"/>
-      <c r="M12" s="188" t="s">
+      <c r="M12" s="170" t="s">
         <v>289</v>
       </c>
-      <c r="N12" s="189"/>
+      <c r="N12" s="171"/>
       <c r="O12" s="39"/>
       <c r="P12" s="39"/>
       <c r="Q12" s="39"/>
@@ -44100,15 +46359,15 @@
         <v>2.6659722222222224</v>
       </c>
       <c r="I18" s="6"/>
-      <c r="J18" s="188" t="s">
+      <c r="J18" s="170" t="s">
         <v>290</v>
       </c>
-      <c r="K18" s="189"/>
+      <c r="K18" s="171"/>
       <c r="L18" s="136"/>
-      <c r="M18" s="188" t="s">
+      <c r="M18" s="170" t="s">
         <v>291</v>
       </c>
-      <c r="N18" s="189"/>
+      <c r="N18" s="171"/>
       <c r="O18" s="39"/>
       <c r="P18" s="39"/>
       <c r="Q18" s="39"/>
@@ -44345,15 +46604,15 @@
         <v>1.8131944444444446</v>
       </c>
       <c r="I23" s="6"/>
-      <c r="J23" s="188" t="s">
+      <c r="J23" s="170" t="s">
         <v>292</v>
       </c>
-      <c r="K23" s="189"/>
+      <c r="K23" s="171"/>
       <c r="L23" s="136"/>
-      <c r="M23" s="188" t="s">
+      <c r="M23" s="170" t="s">
         <v>293</v>
       </c>
-      <c r="N23" s="189"/>
+      <c r="N23" s="171"/>
       <c r="O23" s="39"/>
       <c r="P23" s="94" t="s">
         <v>33</v>
@@ -44709,15 +46968,15 @@
         <v>0.11527777777777778</v>
       </c>
       <c r="I29" s="39"/>
-      <c r="J29" s="188" t="s">
+      <c r="J29" s="170" t="s">
         <v>294</v>
       </c>
-      <c r="K29" s="189"/>
+      <c r="K29" s="171"/>
       <c r="L29" s="136"/>
-      <c r="M29" s="188" t="s">
+      <c r="M29" s="170" t="s">
         <v>295</v>
       </c>
-      <c r="N29" s="189"/>
+      <c r="N29" s="171"/>
       <c r="O29" s="39"/>
       <c r="P29" s="94" t="s">
         <v>39</v>
@@ -45049,9 +47308,9 @@
       <c r="H36" s="61"/>
       <c r="I36" s="39"/>
       <c r="O36" s="39"/>
-      <c r="P36" s="180"/>
-      <c r="Q36" s="180"/>
-      <c r="R36" s="180"/>
+      <c r="P36" s="172"/>
+      <c r="Q36" s="172"/>
+      <c r="R36" s="172"/>
       <c r="S36" s="111"/>
       <c r="T36" s="16"/>
       <c r="U36" s="16"/>
@@ -45069,9 +47328,9 @@
       <c r="H37" s="61"/>
       <c r="I37" s="39"/>
       <c r="O37" s="39"/>
-      <c r="P37" s="187"/>
-      <c r="Q37" s="180"/>
-      <c r="R37" s="180"/>
+      <c r="P37" s="175"/>
+      <c r="Q37" s="172"/>
+      <c r="R37" s="172"/>
       <c r="S37" s="111"/>
       <c r="T37" s="16"/>
       <c r="U37" s="16"/>
@@ -45089,9 +47348,9 @@
       <c r="H38" s="61"/>
       <c r="I38" s="39"/>
       <c r="O38" s="39"/>
-      <c r="P38" s="180"/>
-      <c r="Q38" s="180"/>
-      <c r="R38" s="180"/>
+      <c r="P38" s="172"/>
+      <c r="Q38" s="172"/>
+      <c r="R38" s="172"/>
       <c r="S38" s="111"/>
       <c r="T38" s="16"/>
       <c r="U38" s="16"/>
@@ -45109,9 +47368,9 @@
       <c r="H39" s="61"/>
       <c r="I39" s="39"/>
       <c r="O39" s="39"/>
-      <c r="P39" s="180"/>
-      <c r="Q39" s="180"/>
-      <c r="R39" s="180"/>
+      <c r="P39" s="172"/>
+      <c r="Q39" s="172"/>
+      <c r="R39" s="172"/>
       <c r="S39" s="124"/>
       <c r="T39" s="16"/>
       <c r="U39" s="16"/>
@@ -45129,9 +47388,9 @@
       <c r="H40" s="62"/>
       <c r="I40" s="39"/>
       <c r="O40" s="39"/>
-      <c r="P40" s="180"/>
-      <c r="Q40" s="180"/>
-      <c r="R40" s="180"/>
+      <c r="P40" s="172"/>
+      <c r="Q40" s="172"/>
+      <c r="R40" s="172"/>
       <c r="S40" s="124"/>
       <c r="T40" s="16"/>
       <c r="U40" s="16"/>
@@ -45149,9 +47408,9 @@
       <c r="H41" s="61"/>
       <c r="I41" s="39"/>
       <c r="O41" s="39"/>
-      <c r="P41" s="180"/>
-      <c r="Q41" s="180"/>
-      <c r="R41" s="180"/>
+      <c r="P41" s="172"/>
+      <c r="Q41" s="172"/>
+      <c r="R41" s="172"/>
       <c r="S41" s="124"/>
       <c r="T41" s="16"/>
       <c r="U41" s="16"/>
@@ -48145,11 +50404,11 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="3.140625" style="130" customWidth="1"/>
-    <col min="3" max="3" width="37.140625" style="130" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" style="130" customWidth="1"/>
     <col min="4" max="4" width="7.140625" style="130" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" style="156" customWidth="1"/>
     <col min="6" max="7" width="12.85546875" style="130" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" style="130" customWidth="1"/>
+    <col min="8" max="8" width="10" style="130" customWidth="1"/>
     <col min="9" max="9" width="3.140625" style="130" customWidth="1"/>
     <col min="10" max="10" width="30" style="130" customWidth="1"/>
     <col min="11" max="11" width="9.28515625" style="130" customWidth="1"/>
@@ -48158,7 +50417,8 @@
     <col min="14" max="14" width="9.28515625" style="130" customWidth="1"/>
     <col min="15" max="15" width="3.140625" style="130" customWidth="1"/>
     <col min="16" max="16" width="5.7109375" style="130" customWidth="1"/>
-    <col min="17" max="19" width="10" style="130" customWidth="1"/>
+    <col min="17" max="18" width="10" style="130" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="130" customWidth="1"/>
     <col min="20" max="20" width="3.140625" style="130" customWidth="1"/>
     <col min="21" max="21" width="42.85546875" style="130" customWidth="1"/>
     <col min="22" max="22" width="3.140625" style="130" customWidth="1"/>
@@ -48216,15 +50476,15 @@
         <v>20</v>
       </c>
       <c r="I2" s="6"/>
-      <c r="J2" s="188" t="s">
+      <c r="J2" s="170" t="s">
         <v>284</v>
       </c>
-      <c r="K2" s="189"/>
+      <c r="K2" s="171"/>
       <c r="L2" s="136"/>
-      <c r="M2" s="188" t="s">
+      <c r="M2" s="170" t="s">
         <v>285</v>
       </c>
-      <c r="N2" s="189"/>
+      <c r="N2" s="171"/>
       <c r="O2" s="39"/>
       <c r="P2" s="39"/>
       <c r="Q2" s="39"/>
@@ -48434,15 +50694,15 @@
         <v>2.5249999999999999</v>
       </c>
       <c r="I7" s="6"/>
-      <c r="J7" s="188" t="s">
+      <c r="J7" s="170" t="s">
         <v>286</v>
       </c>
-      <c r="K7" s="189"/>
+      <c r="K7" s="171"/>
       <c r="L7" s="136"/>
-      <c r="M7" s="188" t="s">
+      <c r="M7" s="170" t="s">
         <v>287</v>
       </c>
-      <c r="N7" s="189"/>
+      <c r="N7" s="171"/>
       <c r="O7" s="39"/>
       <c r="P7" s="39"/>
       <c r="Q7" s="39"/>
@@ -48640,15 +50900,15 @@
         <v>1.8055555555555554E-2</v>
       </c>
       <c r="I12" s="6"/>
-      <c r="J12" s="188" t="s">
+      <c r="J12" s="170" t="s">
         <v>288</v>
       </c>
-      <c r="K12" s="189"/>
+      <c r="K12" s="171"/>
       <c r="L12" s="136"/>
-      <c r="M12" s="188" t="s">
+      <c r="M12" s="170" t="s">
         <v>289</v>
       </c>
-      <c r="N12" s="189"/>
+      <c r="N12" s="171"/>
       <c r="O12" s="39"/>
       <c r="P12" s="39"/>
       <c r="Q12" s="39"/>
@@ -48855,15 +51115,15 @@
         <v>0.30902777777777779</v>
       </c>
       <c r="I17" s="6"/>
-      <c r="J17" s="188" t="s">
+      <c r="J17" s="170" t="s">
         <v>290</v>
       </c>
-      <c r="K17" s="189"/>
+      <c r="K17" s="171"/>
       <c r="L17" s="136"/>
-      <c r="M17" s="188" t="s">
+      <c r="M17" s="170" t="s">
         <v>291</v>
       </c>
-      <c r="N17" s="189"/>
+      <c r="N17" s="171"/>
       <c r="O17" s="39"/>
       <c r="P17" s="39"/>
       <c r="Q17" s="39"/>
@@ -49083,15 +51343,15 @@
         <v>2.0166666666666666</v>
       </c>
       <c r="I22" s="6"/>
-      <c r="J22" s="188" t="s">
+      <c r="J22" s="170" t="s">
         <v>292</v>
       </c>
-      <c r="K22" s="189"/>
+      <c r="K22" s="171"/>
       <c r="L22" s="136"/>
-      <c r="M22" s="191" t="s">
+      <c r="M22" s="173" t="s">
         <v>293</v>
       </c>
-      <c r="N22" s="192"/>
+      <c r="N22" s="174"/>
       <c r="O22" s="39"/>
       <c r="P22" s="63" t="s">
         <v>32</v>
@@ -49506,15 +51766,15 @@
         <v>0.35</v>
       </c>
       <c r="I29" s="39"/>
-      <c r="J29" s="188" t="s">
+      <c r="J29" s="170" t="s">
         <v>294</v>
       </c>
-      <c r="K29" s="189"/>
+      <c r="K29" s="171"/>
       <c r="L29" s="136"/>
-      <c r="M29" s="188" t="s">
+      <c r="M29" s="170" t="s">
         <v>295</v>
       </c>
-      <c r="N29" s="189"/>
+      <c r="N29" s="171"/>
       <c r="O29" s="39"/>
       <c r="P29" s="94" t="s">
         <v>39</v>
@@ -49575,8 +51835,12 @@
         <v>0.58750000000000002</v>
       </c>
       <c r="L30" s="137"/>
-      <c r="M30" s="131"/>
-      <c r="N30" s="72"/>
+      <c r="M30" s="131" t="s">
+        <v>555</v>
+      </c>
+      <c r="N30" s="72">
+        <v>0.19166666666666668</v>
+      </c>
       <c r="O30" s="39"/>
       <c r="P30" s="93" t="s">
         <v>40</v>
@@ -49637,8 +51901,12 @@
         <v>0.33402777777777776</v>
       </c>
       <c r="L31" s="137"/>
-      <c r="M31" s="101"/>
-      <c r="N31" s="60"/>
+      <c r="M31" s="101" t="s">
+        <v>644</v>
+      </c>
+      <c r="N31" s="60">
+        <v>7.013888888888889E-2</v>
+      </c>
       <c r="O31" s="39"/>
       <c r="P31" s="94" t="s">
         <v>41</v>
@@ -49758,19 +52026,31 @@
       <c r="P33" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="Q33" s="64"/>
-      <c r="R33" s="64"/>
+      <c r="Q33" s="64">
+        <f>SUM(W33:X33,H38:H40)</f>
+        <v>2.8902777777777775</v>
+      </c>
+      <c r="R33" s="64">
+        <f>SUM(N30:N31)</f>
+        <v>0.26180555555555557</v>
+      </c>
       <c r="S33" s="90">
         <f>Q33+R33</f>
-        <v>0</v>
+        <v>3.1520833333333331</v>
       </c>
       <c r="T33" s="39" t="s">
         <v>256</v>
       </c>
-      <c r="U33" s="166"/>
+      <c r="U33" s="128" t="s">
+        <v>648</v>
+      </c>
       <c r="V33" s="39"/>
-      <c r="W33" s="147"/>
-      <c r="X33" s="111"/>
+      <c r="W33" s="147">
+        <v>0.60833333333333328</v>
+      </c>
+      <c r="X33" s="111">
+        <v>0.75694444444444442</v>
+      </c>
     </row>
     <row r="34" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="39"/>
@@ -49804,15 +52084,15 @@
       </c>
       <c r="Q34" s="126">
         <f>SUM(Q22:Q33)</f>
-        <v>30.684722222222227</v>
+        <v>33.575000000000003</v>
       </c>
       <c r="R34" s="126">
         <f>SUM(R22:R33)</f>
-        <v>8.8458333333333332</v>
+        <v>9.1076388888888893</v>
       </c>
       <c r="S34" s="127">
         <f>SUM(S22:S33)</f>
-        <v>39.530555555555559</v>
+        <v>42.682638888888889</v>
       </c>
       <c r="T34" s="39"/>
       <c r="U34" s="39"/>
@@ -49878,9 +52158,9 @@
       </c>
       <c r="I36" s="39"/>
       <c r="O36" s="39"/>
-      <c r="P36" s="180"/>
-      <c r="Q36" s="180"/>
-      <c r="R36" s="180"/>
+      <c r="P36" s="172"/>
+      <c r="Q36" s="172"/>
+      <c r="R36" s="172"/>
       <c r="S36" s="111"/>
       <c r="T36" s="16"/>
       <c r="U36" s="16"/>
@@ -49905,16 +52185,16 @@
         <v>468</v>
       </c>
       <c r="G37" s="74" t="s">
-        <v>13</v>
-      </c>
-      <c r="H37" s="75" t="s">
-        <v>13</v>
+        <v>108</v>
+      </c>
+      <c r="H37" s="75">
+        <v>1.2645833333333334</v>
       </c>
       <c r="I37" s="39"/>
       <c r="O37" s="39"/>
-      <c r="P37" s="187"/>
-      <c r="Q37" s="180"/>
-      <c r="R37" s="180"/>
+      <c r="P37" s="175"/>
+      <c r="Q37" s="172"/>
+      <c r="R37" s="172"/>
       <c r="S37" s="111"/>
       <c r="T37" s="16"/>
       <c r="U37" s="16"/>
@@ -49926,17 +52206,29 @@
       <c r="B38" s="78">
         <v>36</v>
       </c>
-      <c r="C38" s="54"/>
-      <c r="D38" s="54"/>
-      <c r="E38" s="153"/>
-      <c r="F38" s="69"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="60"/>
+      <c r="C38" s="54" t="s">
+        <v>641</v>
+      </c>
+      <c r="D38" s="54">
+        <v>1999</v>
+      </c>
+      <c r="E38" s="153" t="s">
+        <v>443</v>
+      </c>
+      <c r="F38" s="69" t="s">
+        <v>111</v>
+      </c>
+      <c r="G38" s="69" t="s">
+        <v>115</v>
+      </c>
+      <c r="H38" s="60">
+        <v>0.51249999999999996</v>
+      </c>
       <c r="I38" s="39"/>
       <c r="O38" s="39"/>
-      <c r="P38" s="180"/>
-      <c r="Q38" s="180"/>
-      <c r="R38" s="180"/>
+      <c r="P38" s="172"/>
+      <c r="Q38" s="172"/>
+      <c r="R38" s="172"/>
       <c r="S38" s="111"/>
       <c r="T38" s="16"/>
       <c r="U38" s="16"/>
@@ -49948,17 +52240,29 @@
       <c r="B39" s="70">
         <v>37</v>
       </c>
-      <c r="C39" s="73"/>
-      <c r="D39" s="73"/>
-      <c r="E39" s="152"/>
-      <c r="F39" s="74"/>
-      <c r="G39" s="74"/>
-      <c r="H39" s="75"/>
+      <c r="C39" s="73" t="s">
+        <v>642</v>
+      </c>
+      <c r="D39" s="73">
+        <v>2003</v>
+      </c>
+      <c r="E39" s="152" t="s">
+        <v>440</v>
+      </c>
+      <c r="F39" s="74" t="s">
+        <v>117</v>
+      </c>
+      <c r="G39" s="74" t="s">
+        <v>559</v>
+      </c>
+      <c r="H39" s="75">
+        <v>0.22083333333333333</v>
+      </c>
       <c r="I39" s="39"/>
       <c r="O39" s="39"/>
-      <c r="P39" s="180"/>
-      <c r="Q39" s="180"/>
-      <c r="R39" s="180"/>
+      <c r="P39" s="172"/>
+      <c r="Q39" s="172"/>
+      <c r="R39" s="172"/>
       <c r="S39" s="124"/>
       <c r="T39" s="16"/>
       <c r="U39" s="16"/>
@@ -49970,17 +52274,29 @@
       <c r="B40" s="78">
         <v>38</v>
       </c>
-      <c r="C40" s="54"/>
-      <c r="D40" s="54"/>
-      <c r="E40" s="153"/>
-      <c r="F40" s="69"/>
-      <c r="G40" s="69"/>
-      <c r="H40" s="60"/>
+      <c r="C40" s="54" t="s">
+        <v>643</v>
+      </c>
+      <c r="D40" s="54">
+        <v>2025</v>
+      </c>
+      <c r="E40" s="153" t="s">
+        <v>440</v>
+      </c>
+      <c r="F40" s="69" t="s">
+        <v>559</v>
+      </c>
+      <c r="G40" s="69" t="s">
+        <v>252</v>
+      </c>
+      <c r="H40" s="60">
+        <v>0.79166666666666663</v>
+      </c>
       <c r="I40" s="39"/>
       <c r="O40" s="39"/>
-      <c r="P40" s="180"/>
-      <c r="Q40" s="180"/>
-      <c r="R40" s="180"/>
+      <c r="P40" s="172"/>
+      <c r="Q40" s="172"/>
+      <c r="R40" s="172"/>
       <c r="S40" s="124"/>
       <c r="T40" s="16"/>
       <c r="U40" s="16"/>
@@ -49992,17 +52308,29 @@
       <c r="B41" s="70">
         <v>39</v>
       </c>
-      <c r="C41" s="73"/>
-      <c r="D41" s="73"/>
-      <c r="E41" s="152"/>
-      <c r="F41" s="74"/>
-      <c r="G41" s="74"/>
-      <c r="H41" s="75"/>
+      <c r="C41" s="73" t="s">
+        <v>645</v>
+      </c>
+      <c r="D41" s="73">
+        <v>2025</v>
+      </c>
+      <c r="E41" s="152" t="s">
+        <v>440</v>
+      </c>
+      <c r="F41" s="74" t="s">
+        <v>255</v>
+      </c>
+      <c r="G41" s="74" t="s">
+        <v>646</v>
+      </c>
+      <c r="H41" s="75">
+        <v>0.8125</v>
+      </c>
       <c r="I41" s="39"/>
       <c r="O41" s="39"/>
-      <c r="P41" s="180"/>
-      <c r="Q41" s="180"/>
-      <c r="R41" s="180"/>
+      <c r="P41" s="172"/>
+      <c r="Q41" s="172"/>
+      <c r="R41" s="172"/>
       <c r="S41" s="124"/>
       <c r="T41" s="16"/>
       <c r="U41" s="16"/>
@@ -50011,15 +52339,13 @@
     </row>
     <row r="42" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="39"/>
-      <c r="B42" s="123">
-        <v>40</v>
-      </c>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="154"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="102"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="162"/>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53"/>
+      <c r="H42" s="138"/>
       <c r="I42" s="39"/>
       <c r="O42" s="39"/>
       <c r="P42" s="39"/>
@@ -51887,7 +54213,7 @@
       </c>
       <c r="R117" s="44">
         <f>COUNTIF(D1:D57,Q117)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S117" s="39"/>
       <c r="T117" s="39"/>
@@ -52547,7 +54873,7 @@
       </c>
       <c r="R139" s="46">
         <f>COUNTIF(D3:D59,Q139)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S139" s="39"/>
       <c r="T139" s="39"/>
@@ -52667,7 +54993,7 @@
       </c>
       <c r="R143" s="46">
         <f>COUNTIF(D3:D59,Q143)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S143" s="39"/>
       <c r="T143" s="39"/>
@@ -52877,7 +55203,7 @@
       </c>
       <c r="R150" s="42">
         <f>SUM(R117:R149)</f>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="S150" s="39"/>
       <c r="T150" s="39"/>
@@ -52985,7 +55311,4265 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="Q24:Q25 Q28 Q30:Q32" formulaRange="1"/>
+    <ignoredError sqref="Q24:Q25 Q28 Q30:Q33" formulaRange="1"/>
+  </ignoredErrors>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB1BCA1-0DD6-4E3C-A390-9E8A1708064D}">
+  <dimension ref="A1:Z153"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="3.140625" style="130" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" style="130" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" style="130" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" style="156" customWidth="1"/>
+    <col min="6" max="7" width="12.85546875" style="130" customWidth="1"/>
+    <col min="8" max="8" width="10" style="130" customWidth="1"/>
+    <col min="9" max="9" width="3.140625" style="130" customWidth="1"/>
+    <col min="10" max="10" width="30" style="130" customWidth="1"/>
+    <col min="11" max="11" width="9.28515625" style="130" customWidth="1"/>
+    <col min="12" max="12" width="3.140625" style="130" customWidth="1"/>
+    <col min="13" max="13" width="30" style="130" customWidth="1"/>
+    <col min="14" max="14" width="9.28515625" style="130" customWidth="1"/>
+    <col min="15" max="15" width="3.140625" style="130" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" style="130" customWidth="1"/>
+    <col min="17" max="18" width="10" style="130" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="130" customWidth="1"/>
+    <col min="20" max="20" width="3.140625" style="130" customWidth="1"/>
+    <col min="21" max="21" width="42.85546875" style="130" customWidth="1"/>
+    <col min="22" max="22" width="3.140625" style="130" customWidth="1"/>
+    <col min="23" max="24" width="11.42578125" style="149"/>
+    <col min="25" max="26" width="11.42578125" style="111"/>
+    <col min="27" max="16384" width="11.42578125" style="130"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="39"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="111"/>
+    </row>
+    <row r="2" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="39"/>
+      <c r="B2" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="86" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="86" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="86" t="s">
+        <v>438</v>
+      </c>
+      <c r="F2" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="86" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="79" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="6"/>
+      <c r="J2" s="170" t="s">
+        <v>284</v>
+      </c>
+      <c r="K2" s="171"/>
+      <c r="L2" s="136"/>
+      <c r="M2" s="170" t="s">
+        <v>285</v>
+      </c>
+      <c r="N2" s="171"/>
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="39"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="111"/>
+    </row>
+    <row r="3" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="39"/>
+      <c r="B3" s="70">
+        <v>1</v>
+      </c>
+      <c r="C3" s="73" t="s">
+        <v>645</v>
+      </c>
+      <c r="D3" s="73">
+        <v>2025</v>
+      </c>
+      <c r="E3" s="152" t="s">
+        <v>440</v>
+      </c>
+      <c r="F3" s="74" t="s">
+        <v>647</v>
+      </c>
+      <c r="G3" s="74" t="s">
+        <v>260</v>
+      </c>
+      <c r="H3" s="75">
+        <v>0.8125</v>
+      </c>
+      <c r="I3" s="6"/>
+      <c r="J3" s="168" t="s">
+        <v>465</v>
+      </c>
+      <c r="K3" s="72">
+        <v>6.5972222222222224E-2</v>
+      </c>
+      <c r="L3" s="137"/>
+      <c r="M3" s="112" t="s">
+        <v>644</v>
+      </c>
+      <c r="N3" s="72">
+        <v>0.17986111111111111</v>
+      </c>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="111"/>
+    </row>
+    <row r="4" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="39"/>
+      <c r="B4" s="78">
+        <v>2</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>649</v>
+      </c>
+      <c r="D4" s="54">
+        <v>2013</v>
+      </c>
+      <c r="E4" s="153" t="s">
+        <v>440</v>
+      </c>
+      <c r="F4" s="69" t="s">
+        <v>482</v>
+      </c>
+      <c r="G4" s="69" t="s">
+        <v>651</v>
+      </c>
+      <c r="H4" s="60">
+        <v>0.25694444444444442</v>
+      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="114" t="s">
+        <v>303</v>
+      </c>
+      <c r="K4" s="60">
+        <v>0.11874999999999999</v>
+      </c>
+      <c r="L4" s="140"/>
+      <c r="M4" s="114"/>
+      <c r="N4" s="60"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="39"/>
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="111"/>
+    </row>
+    <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="39"/>
+      <c r="B5" s="70">
+        <v>3</v>
+      </c>
+      <c r="C5" s="73" t="s">
+        <v>650</v>
+      </c>
+      <c r="D5" s="73">
+        <v>2013</v>
+      </c>
+      <c r="E5" s="152" t="s">
+        <v>440</v>
+      </c>
+      <c r="F5" s="74" t="s">
+        <v>651</v>
+      </c>
+      <c r="G5" s="74" t="s">
+        <v>263</v>
+      </c>
+      <c r="H5" s="75">
+        <v>0.39166666666666666</v>
+      </c>
+      <c r="I5" s="6"/>
+      <c r="J5" s="135"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="163"/>
+      <c r="M5" s="135"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="39"/>
+      <c r="R5" s="39"/>
+      <c r="S5" s="39"/>
+      <c r="T5" s="39"/>
+      <c r="U5" s="39"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="111"/>
+    </row>
+    <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="39"/>
+      <c r="B6" s="78">
+        <v>4</v>
+      </c>
+      <c r="C6" s="54" t="s">
+        <v>652</v>
+      </c>
+      <c r="D6" s="54">
+        <v>2005</v>
+      </c>
+      <c r="E6" s="153" t="s">
+        <v>440</v>
+      </c>
+      <c r="F6" s="69" t="s">
+        <v>653</v>
+      </c>
+      <c r="G6" s="69" t="s">
+        <v>486</v>
+      </c>
+      <c r="H6" s="60">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="I6" s="6"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="111"/>
+    </row>
+    <row r="7" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="39"/>
+      <c r="B7" s="70">
+        <v>5</v>
+      </c>
+      <c r="C7" s="73" t="s">
+        <v>654</v>
+      </c>
+      <c r="D7" s="73">
+        <v>2005</v>
+      </c>
+      <c r="E7" s="152" t="s">
+        <v>440</v>
+      </c>
+      <c r="F7" s="74" t="s">
+        <v>655</v>
+      </c>
+      <c r="G7" s="74" t="s">
+        <v>135</v>
+      </c>
+      <c r="H7" s="75">
+        <v>0.88194444444444442</v>
+      </c>
+      <c r="I7" s="6"/>
+      <c r="J7" s="170" t="s">
+        <v>286</v>
+      </c>
+      <c r="K7" s="171"/>
+      <c r="L7" s="136"/>
+      <c r="M7" s="170" t="s">
+        <v>287</v>
+      </c>
+      <c r="N7" s="171"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="39"/>
+      <c r="S7" s="39"/>
+      <c r="T7" s="39"/>
+      <c r="U7" s="39"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="111"/>
+    </row>
+    <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="39"/>
+      <c r="B8" s="78">
+        <v>6</v>
+      </c>
+      <c r="C8" s="54" t="s">
+        <v>657</v>
+      </c>
+      <c r="D8" s="54">
+        <v>2011</v>
+      </c>
+      <c r="E8" s="153" t="s">
+        <v>440</v>
+      </c>
+      <c r="F8" s="69" t="s">
+        <v>656</v>
+      </c>
+      <c r="G8" s="69" t="s">
+        <v>282</v>
+      </c>
+      <c r="H8" s="60">
+        <v>2.9958333333333331</v>
+      </c>
+      <c r="I8" s="6"/>
+      <c r="J8" s="168"/>
+      <c r="K8" s="72"/>
+      <c r="L8" s="137"/>
+      <c r="M8" s="131"/>
+      <c r="N8" s="72"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="39"/>
+      <c r="S8" s="39"/>
+      <c r="T8" s="39"/>
+      <c r="U8" s="39"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="111"/>
+    </row>
+    <row r="9" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="39"/>
+      <c r="B9" s="70">
+        <v>7</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>659</v>
+      </c>
+      <c r="D9" s="73">
+        <v>2013</v>
+      </c>
+      <c r="E9" s="152" t="s">
+        <v>439</v>
+      </c>
+      <c r="F9" s="74" t="s">
+        <v>660</v>
+      </c>
+      <c r="G9" s="74" t="s">
+        <v>282</v>
+      </c>
+      <c r="H9" s="75">
+        <v>0.74513888888888891</v>
+      </c>
+      <c r="I9" s="6"/>
+      <c r="J9" s="114"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="137"/>
+      <c r="M9" s="101"/>
+      <c r="N9" s="60"/>
+      <c r="O9" s="39"/>
+      <c r="P9" s="39"/>
+      <c r="Q9" s="39"/>
+      <c r="R9" s="39"/>
+      <c r="S9" s="39"/>
+      <c r="T9" s="39"/>
+      <c r="U9" s="39"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="111"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="39"/>
+      <c r="B10" s="78">
+        <v>8</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>662</v>
+      </c>
+      <c r="D10" s="54">
+        <v>1997</v>
+      </c>
+      <c r="E10" s="153" t="s">
+        <v>439</v>
+      </c>
+      <c r="F10" s="69" t="s">
+        <v>384</v>
+      </c>
+      <c r="G10" s="69"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="135"/>
+      <c r="K10" s="77"/>
+      <c r="L10" s="163"/>
+      <c r="M10" s="135"/>
+      <c r="N10" s="77"/>
+      <c r="O10" s="39"/>
+      <c r="P10" s="39"/>
+      <c r="Q10" s="39"/>
+      <c r="R10" s="39"/>
+      <c r="S10" s="39"/>
+      <c r="T10" s="39"/>
+      <c r="U10" s="39"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="111"/>
+    </row>
+    <row r="11" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="39"/>
+      <c r="B11" s="70">
+        <v>9</v>
+      </c>
+      <c r="C11" s="73" t="s">
+        <v>663</v>
+      </c>
+      <c r="D11" s="73">
+        <v>2026</v>
+      </c>
+      <c r="E11" s="152" t="s">
+        <v>440</v>
+      </c>
+      <c r="F11" s="74" t="s">
+        <v>664</v>
+      </c>
+      <c r="G11" s="74"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="6"/>
+      <c r="O11" s="39"/>
+      <c r="P11" s="39"/>
+      <c r="Q11" s="39"/>
+      <c r="R11" s="39"/>
+      <c r="S11" s="39"/>
+      <c r="T11" s="39"/>
+      <c r="U11" s="39"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="111"/>
+    </row>
+    <row r="12" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="39"/>
+      <c r="B12" s="78">
+        <v>10</v>
+      </c>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="153"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="170" t="s">
+        <v>288</v>
+      </c>
+      <c r="K12" s="171"/>
+      <c r="L12" s="136"/>
+      <c r="M12" s="170" t="s">
+        <v>289</v>
+      </c>
+      <c r="N12" s="171"/>
+      <c r="O12" s="39"/>
+      <c r="P12" s="39"/>
+      <c r="Q12" s="39"/>
+      <c r="R12" s="39"/>
+      <c r="S12" s="39"/>
+      <c r="T12" s="39"/>
+      <c r="U12" s="39"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="111"/>
+    </row>
+    <row r="13" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="39"/>
+      <c r="B13" s="70">
+        <v>11</v>
+      </c>
+      <c r="C13" s="73"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="152"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="168"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="137"/>
+      <c r="M13" s="131"/>
+      <c r="N13" s="72"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="39"/>
+      <c r="Q13" s="39"/>
+      <c r="R13" s="39"/>
+      <c r="S13" s="39"/>
+      <c r="T13" s="39"/>
+      <c r="U13" s="39"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="111"/>
+    </row>
+    <row r="14" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="39"/>
+      <c r="B14" s="78">
+        <v>12</v>
+      </c>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="153"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="114"/>
+      <c r="K14" s="60"/>
+      <c r="L14" s="137"/>
+      <c r="M14" s="101"/>
+      <c r="N14" s="60"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="39"/>
+      <c r="Q14" s="39"/>
+      <c r="R14" s="39"/>
+      <c r="S14" s="39"/>
+      <c r="T14" s="39"/>
+      <c r="U14" s="39"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="111"/>
+    </row>
+    <row r="15" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="39"/>
+      <c r="B15" s="70">
+        <v>13</v>
+      </c>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="152"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="135"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="163"/>
+      <c r="M15" s="135"/>
+      <c r="N15" s="77"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="39"/>
+      <c r="S15" s="39"/>
+      <c r="T15" s="39"/>
+      <c r="U15" s="39"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="111"/>
+    </row>
+    <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="39"/>
+      <c r="B16" s="78">
+        <v>14</v>
+      </c>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="153"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="6"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="39"/>
+      <c r="R16" s="39"/>
+      <c r="S16" s="39"/>
+      <c r="T16" s="39"/>
+      <c r="U16" s="39"/>
+      <c r="V16" s="6"/>
+      <c r="W16" s="111"/>
+    </row>
+    <row r="17" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="39"/>
+      <c r="B17" s="70">
+        <v>15</v>
+      </c>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="152"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="75"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="170" t="s">
+        <v>290</v>
+      </c>
+      <c r="K17" s="171"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="170" t="s">
+        <v>291</v>
+      </c>
+      <c r="N17" s="171"/>
+      <c r="O17" s="39"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="39"/>
+      <c r="R17" s="39"/>
+      <c r="S17" s="39"/>
+      <c r="T17" s="39"/>
+      <c r="U17" s="39"/>
+      <c r="V17" s="6"/>
+      <c r="W17" s="111"/>
+    </row>
+    <row r="18" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="39"/>
+      <c r="B18" s="78">
+        <v>16</v>
+      </c>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="153"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="168"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="137"/>
+      <c r="M18" s="168"/>
+      <c r="N18" s="72"/>
+      <c r="O18" s="39"/>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="39"/>
+      <c r="R18" s="39"/>
+      <c r="S18" s="39"/>
+      <c r="T18" s="39"/>
+      <c r="U18" s="39"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="111"/>
+    </row>
+    <row r="19" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="39"/>
+      <c r="B19" s="70">
+        <v>17</v>
+      </c>
+      <c r="C19" s="73"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="152"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="114"/>
+      <c r="K19" s="60"/>
+      <c r="L19" s="137"/>
+      <c r="M19" s="114"/>
+      <c r="N19" s="60"/>
+      <c r="O19" s="39"/>
+      <c r="P19" s="39"/>
+      <c r="Q19" s="39"/>
+      <c r="R19" s="39"/>
+      <c r="S19" s="39"/>
+      <c r="T19" s="39"/>
+      <c r="U19" s="39"/>
+      <c r="V19" s="6"/>
+      <c r="W19" s="111"/>
+    </row>
+    <row r="20" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="39"/>
+      <c r="B20" s="78">
+        <v>18</v>
+      </c>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="153"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="135"/>
+      <c r="K20" s="77"/>
+      <c r="L20" s="163"/>
+      <c r="M20" s="135"/>
+      <c r="N20" s="77"/>
+      <c r="O20" s="39"/>
+      <c r="P20" s="39"/>
+      <c r="Q20" s="39"/>
+      <c r="R20" s="39"/>
+      <c r="S20" s="39"/>
+      <c r="T20" s="39"/>
+      <c r="U20" s="39"/>
+      <c r="V20" s="6"/>
+      <c r="W20" s="111"/>
+    </row>
+    <row r="21" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="39"/>
+      <c r="B21" s="70">
+        <v>19</v>
+      </c>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="75"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="61"/>
+      <c r="L21" s="61"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="61"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="89" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q21" s="91" t="s">
+        <v>122</v>
+      </c>
+      <c r="R21" s="91" t="s">
+        <v>121</v>
+      </c>
+      <c r="S21" s="92" t="s">
+        <v>128</v>
+      </c>
+      <c r="T21" s="39"/>
+      <c r="U21" s="88" t="s">
+        <v>62</v>
+      </c>
+      <c r="V21" s="146"/>
+      <c r="W21" s="147"/>
+      <c r="X21" s="150"/>
+      <c r="Y21" s="147"/>
+    </row>
+    <row r="22" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="39"/>
+      <c r="B22" s="78">
+        <v>20</v>
+      </c>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="153"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="170" t="s">
+        <v>292</v>
+      </c>
+      <c r="K22" s="171"/>
+      <c r="L22" s="136"/>
+      <c r="M22" s="173" t="s">
+        <v>293</v>
+      </c>
+      <c r="N22" s="174"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q22" s="95">
+        <f>SUM(H4:H7,W22:X22)</f>
+        <v>2.7666666666666666</v>
+      </c>
+      <c r="R22" s="95">
+        <f>SUM(K3:K4)</f>
+        <v>0.18472222222222223</v>
+      </c>
+      <c r="S22" s="96">
+        <f>SUM(Q22:R22)</f>
+        <v>2.9513888888888888</v>
+      </c>
+      <c r="T22" s="39"/>
+      <c r="U22" s="104" t="s">
+        <v>658</v>
+      </c>
+      <c r="V22" s="146"/>
+      <c r="W22" s="147">
+        <v>4.8611111111111112E-2</v>
+      </c>
+      <c r="X22" s="147">
+        <v>0.66249999999999998</v>
+      </c>
+      <c r="Y22" s="147"/>
+    </row>
+    <row r="23" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="39"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="162"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="138"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="168"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="140"/>
+      <c r="M23" s="168"/>
+      <c r="N23" s="72"/>
+      <c r="O23" s="39"/>
+      <c r="P23" s="94" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q23" s="64">
+        <f>SUM(H9,W23:X23)</f>
+        <v>3.5451388888888893</v>
+      </c>
+      <c r="R23" s="64">
+        <f>SUM(N3:N4)</f>
+        <v>0.17986111111111111</v>
+      </c>
+      <c r="S23" s="90">
+        <f>SUM(Q23:R23)</f>
+        <v>3.7250000000000005</v>
+      </c>
+      <c r="T23" s="39"/>
+      <c r="U23" s="98" t="s">
+        <v>661</v>
+      </c>
+      <c r="V23" s="146"/>
+      <c r="W23" s="147">
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="X23" s="147">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="Y23" s="147">
+        <v>6.1111111111111109E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="39"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="155"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="114"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="137"/>
+      <c r="M24" s="114"/>
+      <c r="N24" s="60"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="93" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q24" s="81"/>
+      <c r="R24" s="81"/>
+      <c r="S24" s="97"/>
+      <c r="T24" s="39"/>
+      <c r="U24" s="99"/>
+      <c r="V24" s="146"/>
+      <c r="W24" s="147"/>
+      <c r="X24" s="147"/>
+      <c r="Y24" s="147"/>
+    </row>
+    <row r="25" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="39"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="155"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="135"/>
+      <c r="K25" s="77"/>
+      <c r="L25" s="163"/>
+      <c r="M25" s="135"/>
+      <c r="N25" s="77"/>
+      <c r="O25" s="39"/>
+      <c r="P25" s="94" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q25" s="64"/>
+      <c r="R25" s="64"/>
+      <c r="S25" s="90"/>
+      <c r="T25" s="39"/>
+      <c r="U25" s="98"/>
+      <c r="V25" s="146"/>
+      <c r="W25" s="147"/>
+      <c r="X25" s="147"/>
+      <c r="Y25" s="147"/>
+    </row>
+    <row r="26" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="39"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="155"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="39"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="93" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q26" s="81"/>
+      <c r="R26" s="81"/>
+      <c r="S26" s="97"/>
+      <c r="T26" s="39"/>
+      <c r="U26" s="100"/>
+      <c r="V26" s="146"/>
+      <c r="W26" s="147"/>
+      <c r="X26" s="147"/>
+      <c r="Y26" s="147"/>
+    </row>
+    <row r="27" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="39"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="155"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="170" t="s">
+        <v>294</v>
+      </c>
+      <c r="K27" s="171"/>
+      <c r="L27" s="136"/>
+      <c r="M27" s="170" t="s">
+        <v>295</v>
+      </c>
+      <c r="N27" s="171"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q27" s="64"/>
+      <c r="R27" s="64"/>
+      <c r="S27" s="90"/>
+      <c r="T27" s="39"/>
+      <c r="U27" s="98"/>
+      <c r="V27" s="146"/>
+      <c r="W27" s="147"/>
+      <c r="X27" s="111"/>
+      <c r="Y27" s="147"/>
+    </row>
+    <row r="28" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="39"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="155"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="168"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="137"/>
+      <c r="M28" s="131"/>
+      <c r="N28" s="72"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="93" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q28" s="81"/>
+      <c r="R28" s="81"/>
+      <c r="S28" s="97"/>
+      <c r="T28" s="39"/>
+      <c r="U28" s="99"/>
+      <c r="V28" s="146"/>
+      <c r="W28" s="147"/>
+      <c r="X28" s="147"/>
+      <c r="Y28" s="147"/>
+    </row>
+    <row r="29" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="39"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="155"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="114"/>
+      <c r="K29" s="60"/>
+      <c r="L29" s="137"/>
+      <c r="M29" s="101"/>
+      <c r="N29" s="60"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="94" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q29" s="64"/>
+      <c r="R29" s="64"/>
+      <c r="S29" s="90"/>
+      <c r="T29" s="39"/>
+      <c r="U29" s="98"/>
+      <c r="V29" s="146"/>
+      <c r="W29" s="111"/>
+      <c r="X29" s="147"/>
+      <c r="Y29" s="147"/>
+    </row>
+    <row r="30" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="39"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="155"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="135"/>
+      <c r="K30" s="77"/>
+      <c r="L30" s="163"/>
+      <c r="M30" s="135"/>
+      <c r="N30" s="77"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="93" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q30" s="81"/>
+      <c r="R30" s="81"/>
+      <c r="S30" s="97"/>
+      <c r="T30" s="39"/>
+      <c r="U30" s="99"/>
+      <c r="V30" s="146"/>
+      <c r="W30" s="147"/>
+      <c r="X30" s="147"/>
+      <c r="Y30" s="147"/>
+    </row>
+    <row r="31" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="39"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="155"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="39"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="94" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q31" s="64"/>
+      <c r="R31" s="64"/>
+      <c r="S31" s="90"/>
+      <c r="T31" s="39"/>
+      <c r="U31" s="98"/>
+      <c r="V31" s="146"/>
+      <c r="W31" s="147"/>
+      <c r="X31" s="147"/>
+      <c r="Y31" s="147"/>
+    </row>
+    <row r="32" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="39"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="155"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="39"/>
+      <c r="O32" s="39"/>
+      <c r="P32" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q32" s="81"/>
+      <c r="R32" s="81"/>
+      <c r="S32" s="97"/>
+      <c r="T32" s="39"/>
+      <c r="U32" s="99"/>
+      <c r="V32" s="146"/>
+      <c r="W32" s="147"/>
+      <c r="X32" s="147"/>
+      <c r="Y32" s="147"/>
+    </row>
+    <row r="33" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="39"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="155"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="61"/>
+      <c r="M33" s="16"/>
+      <c r="N33" s="61"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="94" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q33" s="64"/>
+      <c r="R33" s="64"/>
+      <c r="S33" s="90"/>
+      <c r="T33" s="39" t="s">
+        <v>256</v>
+      </c>
+      <c r="U33" s="128"/>
+      <c r="V33" s="39"/>
+      <c r="W33" s="147"/>
+      <c r="X33" s="111"/>
+    </row>
+    <row r="34" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="39"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="155"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="39"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="61"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="125" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q34" s="126">
+        <f>SUM(Q22:Q33)</f>
+        <v>6.3118055555555559</v>
+      </c>
+      <c r="R34" s="126">
+        <f>SUM(R22:R33)</f>
+        <v>0.36458333333333337</v>
+      </c>
+      <c r="S34" s="127">
+        <f>SUM(S22:S33)</f>
+        <v>6.6763888888888889</v>
+      </c>
+      <c r="T34" s="39"/>
+      <c r="U34" s="39"/>
+      <c r="V34" s="39"/>
+      <c r="W34" s="111"/>
+    </row>
+    <row r="35" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="39"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="155"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="39"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="39"/>
+      <c r="Q35" s="39"/>
+      <c r="R35" s="39"/>
+      <c r="S35" s="39"/>
+      <c r="T35" s="16"/>
+      <c r="U35" s="109"/>
+      <c r="V35" s="39"/>
+      <c r="W35" s="111"/>
+    </row>
+    <row r="36" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="39"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="155"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="39"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="172"/>
+      <c r="Q36" s="172"/>
+      <c r="R36" s="172"/>
+      <c r="S36" s="111"/>
+      <c r="T36" s="16"/>
+      <c r="U36" s="16"/>
+      <c r="V36" s="39"/>
+      <c r="W36" s="111"/>
+    </row>
+    <row r="37" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="39"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="155"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="39"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="175"/>
+      <c r="Q37" s="172"/>
+      <c r="R37" s="172"/>
+      <c r="S37" s="111"/>
+      <c r="T37" s="16"/>
+      <c r="U37" s="16"/>
+      <c r="V37" s="39"/>
+      <c r="W37" s="111"/>
+    </row>
+    <row r="38" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="39"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="155"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="61"/>
+      <c r="I38" s="39"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="172"/>
+      <c r="Q38" s="172"/>
+      <c r="R38" s="172"/>
+      <c r="S38" s="111"/>
+      <c r="T38" s="16"/>
+      <c r="U38" s="16"/>
+      <c r="V38" s="39"/>
+      <c r="W38" s="111"/>
+    </row>
+    <row r="39" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="39"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="155"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="39"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="172"/>
+      <c r="Q39" s="172"/>
+      <c r="R39" s="172"/>
+      <c r="S39" s="124"/>
+      <c r="T39" s="16"/>
+      <c r="U39" s="16"/>
+      <c r="V39" s="39"/>
+      <c r="W39" s="111"/>
+    </row>
+    <row r="40" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="39"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="155"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="39"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="172"/>
+      <c r="Q40" s="172"/>
+      <c r="R40" s="172"/>
+      <c r="S40" s="124"/>
+      <c r="T40" s="16"/>
+      <c r="U40" s="16"/>
+      <c r="V40" s="39"/>
+      <c r="W40" s="111"/>
+    </row>
+    <row r="41" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="39"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="155"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="61"/>
+      <c r="I41" s="39"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="172"/>
+      <c r="Q41" s="172"/>
+      <c r="R41" s="172"/>
+      <c r="S41" s="124"/>
+      <c r="T41" s="16"/>
+      <c r="U41" s="16"/>
+      <c r="V41" s="39"/>
+      <c r="W41" s="111"/>
+    </row>
+    <row r="42" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="39"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="155"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="61"/>
+      <c r="I42" s="39"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="39"/>
+      <c r="Q42" s="39"/>
+      <c r="R42" s="39"/>
+      <c r="S42" s="124"/>
+      <c r="T42" s="16"/>
+      <c r="U42" s="16"/>
+      <c r="V42" s="39"/>
+      <c r="W42" s="111"/>
+    </row>
+    <row r="43" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="39"/>
+      <c r="B43" s="39"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="108"/>
+      <c r="F43" s="39"/>
+      <c r="G43" s="39"/>
+      <c r="H43" s="62"/>
+      <c r="I43" s="39"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="39"/>
+      <c r="Q43" s="39"/>
+      <c r="R43" s="39"/>
+      <c r="S43" s="39"/>
+      <c r="T43" s="16"/>
+      <c r="U43" s="16"/>
+      <c r="V43" s="39"/>
+      <c r="W43" s="111"/>
+    </row>
+    <row r="44" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="39"/>
+      <c r="B44" s="39"/>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="108"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="39"/>
+      <c r="H44" s="62"/>
+      <c r="I44" s="39"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="16"/>
+      <c r="Q44" s="16"/>
+      <c r="R44" s="16"/>
+      <c r="S44" s="16"/>
+      <c r="T44" s="16"/>
+      <c r="U44" s="16"/>
+      <c r="V44" s="39"/>
+      <c r="W44" s="111"/>
+    </row>
+    <row r="45" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="39"/>
+      <c r="B45" s="39"/>
+      <c r="C45" s="39"/>
+      <c r="D45" s="39"/>
+      <c r="E45" s="108"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="39"/>
+      <c r="H45" s="62"/>
+      <c r="I45" s="39"/>
+      <c r="O45" s="39"/>
+      <c r="P45" s="16"/>
+      <c r="Q45" s="16"/>
+      <c r="R45" s="16"/>
+      <c r="S45" s="16"/>
+      <c r="T45" s="16"/>
+      <c r="U45" s="16"/>
+      <c r="V45" s="39"/>
+      <c r="W45" s="111"/>
+    </row>
+    <row r="46" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="39"/>
+      <c r="B46" s="39"/>
+      <c r="C46" s="39"/>
+      <c r="D46" s="39"/>
+      <c r="E46" s="108"/>
+      <c r="F46" s="39"/>
+      <c r="G46" s="39"/>
+      <c r="H46" s="62"/>
+      <c r="I46" s="39"/>
+      <c r="O46" s="39"/>
+      <c r="P46" s="109"/>
+      <c r="Q46" s="16"/>
+      <c r="R46" s="16"/>
+      <c r="S46" s="16"/>
+      <c r="T46" s="16"/>
+      <c r="U46" s="16"/>
+      <c r="V46" s="39"/>
+      <c r="W46" s="111"/>
+    </row>
+    <row r="47" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="39"/>
+      <c r="B47" s="39"/>
+      <c r="C47" s="39"/>
+      <c r="D47" s="39"/>
+      <c r="E47" s="108"/>
+      <c r="F47" s="39"/>
+      <c r="G47" s="39"/>
+      <c r="H47" s="62"/>
+      <c r="I47" s="39"/>
+      <c r="J47" s="16"/>
+      <c r="K47" s="111"/>
+      <c r="L47" s="111"/>
+      <c r="M47" s="111"/>
+      <c r="N47" s="111"/>
+      <c r="O47" s="39"/>
+      <c r="P47" s="16"/>
+      <c r="Q47" s="16"/>
+      <c r="R47" s="16"/>
+      <c r="S47" s="16"/>
+      <c r="T47" s="16"/>
+      <c r="U47" s="16"/>
+      <c r="V47" s="39"/>
+      <c r="W47" s="111"/>
+    </row>
+    <row r="48" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="39"/>
+      <c r="B48" s="39"/>
+      <c r="C48" s="39"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="108"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="39"/>
+      <c r="H48" s="62"/>
+      <c r="I48" s="39"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="111"/>
+      <c r="L48" s="111"/>
+      <c r="M48" s="111"/>
+      <c r="N48" s="111"/>
+      <c r="O48" s="39"/>
+      <c r="P48" s="16"/>
+      <c r="Q48" s="16"/>
+      <c r="R48" s="16"/>
+      <c r="S48" s="16"/>
+      <c r="T48" s="16"/>
+      <c r="U48" s="16"/>
+      <c r="V48" s="39"/>
+      <c r="W48" s="111"/>
+    </row>
+    <row r="49" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="39"/>
+      <c r="B49" s="39"/>
+      <c r="C49" s="39"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="108"/>
+      <c r="F49" s="39"/>
+      <c r="G49" s="39"/>
+      <c r="H49" s="62"/>
+      <c r="I49" s="39"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="111"/>
+      <c r="L49" s="111"/>
+      <c r="M49" s="111"/>
+      <c r="N49" s="111"/>
+      <c r="O49" s="39"/>
+      <c r="P49" s="16"/>
+      <c r="Q49" s="16"/>
+      <c r="R49" s="16"/>
+      <c r="S49" s="16"/>
+      <c r="T49" s="16"/>
+      <c r="U49" s="16"/>
+      <c r="V49" s="39"/>
+      <c r="W49" s="111"/>
+    </row>
+    <row r="50" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="39"/>
+      <c r="B50" s="39"/>
+      <c r="C50" s="39"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="108"/>
+      <c r="F50" s="39"/>
+      <c r="G50" s="39"/>
+      <c r="H50" s="39"/>
+      <c r="I50" s="39"/>
+      <c r="J50" s="16"/>
+      <c r="K50" s="111"/>
+      <c r="L50" s="111"/>
+      <c r="M50" s="111"/>
+      <c r="N50" s="111"/>
+      <c r="O50" s="39"/>
+      <c r="P50" s="39"/>
+      <c r="Q50" s="39"/>
+      <c r="R50" s="39"/>
+      <c r="S50" s="39"/>
+      <c r="T50" s="39"/>
+      <c r="U50" s="39"/>
+      <c r="V50" s="39"/>
+      <c r="W50" s="111"/>
+    </row>
+    <row r="51" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="39"/>
+      <c r="B51" s="39"/>
+      <c r="C51" s="39"/>
+      <c r="D51" s="39"/>
+      <c r="E51" s="108"/>
+      <c r="F51" s="39"/>
+      <c r="G51" s="39"/>
+      <c r="H51" s="39"/>
+      <c r="I51" s="39"/>
+      <c r="J51" s="16"/>
+      <c r="K51" s="111"/>
+      <c r="L51" s="111"/>
+      <c r="M51" s="111"/>
+      <c r="N51" s="111"/>
+      <c r="O51" s="39"/>
+      <c r="P51" s="39"/>
+      <c r="Q51" s="39"/>
+      <c r="R51" s="39"/>
+      <c r="S51" s="39"/>
+      <c r="T51" s="39"/>
+      <c r="U51" s="39"/>
+      <c r="V51" s="39"/>
+      <c r="W51" s="111"/>
+    </row>
+    <row r="52" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="39"/>
+      <c r="B52" s="39"/>
+      <c r="C52" s="39"/>
+      <c r="D52" s="39"/>
+      <c r="E52" s="108"/>
+      <c r="F52" s="39"/>
+      <c r="G52" s="39"/>
+      <c r="H52" s="39"/>
+      <c r="I52" s="39"/>
+      <c r="J52" s="16"/>
+      <c r="K52" s="111"/>
+      <c r="L52" s="111"/>
+      <c r="M52" s="111"/>
+      <c r="N52" s="111"/>
+      <c r="O52" s="39"/>
+      <c r="P52" s="39"/>
+      <c r="Q52" s="39"/>
+      <c r="R52" s="39"/>
+      <c r="S52" s="39"/>
+      <c r="T52" s="39"/>
+      <c r="U52" s="39"/>
+      <c r="V52" s="39"/>
+      <c r="W52" s="111"/>
+    </row>
+    <row r="53" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="39"/>
+      <c r="B53" s="39"/>
+      <c r="C53" s="39"/>
+      <c r="D53" s="39"/>
+      <c r="E53" s="108"/>
+      <c r="F53" s="39"/>
+      <c r="G53" s="39"/>
+      <c r="H53" s="39"/>
+      <c r="I53" s="39"/>
+      <c r="J53" s="16"/>
+      <c r="K53" s="111"/>
+      <c r="L53" s="111"/>
+      <c r="M53" s="111"/>
+      <c r="N53" s="111"/>
+      <c r="O53" s="39"/>
+      <c r="P53" s="39"/>
+      <c r="Q53" s="39"/>
+      <c r="R53" s="39"/>
+      <c r="S53" s="39"/>
+      <c r="T53" s="39"/>
+      <c r="U53" s="39"/>
+      <c r="V53" s="39"/>
+      <c r="W53" s="111"/>
+    </row>
+    <row r="54" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="39"/>
+      <c r="B54" s="39"/>
+      <c r="C54" s="39"/>
+      <c r="D54" s="39"/>
+      <c r="E54" s="108"/>
+      <c r="F54" s="39"/>
+      <c r="G54" s="39"/>
+      <c r="H54" s="39"/>
+      <c r="I54" s="39"/>
+      <c r="J54" s="16"/>
+      <c r="K54" s="111"/>
+      <c r="L54" s="111"/>
+      <c r="M54" s="111"/>
+      <c r="N54" s="111"/>
+      <c r="O54" s="39"/>
+      <c r="P54" s="39"/>
+      <c r="Q54" s="39"/>
+      <c r="R54" s="39"/>
+      <c r="S54" s="39"/>
+      <c r="T54" s="39"/>
+      <c r="U54" s="39"/>
+      <c r="V54" s="39"/>
+      <c r="W54" s="111"/>
+    </row>
+    <row r="55" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="39"/>
+      <c r="B55" s="39"/>
+      <c r="C55" s="39"/>
+      <c r="D55" s="39"/>
+      <c r="E55" s="108"/>
+      <c r="F55" s="39"/>
+      <c r="G55" s="39"/>
+      <c r="H55" s="39"/>
+      <c r="I55" s="39"/>
+      <c r="J55" s="16"/>
+      <c r="K55" s="111"/>
+      <c r="L55" s="111"/>
+      <c r="M55" s="111"/>
+      <c r="N55" s="111"/>
+      <c r="O55" s="39"/>
+      <c r="P55" s="39"/>
+      <c r="Q55" s="39"/>
+      <c r="R55" s="39"/>
+      <c r="S55" s="39"/>
+      <c r="T55" s="39"/>
+      <c r="U55" s="39"/>
+      <c r="V55" s="39"/>
+      <c r="W55" s="111"/>
+    </row>
+    <row r="56" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="39"/>
+      <c r="B56" s="39"/>
+      <c r="C56" s="39"/>
+      <c r="D56" s="39"/>
+      <c r="E56" s="108"/>
+      <c r="F56" s="39"/>
+      <c r="G56" s="39"/>
+      <c r="H56" s="39"/>
+      <c r="I56" s="39"/>
+      <c r="J56" s="16"/>
+      <c r="K56" s="111"/>
+      <c r="L56" s="111"/>
+      <c r="M56" s="111"/>
+      <c r="N56" s="111"/>
+      <c r="O56" s="39"/>
+      <c r="P56" s="39"/>
+      <c r="Q56" s="39"/>
+      <c r="R56" s="39"/>
+      <c r="S56" s="39"/>
+      <c r="T56" s="39"/>
+      <c r="U56" s="39"/>
+      <c r="V56" s="39"/>
+      <c r="W56" s="111"/>
+    </row>
+    <row r="57" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="39"/>
+      <c r="B57" s="39"/>
+      <c r="C57" s="39"/>
+      <c r="D57" s="39"/>
+      <c r="E57" s="108"/>
+      <c r="F57" s="39"/>
+      <c r="G57" s="39"/>
+      <c r="H57" s="39"/>
+      <c r="I57" s="39"/>
+      <c r="J57" s="16"/>
+      <c r="K57" s="111"/>
+      <c r="L57" s="111"/>
+      <c r="M57" s="111"/>
+      <c r="N57" s="111"/>
+      <c r="O57" s="39"/>
+      <c r="P57" s="39"/>
+      <c r="Q57" s="39"/>
+      <c r="R57" s="39"/>
+      <c r="S57" s="39"/>
+      <c r="T57" s="39"/>
+      <c r="U57" s="39"/>
+      <c r="V57" s="39"/>
+      <c r="W57" s="111"/>
+    </row>
+    <row r="58" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="39"/>
+      <c r="B58" s="39"/>
+      <c r="C58" s="39"/>
+      <c r="D58" s="39"/>
+      <c r="E58" s="108"/>
+      <c r="F58" s="39"/>
+      <c r="G58" s="39"/>
+      <c r="H58" s="39"/>
+      <c r="I58" s="39"/>
+      <c r="J58" s="16"/>
+      <c r="K58" s="111"/>
+      <c r="L58" s="111"/>
+      <c r="M58" s="111"/>
+      <c r="N58" s="111"/>
+      <c r="O58" s="39"/>
+      <c r="P58" s="39"/>
+      <c r="Q58" s="39"/>
+      <c r="R58" s="39"/>
+      <c r="S58" s="39"/>
+      <c r="T58" s="39"/>
+      <c r="U58" s="39"/>
+      <c r="V58" s="39"/>
+      <c r="W58" s="111"/>
+    </row>
+    <row r="59" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="39"/>
+      <c r="B59" s="39"/>
+      <c r="C59" s="39"/>
+      <c r="D59" s="39"/>
+      <c r="E59" s="108"/>
+      <c r="F59" s="39"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="39"/>
+      <c r="I59" s="39"/>
+      <c r="J59" s="16"/>
+      <c r="K59" s="111"/>
+      <c r="L59" s="111"/>
+      <c r="M59" s="111"/>
+      <c r="N59" s="111"/>
+      <c r="O59" s="39"/>
+      <c r="P59" s="39"/>
+      <c r="Q59" s="39"/>
+      <c r="R59" s="39"/>
+      <c r="S59" s="39"/>
+      <c r="T59" s="39"/>
+      <c r="U59" s="39"/>
+      <c r="V59" s="39"/>
+      <c r="W59" s="111"/>
+    </row>
+    <row r="60" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="39"/>
+      <c r="B60" s="39"/>
+      <c r="C60" s="39"/>
+      <c r="D60" s="39"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="39"/>
+      <c r="G60" s="39"/>
+      <c r="H60" s="39"/>
+      <c r="I60" s="39"/>
+      <c r="J60" s="16"/>
+      <c r="K60" s="111"/>
+      <c r="L60" s="111"/>
+      <c r="M60" s="111"/>
+      <c r="N60" s="111"/>
+      <c r="O60" s="39"/>
+      <c r="P60" s="39"/>
+      <c r="Q60" s="39"/>
+      <c r="R60" s="39"/>
+      <c r="S60" s="39"/>
+      <c r="T60" s="39"/>
+      <c r="U60" s="39"/>
+      <c r="V60" s="39"/>
+      <c r="W60" s="111"/>
+    </row>
+    <row r="61" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="39"/>
+      <c r="B61" s="39"/>
+      <c r="C61" s="39"/>
+      <c r="D61" s="39"/>
+      <c r="E61" s="108"/>
+      <c r="F61" s="39"/>
+      <c r="G61" s="39"/>
+      <c r="H61" s="39"/>
+      <c r="I61" s="39"/>
+      <c r="J61" s="16"/>
+      <c r="K61" s="111"/>
+      <c r="L61" s="111"/>
+      <c r="M61" s="111"/>
+      <c r="N61" s="111"/>
+      <c r="O61" s="39"/>
+      <c r="P61" s="39"/>
+      <c r="Q61" s="39"/>
+      <c r="R61" s="39"/>
+      <c r="S61" s="39"/>
+      <c r="T61" s="39"/>
+      <c r="U61" s="39"/>
+      <c r="V61" s="39"/>
+      <c r="W61" s="111"/>
+    </row>
+    <row r="62" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="39"/>
+      <c r="B62" s="39"/>
+      <c r="C62" s="39"/>
+      <c r="D62" s="39"/>
+      <c r="E62" s="108"/>
+      <c r="F62" s="39"/>
+      <c r="G62" s="39"/>
+      <c r="H62" s="39"/>
+      <c r="I62" s="39"/>
+      <c r="J62" s="16"/>
+      <c r="K62" s="111"/>
+      <c r="L62" s="111"/>
+      <c r="M62" s="111"/>
+      <c r="N62" s="111"/>
+      <c r="O62" s="39"/>
+      <c r="P62" s="39"/>
+      <c r="Q62" s="39"/>
+      <c r="R62" s="39"/>
+      <c r="S62" s="39"/>
+      <c r="T62" s="39"/>
+      <c r="U62" s="39"/>
+      <c r="V62" s="39"/>
+      <c r="W62" s="111"/>
+    </row>
+    <row r="63" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="39"/>
+      <c r="B63" s="39"/>
+      <c r="C63" s="39"/>
+      <c r="D63" s="39"/>
+      <c r="E63" s="108"/>
+      <c r="F63" s="39"/>
+      <c r="G63" s="39"/>
+      <c r="H63" s="39"/>
+      <c r="I63" s="39"/>
+      <c r="J63" s="16"/>
+      <c r="K63" s="111"/>
+      <c r="L63" s="111"/>
+      <c r="M63" s="111"/>
+      <c r="N63" s="111"/>
+      <c r="O63" s="39"/>
+      <c r="P63" s="39"/>
+      <c r="Q63" s="39"/>
+      <c r="R63" s="39"/>
+      <c r="S63" s="39"/>
+      <c r="T63" s="39"/>
+      <c r="U63" s="39"/>
+      <c r="V63" s="39"/>
+      <c r="W63" s="111"/>
+    </row>
+    <row r="64" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="39"/>
+      <c r="B64" s="39"/>
+      <c r="C64" s="39"/>
+      <c r="D64" s="39"/>
+      <c r="E64" s="108"/>
+      <c r="F64" s="39"/>
+      <c r="G64" s="39"/>
+      <c r="H64" s="39"/>
+      <c r="I64" s="39"/>
+      <c r="J64" s="16"/>
+      <c r="K64" s="111"/>
+      <c r="L64" s="111"/>
+      <c r="M64" s="111"/>
+      <c r="N64" s="111"/>
+      <c r="O64" s="39"/>
+      <c r="P64" s="39"/>
+      <c r="Q64" s="39"/>
+      <c r="R64" s="39"/>
+      <c r="S64" s="39"/>
+      <c r="T64" s="39"/>
+      <c r="U64" s="39"/>
+      <c r="V64" s="39"/>
+      <c r="W64" s="111"/>
+    </row>
+    <row r="65" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="39"/>
+      <c r="B65" s="39"/>
+      <c r="C65" s="39"/>
+      <c r="D65" s="39"/>
+      <c r="E65" s="108"/>
+      <c r="F65" s="39"/>
+      <c r="G65" s="39"/>
+      <c r="H65" s="39"/>
+      <c r="I65" s="39"/>
+      <c r="J65" s="16"/>
+      <c r="K65" s="111"/>
+      <c r="L65" s="111"/>
+      <c r="M65" s="111"/>
+      <c r="N65" s="111"/>
+      <c r="O65" s="39"/>
+      <c r="P65" s="39"/>
+      <c r="Q65" s="39"/>
+      <c r="R65" s="39"/>
+      <c r="S65" s="39"/>
+      <c r="T65" s="39"/>
+      <c r="U65" s="39"/>
+      <c r="V65" s="39"/>
+      <c r="W65" s="111"/>
+    </row>
+    <row r="66" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="39"/>
+      <c r="B66" s="39"/>
+      <c r="C66" s="39"/>
+      <c r="D66" s="39"/>
+      <c r="E66" s="108"/>
+      <c r="F66" s="39"/>
+      <c r="G66" s="39"/>
+      <c r="H66" s="39"/>
+      <c r="I66" s="39"/>
+      <c r="J66" s="16"/>
+      <c r="K66" s="111"/>
+      <c r="L66" s="111"/>
+      <c r="M66" s="111"/>
+      <c r="N66" s="111"/>
+      <c r="O66" s="39"/>
+      <c r="P66" s="39"/>
+      <c r="Q66" s="39"/>
+      <c r="R66" s="39"/>
+      <c r="S66" s="39"/>
+      <c r="T66" s="39"/>
+      <c r="U66" s="39"/>
+      <c r="V66" s="39"/>
+      <c r="W66" s="111"/>
+    </row>
+    <row r="67" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="39"/>
+      <c r="B67" s="39"/>
+      <c r="C67" s="39"/>
+      <c r="D67" s="39"/>
+      <c r="E67" s="108"/>
+      <c r="F67" s="39"/>
+      <c r="G67" s="39"/>
+      <c r="H67" s="39"/>
+      <c r="I67" s="39"/>
+      <c r="J67" s="16"/>
+      <c r="K67" s="111"/>
+      <c r="L67" s="111"/>
+      <c r="M67" s="111"/>
+      <c r="N67" s="111"/>
+      <c r="O67" s="39"/>
+      <c r="P67" s="39"/>
+      <c r="Q67" s="39"/>
+      <c r="R67" s="39"/>
+      <c r="S67" s="39"/>
+      <c r="T67" s="39"/>
+      <c r="U67" s="39"/>
+      <c r="V67" s="39"/>
+      <c r="W67" s="111"/>
+    </row>
+    <row r="68" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="39"/>
+      <c r="B68" s="39"/>
+      <c r="C68" s="39"/>
+      <c r="D68" s="39"/>
+      <c r="E68" s="108"/>
+      <c r="F68" s="39"/>
+      <c r="G68" s="39"/>
+      <c r="H68" s="39"/>
+      <c r="I68" s="39"/>
+      <c r="J68" s="16"/>
+      <c r="K68" s="111"/>
+      <c r="L68" s="111"/>
+      <c r="M68" s="111"/>
+      <c r="N68" s="111"/>
+      <c r="O68" s="39"/>
+      <c r="P68" s="39"/>
+      <c r="Q68" s="39"/>
+      <c r="R68" s="39"/>
+      <c r="S68" s="39"/>
+      <c r="T68" s="39"/>
+      <c r="U68" s="39"/>
+      <c r="V68" s="39"/>
+      <c r="W68" s="111"/>
+    </row>
+    <row r="69" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="39"/>
+      <c r="B69" s="39"/>
+      <c r="C69" s="39"/>
+      <c r="D69" s="39"/>
+      <c r="E69" s="108"/>
+      <c r="F69" s="39"/>
+      <c r="G69" s="39"/>
+      <c r="H69" s="39"/>
+      <c r="I69" s="39"/>
+      <c r="J69" s="16"/>
+      <c r="K69" s="16"/>
+      <c r="L69" s="16"/>
+      <c r="M69" s="16"/>
+      <c r="N69" s="16"/>
+      <c r="O69" s="39"/>
+      <c r="P69" s="39"/>
+      <c r="Q69" s="39"/>
+      <c r="R69" s="39"/>
+      <c r="S69" s="39"/>
+      <c r="T69" s="39"/>
+      <c r="U69" s="39"/>
+      <c r="V69" s="39"/>
+      <c r="W69" s="111"/>
+    </row>
+    <row r="70" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="39"/>
+      <c r="B70" s="39"/>
+      <c r="C70" s="39"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="108"/>
+      <c r="F70" s="39"/>
+      <c r="G70" s="39"/>
+      <c r="H70" s="39"/>
+      <c r="I70" s="39"/>
+      <c r="J70" s="16"/>
+      <c r="K70" s="16"/>
+      <c r="L70" s="16"/>
+      <c r="M70" s="16"/>
+      <c r="N70" s="16"/>
+      <c r="O70" s="39"/>
+      <c r="P70" s="39"/>
+      <c r="Q70" s="39"/>
+      <c r="R70" s="39"/>
+      <c r="S70" s="39"/>
+      <c r="T70" s="39"/>
+      <c r="U70" s="39"/>
+      <c r="V70" s="39"/>
+      <c r="W70" s="111"/>
+    </row>
+    <row r="71" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="39"/>
+      <c r="B71" s="39"/>
+      <c r="C71" s="39"/>
+      <c r="D71" s="39"/>
+      <c r="E71" s="108"/>
+      <c r="F71" s="39"/>
+      <c r="G71" s="39"/>
+      <c r="H71" s="39"/>
+      <c r="I71" s="39"/>
+      <c r="J71" s="16"/>
+      <c r="K71" s="16"/>
+      <c r="L71" s="16"/>
+      <c r="M71" s="16"/>
+      <c r="N71" s="16"/>
+      <c r="O71" s="39"/>
+      <c r="P71" s="39"/>
+      <c r="Q71" s="39"/>
+      <c r="R71" s="39"/>
+      <c r="S71" s="39"/>
+      <c r="T71" s="39"/>
+      <c r="U71" s="39"/>
+      <c r="V71" s="39"/>
+      <c r="W71" s="111"/>
+    </row>
+    <row r="72" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="39"/>
+      <c r="B72" s="39"/>
+      <c r="C72" s="39"/>
+      <c r="D72" s="39"/>
+      <c r="E72" s="108"/>
+      <c r="F72" s="39"/>
+      <c r="G72" s="39"/>
+      <c r="H72" s="39"/>
+      <c r="I72" s="39"/>
+      <c r="J72" s="16"/>
+      <c r="K72" s="16"/>
+      <c r="L72" s="16"/>
+      <c r="M72" s="16"/>
+      <c r="N72" s="16"/>
+      <c r="O72" s="39"/>
+      <c r="P72" s="39"/>
+      <c r="Q72" s="39"/>
+      <c r="R72" s="39"/>
+      <c r="S72" s="39"/>
+      <c r="T72" s="39"/>
+      <c r="U72" s="39"/>
+      <c r="V72" s="39"/>
+      <c r="W72" s="111"/>
+    </row>
+    <row r="73" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="39"/>
+      <c r="B73" s="39"/>
+      <c r="C73" s="39"/>
+      <c r="D73" s="39"/>
+      <c r="E73" s="108"/>
+      <c r="F73" s="39"/>
+      <c r="G73" s="39"/>
+      <c r="H73" s="39"/>
+      <c r="I73" s="39"/>
+      <c r="J73" s="16"/>
+      <c r="K73" s="16"/>
+      <c r="L73" s="16"/>
+      <c r="M73" s="16"/>
+      <c r="N73" s="16"/>
+      <c r="O73" s="39"/>
+      <c r="P73" s="39"/>
+      <c r="Q73" s="39"/>
+      <c r="R73" s="39"/>
+      <c r="S73" s="39"/>
+      <c r="T73" s="39"/>
+      <c r="U73" s="39"/>
+      <c r="V73" s="39"/>
+      <c r="W73" s="111"/>
+    </row>
+    <row r="74" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="39"/>
+      <c r="B74" s="39"/>
+      <c r="C74" s="39"/>
+      <c r="D74" s="39"/>
+      <c r="E74" s="108"/>
+      <c r="F74" s="39"/>
+      <c r="G74" s="39"/>
+      <c r="H74" s="39"/>
+      <c r="I74" s="39"/>
+      <c r="J74" s="16"/>
+      <c r="K74" s="16"/>
+      <c r="L74" s="16"/>
+      <c r="M74" s="16"/>
+      <c r="N74" s="16"/>
+      <c r="O74" s="39"/>
+      <c r="P74" s="39"/>
+      <c r="Q74" s="39"/>
+      <c r="R74" s="39"/>
+      <c r="S74" s="39"/>
+      <c r="T74" s="39"/>
+      <c r="U74" s="39"/>
+      <c r="V74" s="39"/>
+      <c r="W74" s="111"/>
+    </row>
+    <row r="75" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="39"/>
+      <c r="B75" s="39"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="39"/>
+      <c r="E75" s="108"/>
+      <c r="F75" s="39"/>
+      <c r="G75" s="39"/>
+      <c r="H75" s="39"/>
+      <c r="I75" s="39"/>
+      <c r="J75" s="16"/>
+      <c r="K75" s="16"/>
+      <c r="L75" s="16"/>
+      <c r="M75" s="16"/>
+      <c r="N75" s="16"/>
+      <c r="O75" s="39"/>
+      <c r="P75" s="39"/>
+      <c r="Q75" s="39"/>
+      <c r="R75" s="39"/>
+      <c r="S75" s="39"/>
+      <c r="T75" s="39"/>
+      <c r="U75" s="39"/>
+      <c r="V75" s="39"/>
+      <c r="W75" s="111"/>
+    </row>
+    <row r="76" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="39"/>
+      <c r="B76" s="39"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="108"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="39"/>
+      <c r="I76" s="39"/>
+      <c r="J76" s="16"/>
+      <c r="K76" s="16"/>
+      <c r="L76" s="16"/>
+      <c r="M76" s="16"/>
+      <c r="N76" s="16"/>
+      <c r="O76" s="39"/>
+      <c r="P76" s="39"/>
+      <c r="Q76" s="39"/>
+      <c r="R76" s="39"/>
+      <c r="S76" s="39"/>
+      <c r="T76" s="39"/>
+      <c r="U76" s="39"/>
+      <c r="V76" s="39"/>
+      <c r="W76" s="111"/>
+    </row>
+    <row r="77" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="39"/>
+      <c r="B77" s="39"/>
+      <c r="C77" s="39"/>
+      <c r="D77" s="39"/>
+      <c r="E77" s="108"/>
+      <c r="F77" s="39"/>
+      <c r="G77" s="39"/>
+      <c r="H77" s="39"/>
+      <c r="I77" s="39"/>
+      <c r="J77" s="16"/>
+      <c r="K77" s="16"/>
+      <c r="L77" s="16"/>
+      <c r="M77" s="16"/>
+      <c r="N77" s="16"/>
+      <c r="O77" s="39"/>
+      <c r="P77" s="39"/>
+      <c r="Q77" s="39"/>
+      <c r="R77" s="39"/>
+      <c r="S77" s="39"/>
+      <c r="T77" s="39"/>
+      <c r="U77" s="39"/>
+      <c r="V77" s="39"/>
+      <c r="W77" s="111"/>
+    </row>
+    <row r="78" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="39"/>
+      <c r="B78" s="39"/>
+      <c r="C78" s="39"/>
+      <c r="D78" s="39"/>
+      <c r="E78" s="108"/>
+      <c r="F78" s="39"/>
+      <c r="G78" s="39"/>
+      <c r="H78" s="39"/>
+      <c r="I78" s="39"/>
+      <c r="J78" s="16"/>
+      <c r="K78" s="16"/>
+      <c r="L78" s="16"/>
+      <c r="M78" s="16"/>
+      <c r="N78" s="16"/>
+      <c r="O78" s="39"/>
+      <c r="P78" s="39"/>
+      <c r="Q78" s="39"/>
+      <c r="R78" s="39"/>
+      <c r="S78" s="39"/>
+      <c r="T78" s="39"/>
+      <c r="U78" s="39"/>
+      <c r="V78" s="39"/>
+      <c r="W78" s="111"/>
+    </row>
+    <row r="79" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="39"/>
+      <c r="B79" s="39"/>
+      <c r="C79" s="39"/>
+      <c r="D79" s="39"/>
+      <c r="E79" s="108"/>
+      <c r="F79" s="39"/>
+      <c r="G79" s="39"/>
+      <c r="H79" s="39"/>
+      <c r="I79" s="39"/>
+      <c r="J79" s="16"/>
+      <c r="K79" s="16"/>
+      <c r="L79" s="16"/>
+      <c r="M79" s="16"/>
+      <c r="N79" s="16"/>
+      <c r="O79" s="39"/>
+      <c r="P79" s="39"/>
+      <c r="Q79" s="39"/>
+      <c r="R79" s="39"/>
+      <c r="S79" s="39"/>
+      <c r="T79" s="39"/>
+      <c r="U79" s="39"/>
+      <c r="V79" s="39"/>
+      <c r="W79" s="111"/>
+    </row>
+    <row r="80" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="39"/>
+      <c r="B80" s="39"/>
+      <c r="C80" s="39"/>
+      <c r="D80" s="39"/>
+      <c r="E80" s="108"/>
+      <c r="F80" s="39"/>
+      <c r="G80" s="39"/>
+      <c r="H80" s="39"/>
+      <c r="I80" s="39"/>
+      <c r="J80" s="16"/>
+      <c r="K80" s="16"/>
+      <c r="L80" s="16"/>
+      <c r="M80" s="16"/>
+      <c r="N80" s="16"/>
+      <c r="O80" s="39"/>
+      <c r="P80" s="39"/>
+      <c r="Q80" s="39"/>
+      <c r="R80" s="39"/>
+      <c r="S80" s="39"/>
+      <c r="T80" s="39"/>
+      <c r="U80" s="39"/>
+      <c r="V80" s="39"/>
+      <c r="W80" s="111"/>
+    </row>
+    <row r="81" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="39"/>
+      <c r="B81" s="39"/>
+      <c r="C81" s="39"/>
+      <c r="D81" s="39"/>
+      <c r="E81" s="108"/>
+      <c r="F81" s="39"/>
+      <c r="G81" s="39"/>
+      <c r="H81" s="39"/>
+      <c r="I81" s="39"/>
+      <c r="J81" s="16"/>
+      <c r="K81" s="16"/>
+      <c r="L81" s="16"/>
+      <c r="M81" s="16"/>
+      <c r="N81" s="16"/>
+      <c r="O81" s="39"/>
+      <c r="P81" s="39"/>
+      <c r="Q81" s="39"/>
+      <c r="R81" s="39"/>
+      <c r="S81" s="39"/>
+      <c r="T81" s="39"/>
+      <c r="U81" s="39"/>
+      <c r="V81" s="39"/>
+      <c r="W81" s="111"/>
+    </row>
+    <row r="82" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="39"/>
+      <c r="B82" s="39"/>
+      <c r="C82" s="39"/>
+      <c r="D82" s="39"/>
+      <c r="E82" s="108"/>
+      <c r="F82" s="39"/>
+      <c r="G82" s="39"/>
+      <c r="H82" s="39"/>
+      <c r="I82" s="39"/>
+      <c r="J82" s="16"/>
+      <c r="K82" s="16"/>
+      <c r="L82" s="16"/>
+      <c r="M82" s="16"/>
+      <c r="N82" s="16"/>
+      <c r="O82" s="39"/>
+      <c r="P82" s="39"/>
+      <c r="Q82" s="39"/>
+      <c r="R82" s="39"/>
+      <c r="S82" s="39"/>
+      <c r="T82" s="39"/>
+      <c r="U82" s="39"/>
+      <c r="V82" s="39"/>
+      <c r="W82" s="111"/>
+    </row>
+    <row r="83" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="39"/>
+      <c r="B83" s="39"/>
+      <c r="C83" s="39"/>
+      <c r="D83" s="39"/>
+      <c r="E83" s="108"/>
+      <c r="F83" s="39"/>
+      <c r="G83" s="39"/>
+      <c r="H83" s="39"/>
+      <c r="I83" s="39"/>
+      <c r="J83" s="16"/>
+      <c r="K83" s="16"/>
+      <c r="L83" s="16"/>
+      <c r="M83" s="16"/>
+      <c r="N83" s="16"/>
+      <c r="O83" s="39"/>
+      <c r="P83" s="39"/>
+      <c r="Q83" s="39"/>
+      <c r="R83" s="39"/>
+      <c r="S83" s="39"/>
+      <c r="T83" s="39"/>
+      <c r="U83" s="39"/>
+      <c r="V83" s="39"/>
+      <c r="W83" s="111"/>
+    </row>
+    <row r="84" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="39"/>
+      <c r="B84" s="39"/>
+      <c r="C84" s="39"/>
+      <c r="D84" s="39"/>
+      <c r="E84" s="108"/>
+      <c r="F84" s="39"/>
+      <c r="G84" s="39"/>
+      <c r="H84" s="39"/>
+      <c r="I84" s="39"/>
+      <c r="J84" s="16"/>
+      <c r="K84" s="16"/>
+      <c r="L84" s="16"/>
+      <c r="M84" s="16"/>
+      <c r="N84" s="16"/>
+      <c r="O84" s="39"/>
+      <c r="P84" s="39"/>
+      <c r="Q84" s="39"/>
+      <c r="R84" s="39"/>
+      <c r="S84" s="39"/>
+      <c r="T84" s="39"/>
+      <c r="U84" s="39"/>
+      <c r="V84" s="39"/>
+      <c r="W84" s="111"/>
+    </row>
+    <row r="85" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="39"/>
+      <c r="B85" s="39"/>
+      <c r="C85" s="39"/>
+      <c r="D85" s="39"/>
+      <c r="E85" s="108"/>
+      <c r="F85" s="39"/>
+      <c r="G85" s="39"/>
+      <c r="H85" s="39"/>
+      <c r="I85" s="39"/>
+      <c r="J85" s="16"/>
+      <c r="K85" s="16"/>
+      <c r="L85" s="16"/>
+      <c r="M85" s="16"/>
+      <c r="N85" s="16"/>
+      <c r="O85" s="39"/>
+      <c r="P85" s="39"/>
+      <c r="Q85" s="39"/>
+      <c r="R85" s="39"/>
+      <c r="S85" s="39"/>
+      <c r="T85" s="39"/>
+      <c r="U85" s="39"/>
+      <c r="V85" s="39"/>
+      <c r="W85" s="111"/>
+    </row>
+    <row r="86" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="39"/>
+      <c r="B86" s="39"/>
+      <c r="C86" s="39"/>
+      <c r="D86" s="39"/>
+      <c r="E86" s="108"/>
+      <c r="F86" s="39"/>
+      <c r="G86" s="39"/>
+      <c r="H86" s="39"/>
+      <c r="I86" s="39"/>
+      <c r="J86" s="16"/>
+      <c r="K86" s="16"/>
+      <c r="L86" s="16"/>
+      <c r="M86" s="16"/>
+      <c r="N86" s="16"/>
+      <c r="O86" s="39"/>
+      <c r="P86" s="39"/>
+      <c r="Q86" s="39"/>
+      <c r="R86" s="39"/>
+      <c r="S86" s="39"/>
+      <c r="T86" s="39"/>
+      <c r="U86" s="39"/>
+      <c r="V86" s="39"/>
+      <c r="W86" s="111"/>
+    </row>
+    <row r="87" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="39"/>
+      <c r="B87" s="39"/>
+      <c r="C87" s="39"/>
+      <c r="D87" s="39"/>
+      <c r="E87" s="108"/>
+      <c r="F87" s="39"/>
+      <c r="G87" s="39"/>
+      <c r="H87" s="39"/>
+      <c r="I87" s="39"/>
+      <c r="J87" s="16"/>
+      <c r="K87" s="16"/>
+      <c r="L87" s="16"/>
+      <c r="M87" s="16"/>
+      <c r="N87" s="16"/>
+      <c r="O87" s="39"/>
+      <c r="P87" s="39"/>
+      <c r="Q87" s="39"/>
+      <c r="R87" s="39"/>
+      <c r="S87" s="39"/>
+      <c r="T87" s="39"/>
+      <c r="U87" s="39"/>
+      <c r="V87" s="39"/>
+      <c r="W87" s="111"/>
+    </row>
+    <row r="88" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="39"/>
+      <c r="B88" s="39"/>
+      <c r="C88" s="39"/>
+      <c r="D88" s="39"/>
+      <c r="E88" s="108"/>
+      <c r="F88" s="39"/>
+      <c r="G88" s="39"/>
+      <c r="H88" s="39"/>
+      <c r="I88" s="39"/>
+      <c r="J88" s="16"/>
+      <c r="K88" s="16"/>
+      <c r="L88" s="16"/>
+      <c r="M88" s="16"/>
+      <c r="N88" s="16"/>
+      <c r="O88" s="39"/>
+      <c r="P88" s="39"/>
+      <c r="Q88" s="39"/>
+      <c r="R88" s="39"/>
+      <c r="S88" s="39"/>
+      <c r="T88" s="39"/>
+      <c r="U88" s="39"/>
+      <c r="V88" s="39"/>
+      <c r="W88" s="111"/>
+    </row>
+    <row r="89" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="39"/>
+      <c r="B89" s="39"/>
+      <c r="C89" s="39"/>
+      <c r="D89" s="39"/>
+      <c r="E89" s="108"/>
+      <c r="F89" s="39"/>
+      <c r="G89" s="39"/>
+      <c r="H89" s="39"/>
+      <c r="I89" s="39"/>
+      <c r="J89" s="16"/>
+      <c r="K89" s="16"/>
+      <c r="L89" s="16"/>
+      <c r="M89" s="16"/>
+      <c r="N89" s="16"/>
+      <c r="O89" s="39"/>
+      <c r="P89" s="39"/>
+      <c r="Q89" s="39"/>
+      <c r="R89" s="39"/>
+      <c r="S89" s="39"/>
+      <c r="T89" s="39"/>
+      <c r="U89" s="39"/>
+      <c r="V89" s="39"/>
+      <c r="W89" s="111"/>
+    </row>
+    <row r="90" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="39"/>
+      <c r="B90" s="39"/>
+      <c r="C90" s="39"/>
+      <c r="D90" s="39"/>
+      <c r="E90" s="108"/>
+      <c r="F90" s="39"/>
+      <c r="G90" s="39"/>
+      <c r="H90" s="39"/>
+      <c r="I90" s="39"/>
+      <c r="J90" s="16"/>
+      <c r="K90" s="16"/>
+      <c r="L90" s="16"/>
+      <c r="M90" s="16"/>
+      <c r="N90" s="16"/>
+      <c r="O90" s="39"/>
+      <c r="P90" s="39"/>
+      <c r="Q90" s="39"/>
+      <c r="R90" s="39"/>
+      <c r="S90" s="39"/>
+      <c r="T90" s="39"/>
+      <c r="U90" s="39"/>
+      <c r="V90" s="39"/>
+      <c r="W90" s="111"/>
+    </row>
+    <row r="91" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="39"/>
+      <c r="B91" s="39"/>
+      <c r="C91" s="39"/>
+      <c r="D91" s="39"/>
+      <c r="E91" s="108"/>
+      <c r="F91" s="39"/>
+      <c r="G91" s="39"/>
+      <c r="H91" s="39"/>
+      <c r="I91" s="39"/>
+      <c r="J91" s="16"/>
+      <c r="K91" s="16"/>
+      <c r="L91" s="16"/>
+      <c r="M91" s="16"/>
+      <c r="N91" s="16"/>
+      <c r="O91" s="39"/>
+      <c r="P91" s="39"/>
+      <c r="Q91" s="39"/>
+      <c r="R91" s="39"/>
+      <c r="S91" s="39"/>
+      <c r="T91" s="39"/>
+      <c r="U91" s="39"/>
+      <c r="V91" s="39"/>
+      <c r="W91" s="111"/>
+    </row>
+    <row r="92" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="39"/>
+      <c r="B92" s="39"/>
+      <c r="C92" s="39"/>
+      <c r="D92" s="39"/>
+      <c r="E92" s="108"/>
+      <c r="F92" s="39"/>
+      <c r="G92" s="39"/>
+      <c r="H92" s="39"/>
+      <c r="I92" s="39"/>
+      <c r="J92" s="16"/>
+      <c r="K92" s="16"/>
+      <c r="L92" s="16"/>
+      <c r="M92" s="16"/>
+      <c r="N92" s="16"/>
+      <c r="O92" s="39"/>
+      <c r="P92" s="39"/>
+      <c r="Q92" s="39"/>
+      <c r="R92" s="39"/>
+      <c r="S92" s="39"/>
+      <c r="T92" s="39"/>
+      <c r="U92" s="39"/>
+      <c r="V92" s="39"/>
+      <c r="W92" s="111"/>
+    </row>
+    <row r="93" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="39"/>
+      <c r="B93" s="39"/>
+      <c r="C93" s="39"/>
+      <c r="D93" s="39"/>
+      <c r="E93" s="108"/>
+      <c r="F93" s="39"/>
+      <c r="G93" s="39"/>
+      <c r="H93" s="39"/>
+      <c r="I93" s="39"/>
+      <c r="J93" s="16"/>
+      <c r="K93" s="16"/>
+      <c r="L93" s="16"/>
+      <c r="M93" s="16"/>
+      <c r="N93" s="16"/>
+      <c r="O93" s="39"/>
+      <c r="P93" s="39"/>
+      <c r="Q93" s="39"/>
+      <c r="R93" s="39"/>
+      <c r="S93" s="39"/>
+      <c r="T93" s="39"/>
+      <c r="U93" s="39"/>
+      <c r="V93" s="39"/>
+      <c r="W93" s="111"/>
+    </row>
+    <row r="94" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="39"/>
+      <c r="B94" s="39"/>
+      <c r="C94" s="39"/>
+      <c r="D94" s="39"/>
+      <c r="E94" s="108"/>
+      <c r="F94" s="39"/>
+      <c r="G94" s="39"/>
+      <c r="H94" s="39"/>
+      <c r="I94" s="39"/>
+      <c r="J94" s="16"/>
+      <c r="K94" s="16"/>
+      <c r="L94" s="16"/>
+      <c r="M94" s="16"/>
+      <c r="N94" s="16"/>
+      <c r="O94" s="39"/>
+      <c r="P94" s="39"/>
+      <c r="Q94" s="39"/>
+      <c r="R94" s="39"/>
+      <c r="S94" s="39"/>
+      <c r="T94" s="39"/>
+      <c r="U94" s="39"/>
+      <c r="V94" s="39"/>
+      <c r="W94" s="111"/>
+    </row>
+    <row r="95" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="39"/>
+      <c r="B95" s="39"/>
+      <c r="C95" s="39"/>
+      <c r="D95" s="39"/>
+      <c r="E95" s="108"/>
+      <c r="F95" s="39"/>
+      <c r="G95" s="39"/>
+      <c r="H95" s="39"/>
+      <c r="I95" s="39"/>
+      <c r="J95" s="16"/>
+      <c r="K95" s="16"/>
+      <c r="L95" s="16"/>
+      <c r="M95" s="16"/>
+      <c r="N95" s="16"/>
+      <c r="O95" s="39"/>
+      <c r="P95" s="39"/>
+      <c r="Q95" s="39"/>
+      <c r="R95" s="39"/>
+      <c r="S95" s="39"/>
+      <c r="T95" s="39"/>
+      <c r="U95" s="39"/>
+      <c r="V95" s="39"/>
+      <c r="W95" s="111"/>
+    </row>
+    <row r="96" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="39"/>
+      <c r="B96" s="39"/>
+      <c r="C96" s="39"/>
+      <c r="D96" s="39"/>
+      <c r="E96" s="108"/>
+      <c r="F96" s="39"/>
+      <c r="G96" s="39"/>
+      <c r="H96" s="39"/>
+      <c r="I96" s="39"/>
+      <c r="J96" s="16"/>
+      <c r="K96" s="16"/>
+      <c r="L96" s="16"/>
+      <c r="M96" s="16"/>
+      <c r="N96" s="16"/>
+      <c r="O96" s="39"/>
+      <c r="P96" s="39"/>
+      <c r="Q96" s="39"/>
+      <c r="R96" s="39"/>
+      <c r="S96" s="39"/>
+      <c r="T96" s="39"/>
+      <c r="U96" s="39"/>
+      <c r="V96" s="39"/>
+      <c r="W96" s="111"/>
+    </row>
+    <row r="97" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="39"/>
+      <c r="B97" s="39"/>
+      <c r="C97" s="39"/>
+      <c r="D97" s="39"/>
+      <c r="E97" s="108"/>
+      <c r="F97" s="39"/>
+      <c r="G97" s="39"/>
+      <c r="H97" s="39"/>
+      <c r="I97" s="39"/>
+      <c r="J97" s="16"/>
+      <c r="K97" s="16"/>
+      <c r="L97" s="16"/>
+      <c r="M97" s="16"/>
+      <c r="N97" s="16"/>
+      <c r="O97" s="39"/>
+      <c r="P97" s="39"/>
+      <c r="Q97" s="39"/>
+      <c r="R97" s="39"/>
+      <c r="S97" s="39"/>
+      <c r="T97" s="39"/>
+      <c r="U97" s="39"/>
+      <c r="V97" s="39"/>
+      <c r="W97" s="111"/>
+    </row>
+    <row r="98" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="39"/>
+      <c r="B98" s="39"/>
+      <c r="C98" s="39"/>
+      <c r="D98" s="39"/>
+      <c r="E98" s="108"/>
+      <c r="F98" s="39"/>
+      <c r="G98" s="39"/>
+      <c r="H98" s="39"/>
+      <c r="I98" s="39"/>
+      <c r="J98" s="16"/>
+      <c r="K98" s="16"/>
+      <c r="L98" s="16"/>
+      <c r="M98" s="16"/>
+      <c r="N98" s="16"/>
+      <c r="O98" s="39"/>
+      <c r="P98" s="39"/>
+      <c r="Q98" s="39"/>
+      <c r="R98" s="39"/>
+      <c r="S98" s="39"/>
+      <c r="T98" s="39"/>
+      <c r="U98" s="39"/>
+      <c r="V98" s="39"/>
+      <c r="W98" s="111"/>
+    </row>
+    <row r="99" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="39"/>
+      <c r="B99" s="39"/>
+      <c r="C99" s="39"/>
+      <c r="D99" s="39"/>
+      <c r="E99" s="108"/>
+      <c r="F99" s="39"/>
+      <c r="G99" s="39"/>
+      <c r="H99" s="39"/>
+      <c r="I99" s="39"/>
+      <c r="J99" s="16"/>
+      <c r="K99" s="16"/>
+      <c r="L99" s="16"/>
+      <c r="M99" s="16"/>
+      <c r="N99" s="16"/>
+      <c r="O99" s="39"/>
+      <c r="P99" s="39"/>
+      <c r="Q99" s="39"/>
+      <c r="R99" s="39"/>
+      <c r="S99" s="39"/>
+      <c r="T99" s="39"/>
+      <c r="U99" s="39"/>
+      <c r="V99" s="39"/>
+      <c r="W99" s="111"/>
+    </row>
+    <row r="100" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="39"/>
+      <c r="B100" s="39"/>
+      <c r="C100" s="39"/>
+      <c r="D100" s="39"/>
+      <c r="E100" s="108"/>
+      <c r="F100" s="39"/>
+      <c r="G100" s="39"/>
+      <c r="H100" s="39"/>
+      <c r="I100" s="39"/>
+      <c r="J100" s="16"/>
+      <c r="K100" s="16"/>
+      <c r="L100" s="16"/>
+      <c r="M100" s="16"/>
+      <c r="N100" s="16"/>
+      <c r="O100" s="39"/>
+      <c r="P100" s="39"/>
+      <c r="Q100" s="39"/>
+      <c r="R100" s="39"/>
+      <c r="S100" s="39"/>
+      <c r="T100" s="39"/>
+      <c r="U100" s="39"/>
+      <c r="V100" s="39"/>
+      <c r="W100" s="111"/>
+    </row>
+    <row r="101" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="39"/>
+      <c r="B101" s="39"/>
+      <c r="C101" s="39"/>
+      <c r="D101" s="39"/>
+      <c r="E101" s="108"/>
+      <c r="F101" s="39"/>
+      <c r="G101" s="39"/>
+      <c r="H101" s="39"/>
+      <c r="I101" s="39"/>
+      <c r="J101" s="16"/>
+      <c r="K101" s="16"/>
+      <c r="L101" s="16"/>
+      <c r="M101" s="16"/>
+      <c r="N101" s="16"/>
+      <c r="O101" s="39"/>
+      <c r="P101" s="39"/>
+      <c r="Q101" s="39"/>
+      <c r="R101" s="39"/>
+      <c r="S101" s="39"/>
+      <c r="T101" s="39"/>
+      <c r="U101" s="39"/>
+      <c r="V101" s="39"/>
+      <c r="W101" s="111"/>
+    </row>
+    <row r="102" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="39"/>
+      <c r="B102" s="39"/>
+      <c r="C102" s="39"/>
+      <c r="D102" s="39"/>
+      <c r="E102" s="108"/>
+      <c r="F102" s="39"/>
+      <c r="G102" s="39"/>
+      <c r="H102" s="39"/>
+      <c r="I102" s="39"/>
+      <c r="J102" s="16"/>
+      <c r="K102" s="16"/>
+      <c r="L102" s="16"/>
+      <c r="M102" s="16"/>
+      <c r="N102" s="16"/>
+      <c r="O102" s="39"/>
+      <c r="P102" s="39"/>
+      <c r="Q102" s="39"/>
+      <c r="R102" s="39"/>
+      <c r="S102" s="39"/>
+      <c r="T102" s="39"/>
+      <c r="U102" s="39"/>
+      <c r="V102" s="39"/>
+      <c r="W102" s="111"/>
+    </row>
+    <row r="103" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="39"/>
+      <c r="B103" s="39"/>
+      <c r="C103" s="39"/>
+      <c r="D103" s="39"/>
+      <c r="E103" s="108"/>
+      <c r="F103" s="39"/>
+      <c r="G103" s="39"/>
+      <c r="H103" s="39"/>
+      <c r="I103" s="39"/>
+      <c r="J103" s="16"/>
+      <c r="K103" s="16"/>
+      <c r="L103" s="16"/>
+      <c r="M103" s="16"/>
+      <c r="N103" s="16"/>
+      <c r="O103" s="39"/>
+      <c r="P103" s="39"/>
+      <c r="Q103" s="39"/>
+      <c r="R103" s="39"/>
+      <c r="S103" s="39"/>
+      <c r="T103" s="39"/>
+      <c r="U103" s="39"/>
+      <c r="V103" s="39"/>
+      <c r="W103" s="111"/>
+    </row>
+    <row r="104" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="39"/>
+      <c r="B104" s="39"/>
+      <c r="C104" s="39"/>
+      <c r="D104" s="39"/>
+      <c r="E104" s="108"/>
+      <c r="F104" s="39"/>
+      <c r="G104" s="39"/>
+      <c r="H104" s="39"/>
+      <c r="I104" s="39"/>
+      <c r="J104" s="16"/>
+      <c r="K104" s="16"/>
+      <c r="L104" s="16"/>
+      <c r="M104" s="16"/>
+      <c r="N104" s="16"/>
+      <c r="O104" s="39"/>
+      <c r="P104" s="39"/>
+      <c r="Q104" s="39"/>
+      <c r="R104" s="39"/>
+      <c r="S104" s="39"/>
+      <c r="T104" s="39"/>
+      <c r="U104" s="39"/>
+      <c r="V104" s="39"/>
+      <c r="W104" s="111"/>
+    </row>
+    <row r="105" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="39"/>
+      <c r="B105" s="39"/>
+      <c r="C105" s="39"/>
+      <c r="D105" s="39"/>
+      <c r="E105" s="108"/>
+      <c r="F105" s="39"/>
+      <c r="G105" s="39"/>
+      <c r="H105" s="39"/>
+      <c r="I105" s="39"/>
+      <c r="J105" s="16"/>
+      <c r="K105" s="16"/>
+      <c r="L105" s="16"/>
+      <c r="M105" s="16"/>
+      <c r="N105" s="16"/>
+      <c r="O105" s="39"/>
+      <c r="P105" s="39"/>
+      <c r="Q105" s="39"/>
+      <c r="R105" s="39"/>
+      <c r="S105" s="39"/>
+      <c r="T105" s="39"/>
+      <c r="U105" s="39"/>
+      <c r="V105" s="39"/>
+      <c r="W105" s="111"/>
+    </row>
+    <row r="106" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="39"/>
+      <c r="B106" s="39"/>
+      <c r="C106" s="39"/>
+      <c r="D106" s="39"/>
+      <c r="E106" s="108"/>
+      <c r="F106" s="39"/>
+      <c r="G106" s="39"/>
+      <c r="H106" s="39"/>
+      <c r="I106" s="39"/>
+      <c r="J106" s="16"/>
+      <c r="K106" s="16"/>
+      <c r="L106" s="16"/>
+      <c r="M106" s="16"/>
+      <c r="N106" s="16"/>
+      <c r="O106" s="39"/>
+      <c r="P106" s="39"/>
+      <c r="Q106" s="39"/>
+      <c r="R106" s="39"/>
+      <c r="S106" s="39"/>
+      <c r="T106" s="39"/>
+      <c r="U106" s="39"/>
+      <c r="V106" s="39"/>
+      <c r="W106" s="111"/>
+    </row>
+    <row r="107" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="39"/>
+      <c r="B107" s="39"/>
+      <c r="C107" s="39"/>
+      <c r="D107" s="39"/>
+      <c r="E107" s="108"/>
+      <c r="F107" s="39"/>
+      <c r="G107" s="39"/>
+      <c r="H107" s="39"/>
+      <c r="I107" s="39"/>
+      <c r="J107" s="16"/>
+      <c r="K107" s="16"/>
+      <c r="L107" s="16"/>
+      <c r="M107" s="16"/>
+      <c r="N107" s="16"/>
+      <c r="O107" s="39"/>
+      <c r="P107" s="39"/>
+      <c r="Q107" s="39"/>
+      <c r="R107" s="39"/>
+      <c r="S107" s="39"/>
+      <c r="T107" s="39"/>
+      <c r="U107" s="39"/>
+      <c r="V107" s="39"/>
+      <c r="W107" s="111"/>
+    </row>
+    <row r="108" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="39"/>
+      <c r="B108" s="39"/>
+      <c r="C108" s="39"/>
+      <c r="D108" s="39"/>
+      <c r="E108" s="108"/>
+      <c r="F108" s="39"/>
+      <c r="G108" s="39"/>
+      <c r="H108" s="39"/>
+      <c r="I108" s="39"/>
+      <c r="J108" s="16"/>
+      <c r="K108" s="16"/>
+      <c r="L108" s="16"/>
+      <c r="M108" s="16"/>
+      <c r="N108" s="16"/>
+      <c r="O108" s="39"/>
+      <c r="P108" s="39"/>
+      <c r="Q108" s="39"/>
+      <c r="R108" s="39"/>
+      <c r="S108" s="39"/>
+      <c r="T108" s="39"/>
+      <c r="U108" s="39"/>
+      <c r="V108" s="39"/>
+      <c r="W108" s="111"/>
+    </row>
+    <row r="109" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="39"/>
+      <c r="B109" s="39"/>
+      <c r="C109" s="39"/>
+      <c r="D109" s="39"/>
+      <c r="E109" s="108"/>
+      <c r="F109" s="39"/>
+      <c r="G109" s="39"/>
+      <c r="H109" s="39"/>
+      <c r="I109" s="39"/>
+      <c r="J109" s="16"/>
+      <c r="K109" s="16"/>
+      <c r="L109" s="16"/>
+      <c r="M109" s="16"/>
+      <c r="N109" s="16"/>
+      <c r="O109" s="39"/>
+      <c r="P109" s="39"/>
+      <c r="Q109" s="39"/>
+      <c r="R109" s="39"/>
+      <c r="S109" s="39"/>
+      <c r="T109" s="39"/>
+      <c r="U109" s="39"/>
+      <c r="V109" s="39"/>
+      <c r="W109" s="111"/>
+    </row>
+    <row r="110" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="39"/>
+      <c r="B110" s="39"/>
+      <c r="C110" s="39"/>
+      <c r="D110" s="39"/>
+      <c r="E110" s="108"/>
+      <c r="F110" s="39"/>
+      <c r="G110" s="39"/>
+      <c r="H110" s="39"/>
+      <c r="I110" s="39"/>
+      <c r="J110" s="16"/>
+      <c r="K110" s="16"/>
+      <c r="L110" s="16"/>
+      <c r="M110" s="16"/>
+      <c r="N110" s="16"/>
+      <c r="O110" s="39"/>
+      <c r="P110" s="39"/>
+      <c r="Q110" s="39"/>
+      <c r="R110" s="39"/>
+      <c r="S110" s="39"/>
+      <c r="T110" s="39"/>
+      <c r="U110" s="39"/>
+      <c r="V110" s="39"/>
+      <c r="W110" s="111"/>
+    </row>
+    <row r="111" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="39"/>
+      <c r="B111" s="39"/>
+      <c r="C111" s="39"/>
+      <c r="D111" s="39"/>
+      <c r="E111" s="108"/>
+      <c r="F111" s="39"/>
+      <c r="G111" s="39"/>
+      <c r="H111" s="39"/>
+      <c r="I111" s="39"/>
+      <c r="J111" s="16"/>
+      <c r="K111" s="16"/>
+      <c r="L111" s="16"/>
+      <c r="M111" s="16"/>
+      <c r="N111" s="16"/>
+      <c r="O111" s="39"/>
+      <c r="P111" s="39"/>
+      <c r="Q111" s="39"/>
+      <c r="R111" s="39"/>
+      <c r="S111" s="39"/>
+      <c r="T111" s="39"/>
+      <c r="U111" s="39"/>
+      <c r="V111" s="39"/>
+      <c r="W111" s="111"/>
+    </row>
+    <row r="112" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="39"/>
+      <c r="B112" s="39"/>
+      <c r="C112" s="39"/>
+      <c r="D112" s="39"/>
+      <c r="E112" s="108"/>
+      <c r="F112" s="39"/>
+      <c r="G112" s="39"/>
+      <c r="H112" s="39"/>
+      <c r="I112" s="39"/>
+      <c r="J112" s="16"/>
+      <c r="K112" s="16"/>
+      <c r="L112" s="16"/>
+      <c r="M112" s="16"/>
+      <c r="N112" s="16"/>
+      <c r="O112" s="39"/>
+      <c r="P112" s="39"/>
+      <c r="Q112" s="39"/>
+      <c r="R112" s="39"/>
+      <c r="S112" s="39"/>
+      <c r="T112" s="39"/>
+      <c r="U112" s="39"/>
+      <c r="V112" s="39"/>
+      <c r="W112" s="111"/>
+    </row>
+    <row r="113" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="39"/>
+      <c r="B113" s="39"/>
+      <c r="C113" s="39"/>
+      <c r="D113" s="39"/>
+      <c r="E113" s="108"/>
+      <c r="F113" s="39"/>
+      <c r="G113" s="39"/>
+      <c r="H113" s="39"/>
+      <c r="I113" s="39"/>
+      <c r="J113" s="16"/>
+      <c r="K113" s="16"/>
+      <c r="L113" s="16"/>
+      <c r="M113" s="16"/>
+      <c r="N113" s="16"/>
+      <c r="O113" s="39"/>
+      <c r="P113" s="39"/>
+      <c r="Q113" s="39"/>
+      <c r="R113" s="39"/>
+      <c r="S113" s="39"/>
+      <c r="T113" s="39"/>
+      <c r="U113" s="39"/>
+      <c r="V113" s="39"/>
+      <c r="W113" s="111"/>
+    </row>
+    <row r="114" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="39"/>
+      <c r="B114" s="39"/>
+      <c r="C114" s="39"/>
+      <c r="D114" s="39"/>
+      <c r="E114" s="108"/>
+      <c r="F114" s="39"/>
+      <c r="G114" s="39"/>
+      <c r="H114" s="39"/>
+      <c r="I114" s="39"/>
+      <c r="J114" s="16"/>
+      <c r="K114" s="16"/>
+      <c r="L114" s="16"/>
+      <c r="M114" s="16"/>
+      <c r="N114" s="16"/>
+      <c r="O114" s="39"/>
+      <c r="P114" s="39"/>
+      <c r="Q114" s="39"/>
+      <c r="R114" s="39"/>
+      <c r="S114" s="39"/>
+      <c r="T114" s="39"/>
+      <c r="U114" s="39"/>
+      <c r="V114" s="39"/>
+      <c r="W114" s="111"/>
+    </row>
+    <row r="115" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="39"/>
+      <c r="B115" s="39"/>
+      <c r="C115" s="39"/>
+      <c r="D115" s="39"/>
+      <c r="E115" s="108"/>
+      <c r="F115" s="39"/>
+      <c r="G115" s="39"/>
+      <c r="H115" s="62"/>
+      <c r="I115" s="39"/>
+      <c r="J115" s="16"/>
+      <c r="K115" s="111"/>
+      <c r="L115" s="111"/>
+      <c r="M115" s="111"/>
+      <c r="N115" s="111"/>
+      <c r="O115" s="39"/>
+      <c r="P115" s="39"/>
+      <c r="Q115" s="39"/>
+      <c r="R115" s="39"/>
+      <c r="S115" s="39"/>
+      <c r="T115" s="39"/>
+      <c r="U115" s="39"/>
+      <c r="V115" s="39"/>
+      <c r="W115" s="111"/>
+    </row>
+    <row r="116" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="39"/>
+      <c r="B116" s="39"/>
+      <c r="C116" s="39"/>
+      <c r="D116" s="39"/>
+      <c r="E116" s="108"/>
+      <c r="F116" s="39"/>
+      <c r="G116" s="39"/>
+      <c r="H116" s="62"/>
+      <c r="I116" s="39"/>
+      <c r="J116" s="129"/>
+      <c r="K116" s="111"/>
+      <c r="L116" s="111"/>
+      <c r="M116" s="111"/>
+      <c r="N116" s="111"/>
+      <c r="O116" s="39"/>
+      <c r="P116" s="39"/>
+      <c r="Q116" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="R116" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="S116" s="39"/>
+      <c r="T116" s="39"/>
+      <c r="U116" s="39"/>
+      <c r="V116" s="39"/>
+      <c r="W116" s="111"/>
+    </row>
+    <row r="117" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="39"/>
+      <c r="B117" s="39"/>
+      <c r="C117" s="39"/>
+      <c r="D117" s="39"/>
+      <c r="E117" s="108"/>
+      <c r="F117" s="39"/>
+      <c r="G117" s="39"/>
+      <c r="H117" s="62"/>
+      <c r="I117" s="39"/>
+      <c r="J117" s="129"/>
+      <c r="K117" s="111"/>
+      <c r="L117" s="111"/>
+      <c r="M117" s="111"/>
+      <c r="N117" s="111"/>
+      <c r="O117" s="39"/>
+      <c r="P117" s="39"/>
+      <c r="Q117" s="43">
+        <v>2025</v>
+      </c>
+      <c r="R117" s="44">
+        <f>COUNTIF(D1:D57,Q117)</f>
+        <v>1</v>
+      </c>
+      <c r="S117" s="39"/>
+      <c r="T117" s="39"/>
+      <c r="U117" s="39"/>
+      <c r="V117" s="39"/>
+      <c r="W117" s="111"/>
+    </row>
+    <row r="118" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="39"/>
+      <c r="B118" s="39"/>
+      <c r="C118" s="39"/>
+      <c r="D118" s="39"/>
+      <c r="E118" s="108"/>
+      <c r="F118" s="39"/>
+      <c r="G118" s="39"/>
+      <c r="H118" s="62"/>
+      <c r="I118" s="39"/>
+      <c r="J118" s="16"/>
+      <c r="K118" s="111"/>
+      <c r="L118" s="111"/>
+      <c r="M118" s="111"/>
+      <c r="N118" s="111"/>
+      <c r="O118" s="39"/>
+      <c r="P118" s="39"/>
+      <c r="Q118" s="45">
+        <v>2024</v>
+      </c>
+      <c r="R118" s="46">
+        <f>COUNTIF(D2:D58,Q118)</f>
+        <v>0</v>
+      </c>
+      <c r="S118" s="39"/>
+      <c r="T118" s="39"/>
+      <c r="U118" s="39"/>
+      <c r="V118" s="39"/>
+      <c r="W118" s="111"/>
+    </row>
+    <row r="119" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="39"/>
+      <c r="B119" s="39"/>
+      <c r="C119" s="39"/>
+      <c r="D119" s="39"/>
+      <c r="E119" s="108"/>
+      <c r="F119" s="39"/>
+      <c r="G119" s="39"/>
+      <c r="H119" s="62"/>
+      <c r="I119" s="39"/>
+      <c r="J119" s="16"/>
+      <c r="K119" s="111"/>
+      <c r="L119" s="111"/>
+      <c r="M119" s="111"/>
+      <c r="N119" s="111"/>
+      <c r="O119" s="39"/>
+      <c r="P119" s="39"/>
+      <c r="Q119" s="46">
+        <v>2023</v>
+      </c>
+      <c r="R119" s="167">
+        <f>COUNTIF(D3:D59,Q119)</f>
+        <v>0</v>
+      </c>
+      <c r="S119" s="39"/>
+      <c r="T119" s="39"/>
+      <c r="U119" s="39"/>
+      <c r="V119" s="39"/>
+      <c r="W119" s="111"/>
+    </row>
+    <row r="120" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="39"/>
+      <c r="B120" s="39"/>
+      <c r="C120" s="39"/>
+      <c r="D120" s="39"/>
+      <c r="E120" s="108"/>
+      <c r="F120" s="39"/>
+      <c r="G120" s="39"/>
+      <c r="H120" s="62"/>
+      <c r="I120" s="39"/>
+      <c r="J120" s="16"/>
+      <c r="K120" s="111"/>
+      <c r="L120" s="111"/>
+      <c r="M120" s="111"/>
+      <c r="N120" s="111"/>
+      <c r="O120" s="39"/>
+      <c r="P120" s="39"/>
+      <c r="Q120" s="46">
+        <v>2022</v>
+      </c>
+      <c r="R120" s="167">
+        <f>COUNTIF(D3:D58,Q120)</f>
+        <v>0</v>
+      </c>
+      <c r="S120" s="39"/>
+      <c r="T120" s="39"/>
+      <c r="U120" s="39"/>
+      <c r="V120" s="39"/>
+      <c r="W120" s="111"/>
+    </row>
+    <row r="121" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="39"/>
+      <c r="B121" s="39"/>
+      <c r="C121" s="39"/>
+      <c r="D121" s="39"/>
+      <c r="E121" s="108"/>
+      <c r="F121" s="39"/>
+      <c r="G121" s="39"/>
+      <c r="H121" s="62"/>
+      <c r="I121" s="39"/>
+      <c r="J121" s="16"/>
+      <c r="K121" s="111"/>
+      <c r="L121" s="111"/>
+      <c r="M121" s="111"/>
+      <c r="N121" s="111"/>
+      <c r="O121" s="39"/>
+      <c r="P121" s="39"/>
+      <c r="Q121" s="144">
+        <v>2021</v>
+      </c>
+      <c r="R121" s="145">
+        <f>COUNTIF(D3:D59,Q121)</f>
+        <v>0</v>
+      </c>
+      <c r="S121" s="39"/>
+      <c r="T121" s="39"/>
+      <c r="U121" s="39"/>
+      <c r="V121" s="39"/>
+      <c r="W121" s="111"/>
+    </row>
+    <row r="122" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="39"/>
+      <c r="B122" s="39"/>
+      <c r="C122" s="39"/>
+      <c r="D122" s="39"/>
+      <c r="E122" s="108"/>
+      <c r="F122" s="39"/>
+      <c r="G122" s="39"/>
+      <c r="H122" s="62"/>
+      <c r="I122" s="39"/>
+      <c r="J122" s="16"/>
+      <c r="K122" s="111"/>
+      <c r="L122" s="111"/>
+      <c r="M122" s="111"/>
+      <c r="N122" s="111"/>
+      <c r="O122" s="39"/>
+      <c r="P122" s="39"/>
+      <c r="Q122" s="45">
+        <v>2020</v>
+      </c>
+      <c r="R122" s="46">
+        <f>COUNTIF(D3:D59,Q122)</f>
+        <v>0</v>
+      </c>
+      <c r="S122" s="39"/>
+      <c r="T122" s="39"/>
+      <c r="U122" s="39"/>
+      <c r="V122" s="39"/>
+      <c r="W122" s="111"/>
+    </row>
+    <row r="123" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="39"/>
+      <c r="B123" s="39"/>
+      <c r="C123" s="39"/>
+      <c r="D123" s="39"/>
+      <c r="E123" s="108"/>
+      <c r="F123" s="39"/>
+      <c r="G123" s="39"/>
+      <c r="H123" s="62"/>
+      <c r="I123" s="39"/>
+      <c r="J123" s="16"/>
+      <c r="K123" s="111"/>
+      <c r="L123" s="111"/>
+      <c r="M123" s="111"/>
+      <c r="N123" s="111"/>
+      <c r="O123" s="39"/>
+      <c r="P123" s="39"/>
+      <c r="Q123" s="45">
+        <v>2019</v>
+      </c>
+      <c r="R123" s="46">
+        <f>COUNTIF(D3:D59,Q123)</f>
+        <v>0</v>
+      </c>
+      <c r="S123" s="39"/>
+      <c r="T123" s="39"/>
+      <c r="U123" s="39"/>
+      <c r="V123" s="39"/>
+      <c r="W123" s="111"/>
+    </row>
+    <row r="124" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="39"/>
+      <c r="B124" s="39"/>
+      <c r="C124" s="39"/>
+      <c r="D124" s="39"/>
+      <c r="E124" s="108"/>
+      <c r="F124" s="39"/>
+      <c r="G124" s="39"/>
+      <c r="H124" s="62"/>
+      <c r="I124" s="39"/>
+      <c r="J124" s="16"/>
+      <c r="K124" s="111"/>
+      <c r="L124" s="111"/>
+      <c r="M124" s="111"/>
+      <c r="N124" s="111"/>
+      <c r="O124" s="39"/>
+      <c r="P124" s="39"/>
+      <c r="Q124" s="45">
+        <v>2018</v>
+      </c>
+      <c r="R124" s="46">
+        <f>COUNTIF(D3:D59,Q124)</f>
+        <v>0</v>
+      </c>
+      <c r="S124" s="39"/>
+      <c r="T124" s="39"/>
+      <c r="U124" s="39"/>
+      <c r="V124" s="39"/>
+      <c r="W124" s="111"/>
+    </row>
+    <row r="125" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="39"/>
+      <c r="B125" s="39"/>
+      <c r="C125" s="39"/>
+      <c r="D125" s="39"/>
+      <c r="E125" s="108"/>
+      <c r="F125" s="39"/>
+      <c r="G125" s="39"/>
+      <c r="H125" s="39"/>
+      <c r="I125" s="39"/>
+      <c r="J125" s="16"/>
+      <c r="K125" s="16"/>
+      <c r="L125" s="16"/>
+      <c r="M125" s="16"/>
+      <c r="N125" s="16"/>
+      <c r="O125" s="39"/>
+      <c r="P125" s="39"/>
+      <c r="Q125" s="45">
+        <v>2017</v>
+      </c>
+      <c r="R125" s="46">
+        <f>COUNTIF(D3:D59,Q125)</f>
+        <v>0</v>
+      </c>
+      <c r="S125" s="39"/>
+      <c r="T125" s="39"/>
+      <c r="U125" s="39"/>
+      <c r="V125" s="39"/>
+      <c r="W125" s="111"/>
+    </row>
+    <row r="126" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="39"/>
+      <c r="B126" s="39"/>
+      <c r="C126" s="39"/>
+      <c r="D126" s="39"/>
+      <c r="E126" s="108"/>
+      <c r="F126" s="39"/>
+      <c r="G126" s="39"/>
+      <c r="H126" s="39"/>
+      <c r="I126" s="39"/>
+      <c r="J126" s="16"/>
+      <c r="K126" s="16"/>
+      <c r="L126" s="16"/>
+      <c r="M126" s="16"/>
+      <c r="N126" s="16"/>
+      <c r="O126" s="39"/>
+      <c r="P126" s="39"/>
+      <c r="Q126" s="45">
+        <v>2016</v>
+      </c>
+      <c r="R126" s="46">
+        <f>COUNTIF(D3:D59,Q126)</f>
+        <v>0</v>
+      </c>
+      <c r="S126" s="39"/>
+      <c r="T126" s="39"/>
+      <c r="U126" s="39"/>
+      <c r="V126" s="39"/>
+      <c r="W126" s="111"/>
+    </row>
+    <row r="127" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="39"/>
+      <c r="B127" s="39"/>
+      <c r="C127" s="39"/>
+      <c r="D127" s="39"/>
+      <c r="E127" s="108"/>
+      <c r="F127" s="39"/>
+      <c r="G127" s="39"/>
+      <c r="H127" s="39"/>
+      <c r="I127" s="39"/>
+      <c r="J127" s="16"/>
+      <c r="K127" s="16"/>
+      <c r="L127" s="16"/>
+      <c r="M127" s="16"/>
+      <c r="N127" s="16"/>
+      <c r="O127" s="39"/>
+      <c r="P127" s="39"/>
+      <c r="Q127" s="45">
+        <v>2015</v>
+      </c>
+      <c r="R127" s="46">
+        <f>COUNTIF(D3:D59,Q127)</f>
+        <v>0</v>
+      </c>
+      <c r="S127" s="39"/>
+      <c r="T127" s="39"/>
+      <c r="U127" s="39"/>
+      <c r="V127" s="39"/>
+      <c r="W127" s="111"/>
+    </row>
+    <row r="128" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="39"/>
+      <c r="B128" s="39"/>
+      <c r="C128" s="39"/>
+      <c r="D128" s="39"/>
+      <c r="E128" s="108"/>
+      <c r="F128" s="39"/>
+      <c r="G128" s="39"/>
+      <c r="H128" s="39"/>
+      <c r="I128" s="39"/>
+      <c r="J128" s="16"/>
+      <c r="K128" s="16"/>
+      <c r="L128" s="16"/>
+      <c r="M128" s="16"/>
+      <c r="N128" s="16"/>
+      <c r="O128" s="39"/>
+      <c r="P128" s="39"/>
+      <c r="Q128" s="45">
+        <v>2014</v>
+      </c>
+      <c r="R128" s="46">
+        <f>COUNTIF(D3:D59,Q128)</f>
+        <v>0</v>
+      </c>
+      <c r="S128" s="39"/>
+      <c r="T128" s="39"/>
+      <c r="U128" s="39"/>
+      <c r="V128" s="39"/>
+      <c r="W128" s="111"/>
+    </row>
+    <row r="129" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="39"/>
+      <c r="B129" s="39"/>
+      <c r="C129" s="39"/>
+      <c r="D129" s="39"/>
+      <c r="E129" s="108"/>
+      <c r="F129" s="39"/>
+      <c r="G129" s="39"/>
+      <c r="H129" s="39"/>
+      <c r="I129" s="39"/>
+      <c r="J129" s="16"/>
+      <c r="K129" s="16"/>
+      <c r="L129" s="16"/>
+      <c r="M129" s="16"/>
+      <c r="N129" s="16"/>
+      <c r="O129" s="39"/>
+      <c r="P129" s="39"/>
+      <c r="Q129" s="45">
+        <v>2013</v>
+      </c>
+      <c r="R129" s="46">
+        <f>COUNTIF(D3:D59,Q129)</f>
+        <v>3</v>
+      </c>
+      <c r="S129" s="39"/>
+      <c r="T129" s="39"/>
+      <c r="U129" s="39"/>
+      <c r="V129" s="39"/>
+      <c r="W129" s="111"/>
+    </row>
+    <row r="130" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="39"/>
+      <c r="B130" s="39"/>
+      <c r="C130" s="39"/>
+      <c r="D130" s="39"/>
+      <c r="E130" s="108"/>
+      <c r="F130" s="39"/>
+      <c r="G130" s="39"/>
+      <c r="H130" s="39"/>
+      <c r="I130" s="39"/>
+      <c r="J130" s="16"/>
+      <c r="K130" s="16"/>
+      <c r="L130" s="16"/>
+      <c r="M130" s="16"/>
+      <c r="N130" s="16"/>
+      <c r="O130" s="39"/>
+      <c r="P130" s="39"/>
+      <c r="Q130" s="45">
+        <v>2012</v>
+      </c>
+      <c r="R130" s="46">
+        <f>COUNTIF(D3:D59,Q130)</f>
+        <v>0</v>
+      </c>
+      <c r="S130" s="39"/>
+      <c r="T130" s="39"/>
+      <c r="U130" s="39"/>
+      <c r="V130" s="39"/>
+      <c r="W130" s="111"/>
+    </row>
+    <row r="131" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="39"/>
+      <c r="B131" s="39"/>
+      <c r="C131" s="39"/>
+      <c r="D131" s="39"/>
+      <c r="E131" s="108"/>
+      <c r="F131" s="39"/>
+      <c r="G131" s="39"/>
+      <c r="H131" s="39"/>
+      <c r="I131" s="39"/>
+      <c r="J131" s="16"/>
+      <c r="K131" s="16"/>
+      <c r="L131" s="16"/>
+      <c r="M131" s="16"/>
+      <c r="N131" s="16"/>
+      <c r="O131" s="39"/>
+      <c r="P131" s="39"/>
+      <c r="Q131" s="45">
+        <v>2011</v>
+      </c>
+      <c r="R131" s="46">
+        <f>COUNTIF(D3:D59,Q131)</f>
+        <v>1</v>
+      </c>
+      <c r="S131" s="39"/>
+      <c r="T131" s="39"/>
+      <c r="U131" s="39"/>
+      <c r="V131" s="39"/>
+      <c r="W131" s="111"/>
+    </row>
+    <row r="132" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="39"/>
+      <c r="B132" s="39"/>
+      <c r="C132" s="39"/>
+      <c r="D132" s="39"/>
+      <c r="E132" s="108"/>
+      <c r="F132" s="39"/>
+      <c r="G132" s="39"/>
+      <c r="H132" s="39"/>
+      <c r="I132" s="39"/>
+      <c r="J132" s="16"/>
+      <c r="K132" s="16"/>
+      <c r="L132" s="16"/>
+      <c r="M132" s="16"/>
+      <c r="N132" s="16"/>
+      <c r="O132" s="39"/>
+      <c r="P132" s="39"/>
+      <c r="Q132" s="45">
+        <v>2010</v>
+      </c>
+      <c r="R132" s="46">
+        <f>COUNTIF(D3:D59,Q132)</f>
+        <v>0</v>
+      </c>
+      <c r="S132" s="39"/>
+      <c r="T132" s="39"/>
+      <c r="U132" s="39"/>
+      <c r="V132" s="39"/>
+      <c r="W132" s="111"/>
+    </row>
+    <row r="133" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="39"/>
+      <c r="B133" s="39"/>
+      <c r="C133" s="39"/>
+      <c r="D133" s="39"/>
+      <c r="E133" s="108"/>
+      <c r="F133" s="39"/>
+      <c r="G133" s="39"/>
+      <c r="H133" s="39"/>
+      <c r="I133" s="39"/>
+      <c r="J133" s="16"/>
+      <c r="K133" s="16"/>
+      <c r="L133" s="16"/>
+      <c r="M133" s="16"/>
+      <c r="N133" s="16"/>
+      <c r="O133" s="39"/>
+      <c r="P133" s="39"/>
+      <c r="Q133" s="45">
+        <v>2009</v>
+      </c>
+      <c r="R133" s="46">
+        <f>COUNTIF(D3:D59,Q133)</f>
+        <v>0</v>
+      </c>
+      <c r="S133" s="39"/>
+      <c r="T133" s="39"/>
+      <c r="U133" s="39"/>
+      <c r="V133" s="39"/>
+      <c r="W133" s="111"/>
+    </row>
+    <row r="134" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="39"/>
+      <c r="B134" s="39"/>
+      <c r="C134" s="39"/>
+      <c r="D134" s="39"/>
+      <c r="E134" s="108"/>
+      <c r="F134" s="39"/>
+      <c r="G134" s="39"/>
+      <c r="H134" s="39"/>
+      <c r="I134" s="39"/>
+      <c r="J134" s="16"/>
+      <c r="K134" s="16"/>
+      <c r="L134" s="16"/>
+      <c r="M134" s="16"/>
+      <c r="N134" s="16"/>
+      <c r="O134" s="39"/>
+      <c r="P134" s="39"/>
+      <c r="Q134" s="45">
+        <v>2008</v>
+      </c>
+      <c r="R134" s="46">
+        <f>COUNTIF(D3:D59,Q134)</f>
+        <v>0</v>
+      </c>
+      <c r="S134" s="39"/>
+      <c r="T134" s="39"/>
+      <c r="U134" s="39"/>
+      <c r="V134" s="39"/>
+      <c r="W134" s="111"/>
+    </row>
+    <row r="135" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="39"/>
+      <c r="B135" s="39"/>
+      <c r="C135" s="39"/>
+      <c r="D135" s="39"/>
+      <c r="E135" s="108"/>
+      <c r="F135" s="39"/>
+      <c r="G135" s="39"/>
+      <c r="H135" s="39"/>
+      <c r="I135" s="39"/>
+      <c r="J135" s="16"/>
+      <c r="K135" s="16"/>
+      <c r="L135" s="16"/>
+      <c r="M135" s="16"/>
+      <c r="N135" s="16"/>
+      <c r="O135" s="39"/>
+      <c r="P135" s="39"/>
+      <c r="Q135" s="45">
+        <v>2007</v>
+      </c>
+      <c r="R135" s="46">
+        <f>COUNTIF(D3:D59,Q135)</f>
+        <v>0</v>
+      </c>
+      <c r="S135" s="39"/>
+      <c r="T135" s="39"/>
+      <c r="U135" s="39"/>
+      <c r="V135" s="39"/>
+      <c r="W135" s="111"/>
+    </row>
+    <row r="136" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="39"/>
+      <c r="B136" s="39"/>
+      <c r="C136" s="39"/>
+      <c r="D136" s="39"/>
+      <c r="E136" s="108"/>
+      <c r="F136" s="39"/>
+      <c r="G136" s="39"/>
+      <c r="H136" s="39"/>
+      <c r="I136" s="39"/>
+      <c r="J136" s="16"/>
+      <c r="K136" s="16"/>
+      <c r="L136" s="16"/>
+      <c r="M136" s="16"/>
+      <c r="N136" s="16"/>
+      <c r="O136" s="39"/>
+      <c r="P136" s="39"/>
+      <c r="Q136" s="45">
+        <v>2006</v>
+      </c>
+      <c r="R136" s="46">
+        <f>COUNTIF(D3:D59,Q136)</f>
+        <v>0</v>
+      </c>
+      <c r="S136" s="39"/>
+      <c r="T136" s="39"/>
+      <c r="U136" s="39"/>
+      <c r="V136" s="39"/>
+      <c r="W136" s="111"/>
+    </row>
+    <row r="137" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="39"/>
+      <c r="B137" s="39"/>
+      <c r="C137" s="39"/>
+      <c r="D137" s="39"/>
+      <c r="E137" s="108"/>
+      <c r="F137" s="39"/>
+      <c r="G137" s="39"/>
+      <c r="H137" s="39"/>
+      <c r="I137" s="39"/>
+      <c r="J137" s="16"/>
+      <c r="K137" s="16"/>
+      <c r="L137" s="16"/>
+      <c r="M137" s="16"/>
+      <c r="N137" s="16"/>
+      <c r="O137" s="39"/>
+      <c r="P137" s="39"/>
+      <c r="Q137" s="45">
+        <v>2005</v>
+      </c>
+      <c r="R137" s="46">
+        <f>COUNTIF(D3:D59,Q137)</f>
+        <v>2</v>
+      </c>
+      <c r="S137" s="39"/>
+      <c r="T137" s="39"/>
+      <c r="U137" s="39"/>
+      <c r="V137" s="39"/>
+      <c r="W137" s="111"/>
+    </row>
+    <row r="138" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="39"/>
+      <c r="B138" s="39"/>
+      <c r="C138" s="39"/>
+      <c r="D138" s="39"/>
+      <c r="E138" s="108"/>
+      <c r="F138" s="39"/>
+      <c r="G138" s="39"/>
+      <c r="H138" s="39"/>
+      <c r="I138" s="39"/>
+      <c r="J138" s="16"/>
+      <c r="K138" s="16"/>
+      <c r="L138" s="16"/>
+      <c r="M138" s="16"/>
+      <c r="N138" s="16"/>
+      <c r="O138" s="39"/>
+      <c r="P138" s="39"/>
+      <c r="Q138" s="45">
+        <v>2004</v>
+      </c>
+      <c r="R138" s="46">
+        <f>COUNTIF(D3:D59,Q138)</f>
+        <v>0</v>
+      </c>
+      <c r="S138" s="39"/>
+      <c r="T138" s="39"/>
+      <c r="U138" s="39"/>
+      <c r="V138" s="39"/>
+      <c r="W138" s="111"/>
+    </row>
+    <row r="139" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="39"/>
+      <c r="B139" s="39"/>
+      <c r="C139" s="39"/>
+      <c r="D139" s="39"/>
+      <c r="E139" s="108"/>
+      <c r="F139" s="39"/>
+      <c r="G139" s="39"/>
+      <c r="H139" s="39"/>
+      <c r="I139" s="39"/>
+      <c r="J139" s="16"/>
+      <c r="K139" s="16"/>
+      <c r="L139" s="16"/>
+      <c r="M139" s="16"/>
+      <c r="N139" s="16"/>
+      <c r="O139" s="39"/>
+      <c r="P139" s="39"/>
+      <c r="Q139" s="45">
+        <v>2003</v>
+      </c>
+      <c r="R139" s="46">
+        <f>COUNTIF(D3:D59,Q139)</f>
+        <v>0</v>
+      </c>
+      <c r="S139" s="39"/>
+      <c r="T139" s="39"/>
+      <c r="U139" s="39"/>
+      <c r="V139" s="39"/>
+      <c r="W139" s="111"/>
+    </row>
+    <row r="140" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="39"/>
+      <c r="B140" s="39"/>
+      <c r="C140" s="39"/>
+      <c r="D140" s="39"/>
+      <c r="E140" s="108"/>
+      <c r="F140" s="39"/>
+      <c r="G140" s="39"/>
+      <c r="H140" s="39"/>
+      <c r="I140" s="39"/>
+      <c r="J140" s="16"/>
+      <c r="K140" s="16"/>
+      <c r="L140" s="16"/>
+      <c r="M140" s="16"/>
+      <c r="N140" s="16"/>
+      <c r="O140" s="39"/>
+      <c r="P140" s="39"/>
+      <c r="Q140" s="45">
+        <v>2002</v>
+      </c>
+      <c r="R140" s="46">
+        <f>COUNTIF(D3:D59,Q140)</f>
+        <v>0</v>
+      </c>
+      <c r="S140" s="39"/>
+      <c r="T140" s="39"/>
+      <c r="U140" s="39"/>
+      <c r="V140" s="39"/>
+      <c r="W140" s="111"/>
+    </row>
+    <row r="141" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="39"/>
+      <c r="B141" s="39"/>
+      <c r="C141" s="39"/>
+      <c r="D141" s="39"/>
+      <c r="E141" s="108"/>
+      <c r="F141" s="39"/>
+      <c r="G141" s="39"/>
+      <c r="H141" s="39"/>
+      <c r="I141" s="39"/>
+      <c r="J141" s="16"/>
+      <c r="K141" s="16"/>
+      <c r="L141" s="16"/>
+      <c r="M141" s="16"/>
+      <c r="N141" s="16"/>
+      <c r="O141" s="39"/>
+      <c r="P141" s="39"/>
+      <c r="Q141" s="45">
+        <v>2001</v>
+      </c>
+      <c r="R141" s="46">
+        <f>COUNTIF(D3:D59,Q141)</f>
+        <v>0</v>
+      </c>
+      <c r="S141" s="39"/>
+      <c r="T141" s="39"/>
+      <c r="U141" s="39"/>
+      <c r="V141" s="39"/>
+      <c r="W141" s="111"/>
+    </row>
+    <row r="142" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="39"/>
+      <c r="B142" s="39"/>
+      <c r="C142" s="39"/>
+      <c r="D142" s="39"/>
+      <c r="E142" s="108"/>
+      <c r="F142" s="39"/>
+      <c r="G142" s="39"/>
+      <c r="H142" s="39"/>
+      <c r="I142" s="39"/>
+      <c r="J142" s="16"/>
+      <c r="K142" s="16"/>
+      <c r="L142" s="16"/>
+      <c r="M142" s="16"/>
+      <c r="N142" s="16"/>
+      <c r="O142" s="39"/>
+      <c r="P142" s="39"/>
+      <c r="Q142" s="45">
+        <v>2000</v>
+      </c>
+      <c r="R142" s="46">
+        <f>COUNTIF(D3:D59,Q142)</f>
+        <v>0</v>
+      </c>
+      <c r="S142" s="39"/>
+      <c r="T142" s="39"/>
+      <c r="U142" s="39"/>
+      <c r="V142" s="39"/>
+      <c r="W142" s="111"/>
+    </row>
+    <row r="143" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="39"/>
+      <c r="B143" s="39"/>
+      <c r="C143" s="39"/>
+      <c r="D143" s="39"/>
+      <c r="E143" s="108"/>
+      <c r="F143" s="39"/>
+      <c r="G143" s="39"/>
+      <c r="H143" s="39"/>
+      <c r="I143" s="39"/>
+      <c r="J143" s="16"/>
+      <c r="K143" s="16"/>
+      <c r="L143" s="16"/>
+      <c r="M143" s="16"/>
+      <c r="N143" s="16"/>
+      <c r="O143" s="39"/>
+      <c r="P143" s="39"/>
+      <c r="Q143" s="45">
+        <v>1999</v>
+      </c>
+      <c r="R143" s="46">
+        <f>COUNTIF(D3:D59,Q143)</f>
+        <v>0</v>
+      </c>
+      <c r="S143" s="39"/>
+      <c r="T143" s="39"/>
+      <c r="U143" s="39"/>
+      <c r="V143" s="39"/>
+      <c r="W143" s="111"/>
+    </row>
+    <row r="144" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="39"/>
+      <c r="B144" s="39"/>
+      <c r="C144" s="39"/>
+      <c r="D144" s="39"/>
+      <c r="E144" s="108"/>
+      <c r="F144" s="39"/>
+      <c r="G144" s="39"/>
+      <c r="H144" s="39"/>
+      <c r="I144" s="39"/>
+      <c r="J144" s="16"/>
+      <c r="K144" s="16"/>
+      <c r="L144" s="16"/>
+      <c r="M144" s="16"/>
+      <c r="N144" s="16"/>
+      <c r="O144" s="39"/>
+      <c r="P144" s="39"/>
+      <c r="Q144" s="45">
+        <v>1998</v>
+      </c>
+      <c r="R144" s="46">
+        <f>COUNTIF(D3:D59,Q144)</f>
+        <v>0</v>
+      </c>
+      <c r="S144" s="39"/>
+      <c r="T144" s="39"/>
+      <c r="U144" s="39"/>
+      <c r="V144" s="39"/>
+      <c r="W144" s="111"/>
+    </row>
+    <row r="145" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="39"/>
+      <c r="B145" s="39"/>
+      <c r="C145" s="39"/>
+      <c r="D145" s="39"/>
+      <c r="E145" s="108"/>
+      <c r="F145" s="39"/>
+      <c r="G145" s="39"/>
+      <c r="H145" s="39"/>
+      <c r="I145" s="39"/>
+      <c r="J145" s="16"/>
+      <c r="K145" s="16"/>
+      <c r="L145" s="16"/>
+      <c r="M145" s="16"/>
+      <c r="N145" s="16"/>
+      <c r="O145" s="39"/>
+      <c r="P145" s="39"/>
+      <c r="Q145" s="45">
+        <v>1997</v>
+      </c>
+      <c r="R145" s="46">
+        <f>COUNTIF(D3:D45,Q145)</f>
+        <v>1</v>
+      </c>
+      <c r="S145" s="39"/>
+      <c r="T145" s="39"/>
+      <c r="U145" s="39"/>
+      <c r="V145" s="39"/>
+      <c r="W145" s="111"/>
+    </row>
+    <row r="146" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="39"/>
+      <c r="B146" s="39"/>
+      <c r="C146" s="39"/>
+      <c r="D146" s="39"/>
+      <c r="E146" s="108"/>
+      <c r="F146" s="39"/>
+      <c r="G146" s="39"/>
+      <c r="H146" s="39"/>
+      <c r="I146" s="39"/>
+      <c r="J146" s="16"/>
+      <c r="K146" s="16"/>
+      <c r="L146" s="16"/>
+      <c r="M146" s="16"/>
+      <c r="N146" s="16"/>
+      <c r="O146" s="39"/>
+      <c r="P146" s="39"/>
+      <c r="Q146" s="45">
+        <v>1996</v>
+      </c>
+      <c r="R146" s="46">
+        <f>COUNTIF(D3:D46,Q146)</f>
+        <v>0</v>
+      </c>
+      <c r="S146" s="39"/>
+      <c r="T146" s="39"/>
+      <c r="U146" s="39"/>
+      <c r="V146" s="39"/>
+      <c r="W146" s="111"/>
+    </row>
+    <row r="147" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="39"/>
+      <c r="B147" s="39"/>
+      <c r="C147" s="39"/>
+      <c r="D147" s="39"/>
+      <c r="E147" s="108"/>
+      <c r="F147" s="39"/>
+      <c r="G147" s="39"/>
+      <c r="H147" s="39"/>
+      <c r="I147" s="39"/>
+      <c r="J147" s="16"/>
+      <c r="K147" s="16"/>
+      <c r="L147" s="16"/>
+      <c r="M147" s="16"/>
+      <c r="N147" s="16"/>
+      <c r="O147" s="39"/>
+      <c r="P147" s="39"/>
+      <c r="Q147" s="45">
+        <v>1995</v>
+      </c>
+      <c r="R147" s="46">
+        <f>COUNTIF(D3:D47,Q147)</f>
+        <v>0</v>
+      </c>
+      <c r="S147" s="39"/>
+      <c r="T147" s="39"/>
+      <c r="U147" s="39"/>
+      <c r="V147" s="39"/>
+      <c r="W147" s="111"/>
+    </row>
+    <row r="148" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="39"/>
+      <c r="B148" s="39"/>
+      <c r="C148" s="39"/>
+      <c r="D148" s="39"/>
+      <c r="E148" s="108"/>
+      <c r="F148" s="39"/>
+      <c r="G148" s="39"/>
+      <c r="H148" s="39"/>
+      <c r="I148" s="39"/>
+      <c r="J148" s="16"/>
+      <c r="K148" s="16"/>
+      <c r="L148" s="16"/>
+      <c r="M148" s="16"/>
+      <c r="N148" s="16"/>
+      <c r="O148" s="39"/>
+      <c r="P148" s="39"/>
+      <c r="Q148" s="45">
+        <v>1994</v>
+      </c>
+      <c r="R148" s="46">
+        <f>COUNTIF(D3:D48,Q148)</f>
+        <v>0</v>
+      </c>
+      <c r="S148" s="39"/>
+      <c r="T148" s="39"/>
+      <c r="U148" s="39"/>
+      <c r="V148" s="39"/>
+      <c r="W148" s="111"/>
+    </row>
+    <row r="149" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="39"/>
+      <c r="B149" s="39"/>
+      <c r="C149" s="39"/>
+      <c r="D149" s="39"/>
+      <c r="E149" s="108"/>
+      <c r="F149" s="39"/>
+      <c r="G149" s="39"/>
+      <c r="H149" s="39"/>
+      <c r="I149" s="39"/>
+      <c r="J149" s="16"/>
+      <c r="K149" s="16"/>
+      <c r="L149" s="16"/>
+      <c r="M149" s="16"/>
+      <c r="N149" s="16"/>
+      <c r="O149" s="39"/>
+      <c r="P149" s="39"/>
+      <c r="Q149" s="47">
+        <v>1993</v>
+      </c>
+      <c r="R149" s="48">
+        <f>COUNTIF(D3:D49,Q149)</f>
+        <v>0</v>
+      </c>
+      <c r="S149" s="39"/>
+      <c r="T149" s="39"/>
+      <c r="U149" s="39"/>
+      <c r="V149" s="39"/>
+      <c r="W149" s="111"/>
+    </row>
+    <row r="150" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="39"/>
+      <c r="B150" s="39"/>
+      <c r="C150" s="39"/>
+      <c r="D150" s="39"/>
+      <c r="E150" s="108"/>
+      <c r="F150" s="39"/>
+      <c r="G150" s="39"/>
+      <c r="H150" s="39"/>
+      <c r="I150" s="39"/>
+      <c r="J150" s="16"/>
+      <c r="K150" s="16"/>
+      <c r="L150" s="16"/>
+      <c r="M150" s="16"/>
+      <c r="N150" s="16"/>
+      <c r="O150" s="39"/>
+      <c r="P150" s="39"/>
+      <c r="Q150" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="R150" s="42">
+        <f>SUM(R117:R149)</f>
+        <v>8</v>
+      </c>
+      <c r="S150" s="39"/>
+      <c r="T150" s="39"/>
+      <c r="U150" s="39"/>
+      <c r="V150" s="39"/>
+      <c r="W150" s="111"/>
+    </row>
+    <row r="151" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="39"/>
+      <c r="B151" s="39"/>
+      <c r="C151" s="39"/>
+      <c r="D151" s="39"/>
+      <c r="E151" s="108"/>
+      <c r="F151" s="39"/>
+      <c r="G151" s="39"/>
+      <c r="H151" s="39"/>
+      <c r="I151" s="39"/>
+      <c r="J151" s="16"/>
+      <c r="K151" s="16"/>
+      <c r="L151" s="16"/>
+      <c r="M151" s="16"/>
+      <c r="N151" s="16"/>
+      <c r="O151" s="39"/>
+      <c r="P151" s="39"/>
+      <c r="Q151" s="39"/>
+      <c r="R151" s="39"/>
+      <c r="S151" s="39"/>
+      <c r="T151" s="39"/>
+      <c r="U151" s="39"/>
+      <c r="V151" s="39"/>
+      <c r="W151" s="111"/>
+    </row>
+    <row r="152" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="39"/>
+      <c r="B152" s="39"/>
+      <c r="C152" s="39"/>
+      <c r="D152" s="39"/>
+      <c r="E152" s="108"/>
+      <c r="F152" s="39"/>
+      <c r="G152" s="39"/>
+      <c r="H152" s="39"/>
+      <c r="I152" s="39"/>
+      <c r="J152" s="16"/>
+      <c r="K152" s="16"/>
+      <c r="L152" s="16"/>
+      <c r="M152" s="16"/>
+      <c r="N152" s="16"/>
+      <c r="O152" s="39"/>
+      <c r="P152" s="39"/>
+      <c r="Q152" s="39"/>
+      <c r="R152" s="39"/>
+      <c r="S152" s="39"/>
+      <c r="T152" s="39"/>
+      <c r="U152" s="39"/>
+      <c r="V152" s="39"/>
+      <c r="W152" s="111"/>
+    </row>
+    <row r="153" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="39"/>
+      <c r="B153" s="39"/>
+      <c r="C153" s="39"/>
+      <c r="D153" s="39"/>
+      <c r="E153" s="108"/>
+      <c r="F153" s="39"/>
+      <c r="G153" s="39"/>
+      <c r="H153" s="39"/>
+      <c r="I153" s="39"/>
+      <c r="J153" s="16"/>
+      <c r="K153" s="16"/>
+      <c r="L153" s="16"/>
+      <c r="M153" s="16"/>
+      <c r="N153" s="16"/>
+      <c r="O153" s="39"/>
+      <c r="P153" s="39"/>
+      <c r="Q153" s="39"/>
+      <c r="R153" s="39"/>
+      <c r="S153" s="39"/>
+      <c r="T153" s="39"/>
+      <c r="U153" s="39"/>
+      <c r="V153" s="39"/>
+      <c r="W153" s="111"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="P41:R41"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="P36:R36"/>
+    <mergeCell ref="P37:R37"/>
+    <mergeCell ref="P38:R38"/>
+    <mergeCell ref="P39:R39"/>
+    <mergeCell ref="P40:R40"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="M12:N12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="Q22:Q23" formulaRange="1"/>
   </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/spreadsheets/Games.xlsx
+++ b/spreadsheets/Games.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\ucer0.github.io\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8879D598-26AD-4B66-9BCA-B7D185243A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D83101-FF7B-46E0-B70A-50D9B998E9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30780" yWindow="315" windowWidth="24390" windowHeight="11685" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2019" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="680">
   <si>
     <t>Nier: Automata</t>
   </si>
@@ -573,9 +573,6 @@
     <t>MAR</t>
   </si>
   <si>
-    <t>ONLINE</t>
-  </si>
-  <si>
     <t>SOLO</t>
   </si>
   <si>
@@ -2729,16 +2726,64 @@
     <t>10-feb.</t>
   </si>
   <si>
-    <t>TtA (56h 00m)</t>
-  </si>
-  <si>
     <t>Devil Summoner: Soul Hackers</t>
   </si>
   <si>
-    <t>Tiling Forest - Tiling Town Demo -</t>
-  </si>
-  <si>
     <t>28-feb.</t>
+  </si>
+  <si>
+    <t>1-mar.</t>
+  </si>
+  <si>
+    <t>Tiling Forest -Tiling Town Demo-</t>
+  </si>
+  <si>
+    <t>TtA (56h 00m), SH (11h 12m), TF (1h 28m)</t>
+  </si>
+  <si>
+    <t>25-mar.</t>
+  </si>
+  <si>
+    <t>Slay the Spire 2</t>
+  </si>
+  <si>
+    <t>Z.A.T.O. // I Love the World and Everything In It</t>
+  </si>
+  <si>
+    <t>30-mar.</t>
+  </si>
+  <si>
+    <t>Angeline Era</t>
+  </si>
+  <si>
+    <t>TF (4h 14m), SH (35h 10m) , AE (6h 00m)</t>
+  </si>
+  <si>
+    <t>Cookie's Bustle</t>
+  </si>
+  <si>
+    <t>16-abr.</t>
+  </si>
+  <si>
+    <t>19-abr.</t>
+  </si>
+  <si>
+    <t>King Exit</t>
+  </si>
+  <si>
+    <t>AE (19h 54m), KE (22h 38m)</t>
+  </si>
+  <si>
+    <t>ONGOING</t>
+  </si>
+  <si>
+    <t>KE (6h 58m)</t>
+  </si>
+  <si>
+    <t>Demons Roots</t>
+  </si>
+  <si>
+    <t>5-may.</t>
   </si>
 </sst>
 </file>
@@ -3675,14 +3720,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4782,7 +4827,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>ONLINE</c:v>
+                  <c:v>ONGOING</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5778,7 +5823,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>ONLINE</c:v>
+                  <c:v>ONGOING</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6366,7 +6411,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -6378,7 +6423,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -6390,7 +6435,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -6444,7 +6489,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0</c:v>
@@ -6726,6 +6771,15 @@
                 <c:pt idx="1">
                   <c:v>3.5451388888888893</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.1541666666666668</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.0465277777777775</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.2902777777777778</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6744,7 +6798,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>ONLINE</c:v>
+                  <c:v>ONGOING</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6817,6 +6871,12 @@
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.17986111111111111</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.2041666666666666</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.9472222222222222</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8097,7 +8157,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>ONLINE</c:v>
+                  <c:v>ONGOING</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9154,7 +9214,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>ONLINE</c:v>
+                  <c:v>ONGOING</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10138,7 +10198,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>ONLINE</c:v>
+                  <c:v>ONGOING</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -19811,7 +19871,7 @@
       <c r="D2" s="177"/>
       <c r="E2" s="67"/>
       <c r="F2" s="182" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G2" s="182"/>
       <c r="H2" s="182"/>
@@ -20004,7 +20064,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D8" s="9">
         <v>2017</v>
@@ -21496,7 +21556,7 @@
         <v>42</v>
       </c>
       <c r="K14" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L14" s="6"/>
       <c r="M14" s="39"/>
@@ -21520,7 +21580,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E15" s="11">
         <v>2019</v>
@@ -21539,7 +21599,7 @@
         <v>43</v>
       </c>
       <c r="K15" s="18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L15" s="6"/>
       <c r="M15" s="39"/>
@@ -21758,7 +21818,7 @@
         <v>18</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E21" s="9">
         <v>2018</v>
@@ -21797,7 +21857,7 @@
         <v>19</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E22" s="9">
         <v>2017</v>
@@ -21842,7 +21902,7 @@
         <v>20</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E23" s="9">
         <v>2018</v>
@@ -21977,7 +22037,7 @@
         <v>23</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E26" s="9">
         <v>2015</v>
@@ -22364,7 +22424,7 @@
       </c>
       <c r="P34" s="16"/>
       <c r="Q34" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R34" s="39"/>
       <c r="S34" s="39"/>
@@ -22469,7 +22529,7 @@
         <v>2020</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G37" s="19" t="s">
         <v>106</v>
@@ -25791,7 +25851,7 @@
         <v>77</v>
       </c>
       <c r="E2" s="86" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F2" s="86" t="s">
         <v>12</v>
@@ -25865,7 +25925,7 @@
         <v>2017</v>
       </c>
       <c r="E3" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F3" s="84">
         <v>44186</v>
@@ -25933,19 +25993,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D4" s="54">
         <v>2019</v>
       </c>
       <c r="E4" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F4" s="69" t="s">
+        <v>133</v>
+      </c>
+      <c r="G4" s="69" t="s">
         <v>134</v>
-      </c>
-      <c r="G4" s="69" t="s">
-        <v>135</v>
       </c>
       <c r="H4" s="60">
         <v>0.30138888888888887</v>
@@ -25953,7 +26013,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="190"/>
       <c r="K4" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L4" s="60">
         <v>1.9791666666666667</v>
@@ -26005,19 +26065,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="73" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D5" s="73">
         <v>2016</v>
       </c>
       <c r="E5" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F5" s="74">
         <v>44228</v>
       </c>
       <c r="G5" s="74" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H5" s="75">
         <v>0.2076388888888889</v>
@@ -26025,7 +26085,7 @@
       <c r="I5" s="6"/>
       <c r="J5" s="190"/>
       <c r="K5" s="73" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L5" s="75">
         <v>0.46180555555555558</v>
@@ -26077,19 +26137,19 @@
         <v>4</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D6" s="54">
         <v>2021</v>
       </c>
       <c r="E6" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G6" s="69" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H6" s="60">
         <v>1.2437499999999999</v>
@@ -26097,7 +26157,7 @@
       <c r="I6" s="6"/>
       <c r="J6" s="190"/>
       <c r="K6" s="54" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L6" s="60">
         <v>0.27777777777777779</v>
@@ -26149,19 +26209,19 @@
         <v>5</v>
       </c>
       <c r="C7" s="73" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D7" s="73">
         <v>2021</v>
       </c>
       <c r="E7" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F7" s="74" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G7" s="74" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H7" s="75">
         <v>0.27916666666666667</v>
@@ -26169,7 +26229,7 @@
       <c r="I7" s="6"/>
       <c r="J7" s="190"/>
       <c r="K7" s="73" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L7" s="75">
         <v>8.1944444444444445E-2</v>
@@ -26221,19 +26281,19 @@
         <v>6</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D8" s="54">
         <v>2011</v>
       </c>
       <c r="E8" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G8" s="69" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H8" s="60">
         <v>6.1111111111111116E-2</v>
@@ -26241,7 +26301,7 @@
       <c r="I8" s="6"/>
       <c r="J8" s="190"/>
       <c r="K8" s="54" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L8" s="60">
         <v>7.1527777777777787E-2</v>
@@ -26293,19 +26353,19 @@
         <v>7</v>
       </c>
       <c r="C9" s="73" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D9" s="73">
         <v>2020</v>
       </c>
       <c r="E9" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F9" s="74" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G9" s="74" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H9" s="75">
         <v>0.11180555555555556</v>
@@ -26315,7 +26375,7 @@
         <v>119</v>
       </c>
       <c r="K9" s="71" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L9" s="72">
         <v>0.17986111111111111</v>
@@ -26367,19 +26427,19 @@
         <v>8</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D10" s="54">
         <v>2021</v>
       </c>
       <c r="E10" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F10" s="69" t="s">
+        <v>158</v>
+      </c>
+      <c r="G10" s="69" t="s">
         <v>159</v>
-      </c>
-      <c r="G10" s="69" t="s">
-        <v>160</v>
       </c>
       <c r="H10" s="60">
         <v>0.19027777777777777</v>
@@ -26387,7 +26447,7 @@
       <c r="I10" s="6"/>
       <c r="J10" s="190"/>
       <c r="K10" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L10" s="60">
         <v>0.72569444444444453</v>
@@ -26439,19 +26499,19 @@
         <v>9</v>
       </c>
       <c r="C11" s="73" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D11" s="73">
         <v>2021</v>
       </c>
       <c r="E11" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F11" s="74" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G11" s="74" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H11" s="75">
         <v>3.3333333333333333E-2</v>
@@ -26459,7 +26519,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="190"/>
       <c r="K11" s="73" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L11" s="75">
         <v>0.32430555555555557</v>
@@ -26511,19 +26571,19 @@
         <v>10</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D12" s="54">
         <v>2021</v>
       </c>
       <c r="E12" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F12" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G12" s="69" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H12" s="60">
         <v>1.7097222222222221</v>
@@ -26531,7 +26591,7 @@
       <c r="I12" s="6"/>
       <c r="J12" s="190"/>
       <c r="K12" s="54" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L12" s="60">
         <v>2.2222222222222223E-2</v>
@@ -26583,19 +26643,19 @@
         <v>11</v>
       </c>
       <c r="C13" s="73" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D13" s="73">
         <v>2016</v>
       </c>
       <c r="E13" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F13" s="74" t="s">
+        <v>172</v>
+      </c>
+      <c r="G13" s="74" t="s">
         <v>173</v>
-      </c>
-      <c r="G13" s="74" t="s">
-        <v>174</v>
       </c>
       <c r="H13" s="75">
         <v>0.15972222222222224</v>
@@ -26603,7 +26663,7 @@
       <c r="I13" s="6"/>
       <c r="J13" s="190"/>
       <c r="K13" s="73" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L13" s="75">
         <v>5.9027777777777783E-2</v>
@@ -26655,19 +26715,19 @@
         <v>12</v>
       </c>
       <c r="C14" s="54" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D14" s="54">
         <v>2013</v>
       </c>
       <c r="E14" s="153" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F14" s="69" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G14" s="69" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H14" s="60">
         <v>0.14722222222222223</v>
@@ -26677,7 +26737,7 @@
         <v>120</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L14" s="59">
         <v>7.1527777777777787E-2</v>
@@ -26729,16 +26789,16 @@
         <v>13</v>
       </c>
       <c r="C15" s="73" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D15" s="73">
         <v>2007</v>
       </c>
       <c r="E15" s="152" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F15" s="74" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G15" s="74" t="s">
         <v>52</v>
@@ -26749,7 +26809,7 @@
       <c r="I15" s="6"/>
       <c r="J15" s="190"/>
       <c r="K15" s="73" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L15" s="75">
         <v>7.9166666666666663E-2</v>
@@ -26801,13 +26861,13 @@
         <v>14</v>
       </c>
       <c r="C16" s="54" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D16" s="54">
         <v>2013</v>
       </c>
       <c r="E16" s="153" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F16" s="69" t="s">
         <v>52</v>
@@ -26821,7 +26881,7 @@
       <c r="I16" s="6"/>
       <c r="J16" s="190"/>
       <c r="K16" s="54" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L16" s="60">
         <v>0.27013888888888887</v>
@@ -26873,16 +26933,16 @@
         <v>15</v>
       </c>
       <c r="C17" s="73" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D17" s="73">
         <v>2004</v>
       </c>
       <c r="E17" s="152" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F17" s="74" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G17" s="74" t="s">
         <v>13</v>
@@ -26893,7 +26953,7 @@
       <c r="I17" s="6"/>
       <c r="J17" s="190"/>
       <c r="K17" s="73" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L17" s="75">
         <v>6.8749999999999992E-2</v>
@@ -26945,19 +27005,19 @@
         <v>16</v>
       </c>
       <c r="C18" s="103" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D18" s="54">
         <v>2019</v>
       </c>
       <c r="E18" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F18" s="69" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G18" s="69" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H18" s="60">
         <v>0.24583333333333335</v>
@@ -26965,7 +27025,7 @@
       <c r="I18" s="6"/>
       <c r="J18" s="190"/>
       <c r="K18" s="54" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L18" s="60">
         <v>0.11041666666666666</v>
@@ -27017,19 +27077,19 @@
         <v>17</v>
       </c>
       <c r="C19" s="73" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D19" s="73">
         <v>2020</v>
       </c>
       <c r="E19" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F19" s="74" t="s">
+        <v>187</v>
+      </c>
+      <c r="G19" s="74" t="s">
         <v>188</v>
-      </c>
-      <c r="G19" s="74" t="s">
-        <v>189</v>
       </c>
       <c r="H19" s="75">
         <v>0.49513888888888885</v>
@@ -27037,7 +27097,7 @@
       <c r="I19" s="6"/>
       <c r="J19" s="191"/>
       <c r="K19" s="76" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L19" s="77">
         <v>0.11388888888888889</v>
@@ -27089,29 +27149,29 @@
         <v>18</v>
       </c>
       <c r="C20" s="54" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D20" s="54">
         <v>2018</v>
       </c>
       <c r="E20" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F20" s="69" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G20" s="69" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H20" s="60">
         <v>0.20972222222222223</v>
       </c>
       <c r="I20" s="6"/>
       <c r="J20" s="189" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L20" s="59">
         <v>6.5277777777777782E-2</v>
@@ -27163,19 +27223,19 @@
         <v>19</v>
       </c>
       <c r="C21" s="73" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D21" s="73">
         <v>2015</v>
       </c>
       <c r="E21" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F21" s="74" t="s">
+        <v>190</v>
+      </c>
+      <c r="G21" s="74" t="s">
         <v>191</v>
-      </c>
-      <c r="G21" s="74" t="s">
-        <v>192</v>
       </c>
       <c r="H21" s="75">
         <v>0.25486111111111109</v>
@@ -27183,7 +27243,7 @@
       <c r="I21" s="6"/>
       <c r="J21" s="191"/>
       <c r="K21" s="76" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L21" s="77">
         <v>0.18194444444444444</v>
@@ -27193,13 +27253,13 @@
         <v>31</v>
       </c>
       <c r="O21" s="91" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P21" s="91" t="s">
-        <v>121</v>
+        <v>676</v>
       </c>
       <c r="Q21" s="92" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R21" s="39"/>
       <c r="S21" s="88" t="s">
@@ -27245,29 +27305,29 @@
         <v>20</v>
       </c>
       <c r="C22" s="54" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D22" s="54">
         <v>2018</v>
       </c>
       <c r="E22" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F22" s="69" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G22" s="69" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H22" s="60">
         <v>0.26666666666666666</v>
       </c>
       <c r="I22" s="6"/>
       <c r="J22" s="190" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K22" s="54" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L22" s="60">
         <v>2.2916666666666669E-2</v>
@@ -27289,7 +27349,7 @@
       </c>
       <c r="R22" s="39"/>
       <c r="S22" s="104" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="T22" s="39"/>
       <c r="U22" s="39"/>
@@ -27331,19 +27391,19 @@
         <v>21</v>
       </c>
       <c r="C23" s="73" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D23" s="73">
         <v>1997</v>
       </c>
       <c r="E23" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F23" s="74" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G23" s="74" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H23" s="75">
         <v>0.26944444444444443</v>
@@ -27351,7 +27411,7 @@
       <c r="I23" s="6"/>
       <c r="J23" s="190"/>
       <c r="K23" s="80" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L23" s="82">
         <v>5.2777777777777778E-2</v>
@@ -27415,16 +27475,16 @@
         <v>22</v>
       </c>
       <c r="C24" s="54" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D24" s="54">
         <v>2019</v>
       </c>
       <c r="E24" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F24" s="69" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G24" s="69" t="s">
         <v>75</v>
@@ -27435,7 +27495,7 @@
       <c r="I24" s="39"/>
       <c r="J24" s="190"/>
       <c r="K24" s="54" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L24" s="60">
         <v>7.2222222222222229E-2</v>
@@ -27457,7 +27517,7 @@
       </c>
       <c r="R24" s="39"/>
       <c r="S24" s="99" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="T24" s="39"/>
       <c r="U24" s="39"/>
@@ -27499,19 +27559,19 @@
         <v>23</v>
       </c>
       <c r="C25" s="73" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D25" s="73">
         <v>2020</v>
       </c>
       <c r="E25" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F25" s="74" t="s">
+        <v>217</v>
+      </c>
+      <c r="G25" s="74" t="s">
         <v>218</v>
-      </c>
-      <c r="G25" s="74" t="s">
-        <v>219</v>
       </c>
       <c r="H25" s="75">
         <v>0.32847222222222222</v>
@@ -27519,7 +27579,7 @@
       <c r="I25" s="39"/>
       <c r="J25" s="190"/>
       <c r="K25" s="73" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L25" s="75">
         <v>0.23472222222222219</v>
@@ -27541,7 +27601,7 @@
       </c>
       <c r="R25" s="39"/>
       <c r="S25" s="98" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="T25" s="39"/>
       <c r="U25" s="39"/>
@@ -27583,19 +27643,19 @@
         <v>24</v>
       </c>
       <c r="C26" s="54" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D26" s="54">
         <v>2019</v>
       </c>
       <c r="E26" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F26" s="69" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G26" s="69" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H26" s="60">
         <v>0.67013888888888884</v>
@@ -27603,7 +27663,7 @@
       <c r="I26" s="39"/>
       <c r="J26" s="191"/>
       <c r="K26" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L26" s="87">
         <v>6.3888888888888884E-2</v>
@@ -27667,16 +27727,16 @@
         <v>25</v>
       </c>
       <c r="C27" s="73" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D27" s="73">
         <v>2018</v>
       </c>
       <c r="E27" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F27" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G27" s="74">
         <v>44456</v>
@@ -27686,10 +27746,10 @@
       </c>
       <c r="I27" s="39"/>
       <c r="J27" s="189" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K27" s="73" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L27" s="75">
         <v>0.59166666666666667</v>
@@ -27711,7 +27771,7 @@
       </c>
       <c r="R27" s="39"/>
       <c r="S27" s="98" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="T27" s="39"/>
       <c r="U27" s="39"/>
@@ -27753,19 +27813,19 @@
         <v>26</v>
       </c>
       <c r="C28" s="54" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D28" s="54">
         <v>2021</v>
       </c>
       <c r="E28" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F28" s="69" t="s">
+        <v>224</v>
+      </c>
+      <c r="G28" s="69" t="s">
         <v>225</v>
-      </c>
-      <c r="G28" s="69" t="s">
-        <v>226</v>
       </c>
       <c r="H28" s="60">
         <v>0.22291666666666665</v>
@@ -27773,7 +27833,7 @@
       <c r="I28" s="39"/>
       <c r="J28" s="190"/>
       <c r="K28" s="101" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L28" s="83">
         <v>0.18958333333333333</v>
@@ -27795,7 +27855,7 @@
       </c>
       <c r="R28" s="39"/>
       <c r="S28" s="99" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="T28" s="39"/>
       <c r="U28" s="39"/>
@@ -27837,19 +27897,19 @@
         <v>27</v>
       </c>
       <c r="C29" s="73" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D29" s="73">
         <v>2019</v>
       </c>
       <c r="E29" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F29" s="74" t="s">
+        <v>227</v>
+      </c>
+      <c r="G29" s="74" t="s">
         <v>228</v>
-      </c>
-      <c r="G29" s="74" t="s">
-        <v>229</v>
       </c>
       <c r="H29" s="75">
         <v>0.13194444444444445</v>
@@ -27879,7 +27939,7 @@
       </c>
       <c r="R29" s="39"/>
       <c r="S29" s="98" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T29" s="39"/>
       <c r="U29" s="39"/>
@@ -27921,16 +27981,16 @@
         <v>28</v>
       </c>
       <c r="C30" s="54" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D30" s="54">
         <v>2008</v>
       </c>
       <c r="E30" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F30" s="69" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G30" s="69" t="s">
         <v>13</v>
@@ -27941,7 +28001,7 @@
       <c r="I30" s="39"/>
       <c r="J30" s="190"/>
       <c r="K30" s="101" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L30" s="83">
         <v>5.486111111111111E-2</v>
@@ -27963,7 +28023,7 @@
       </c>
       <c r="R30" s="39"/>
       <c r="S30" s="99" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="T30" s="39"/>
       <c r="U30" s="39"/>
@@ -28005,19 +28065,19 @@
         <v>29</v>
       </c>
       <c r="C31" s="73" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D31" s="73">
         <v>2021</v>
       </c>
       <c r="E31" s="152" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F31" s="74" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G31" s="74" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H31" s="75">
         <v>0.43888888888888888</v>
@@ -28025,7 +28085,7 @@
       <c r="I31" s="39"/>
       <c r="J31" s="191"/>
       <c r="K31" s="73" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L31" s="75">
         <v>0.55208333333333337</v>
@@ -28047,7 +28107,7 @@
       </c>
       <c r="R31" s="39"/>
       <c r="S31" s="98" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="T31" s="39"/>
       <c r="U31" s="39"/>
@@ -28089,29 +28149,29 @@
         <v>30</v>
       </c>
       <c r="C32" s="54" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D32" s="54">
         <v>1995</v>
       </c>
       <c r="E32" s="153" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F32" s="69" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G32" s="69" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H32" s="60">
         <v>0.42083333333333334</v>
       </c>
       <c r="I32" s="39"/>
       <c r="J32" s="189" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K32" s="107" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L32" s="106">
         <v>0.17569444444444446</v>
@@ -28133,7 +28193,7 @@
       </c>
       <c r="R32" s="39"/>
       <c r="S32" s="99" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="T32" s="39"/>
       <c r="U32" s="39"/>
@@ -28175,19 +28235,19 @@
         <v>31</v>
       </c>
       <c r="C33" s="73" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D33" s="73">
         <v>2021</v>
       </c>
       <c r="E33" s="152" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F33" s="74" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G33" s="74" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H33" s="75">
         <v>2.7097222222222221</v>
@@ -28195,7 +28255,7 @@
       <c r="I33" s="39"/>
       <c r="J33" s="190"/>
       <c r="K33" s="73" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L33" s="75">
         <v>0.87083333333333324</v>
@@ -28216,10 +28276,10 @@
         <v>5.4847222222222216</v>
       </c>
       <c r="R33" s="39" t="s">
+        <v>255</v>
+      </c>
+      <c r="S33" s="128" t="s">
         <v>256</v>
-      </c>
-      <c r="S33" s="128" t="s">
-        <v>257</v>
       </c>
       <c r="T33" s="39"/>
       <c r="U33" s="39"/>
@@ -28261,16 +28321,16 @@
         <v>32</v>
       </c>
       <c r="C34" s="54" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D34" s="54">
         <v>2021</v>
       </c>
       <c r="E34" s="153" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F34" s="69" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G34" s="69" t="s">
         <v>13</v>
@@ -28281,7 +28341,7 @@
       <c r="I34" s="39"/>
       <c r="J34" s="190"/>
       <c r="K34" s="54" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L34" s="83">
         <v>4.9999999999999996E-2</v>
@@ -28344,19 +28404,19 @@
         <v>33</v>
       </c>
       <c r="C35" s="73" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D35" s="73">
         <v>2019</v>
       </c>
       <c r="E35" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F35" s="74" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G35" s="74" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H35" s="75">
         <v>0.11041666666666666</v>
@@ -28364,7 +28424,7 @@
       <c r="I35" s="39"/>
       <c r="J35" s="190"/>
       <c r="K35" s="80" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L35" s="75">
         <v>0.23750000000000002</v>
@@ -28416,19 +28476,19 @@
         <v>34</v>
       </c>
       <c r="C36" s="54" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D36" s="54">
         <v>2021</v>
       </c>
       <c r="E36" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F36" s="69" t="s">
+        <v>250</v>
+      </c>
+      <c r="G36" s="69" t="s">
         <v>251</v>
-      </c>
-      <c r="G36" s="69" t="s">
-        <v>252</v>
       </c>
       <c r="H36" s="60">
         <v>0.37083333333333335</v>
@@ -28436,15 +28496,15 @@
       <c r="I36" s="39"/>
       <c r="J36" s="190"/>
       <c r="K36" s="54" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L36" s="60">
         <v>4.5138888888888888E-2</v>
       </c>
       <c r="M36" s="39"/>
-      <c r="N36" s="172"/>
-      <c r="O36" s="172"/>
-      <c r="P36" s="172"/>
+      <c r="N36" s="170"/>
+      <c r="O36" s="170"/>
+      <c r="P36" s="170"/>
       <c r="Q36" s="111"/>
       <c r="R36" s="16"/>
       <c r="S36" s="16"/>
@@ -28488,19 +28548,19 @@
         <v>35</v>
       </c>
       <c r="C37" s="73" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D37" s="73">
         <v>2019</v>
       </c>
       <c r="E37" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F37" s="74" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G37" s="74" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H37" s="75">
         <v>0.80694444444444446</v>
@@ -28508,15 +28568,15 @@
       <c r="I37" s="39"/>
       <c r="J37" s="190"/>
       <c r="K37" s="80" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L37" s="75">
         <v>7.7777777777777779E-2</v>
       </c>
       <c r="M37" s="39"/>
-      <c r="N37" s="172"/>
-      <c r="O37" s="172"/>
-      <c r="P37" s="172"/>
+      <c r="N37" s="170"/>
+      <c r="O37" s="170"/>
+      <c r="P37" s="170"/>
       <c r="Q37" s="111"/>
       <c r="R37" s="16"/>
       <c r="S37" s="16"/>
@@ -28560,19 +28620,19 @@
         <v>36</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D38" s="11">
         <v>2021</v>
       </c>
       <c r="E38" s="154" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F38" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="G38" s="21" t="s">
         <v>254</v>
-      </c>
-      <c r="G38" s="21" t="s">
-        <v>255</v>
       </c>
       <c r="H38" s="102">
         <v>9.1666666666666674E-2</v>
@@ -28580,15 +28640,15 @@
       <c r="I38" s="39"/>
       <c r="J38" s="191"/>
       <c r="K38" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L38" s="102">
         <v>9.1666666666666674E-2</v>
       </c>
       <c r="M38" s="39"/>
-      <c r="N38" s="172"/>
-      <c r="O38" s="172"/>
-      <c r="P38" s="172"/>
+      <c r="N38" s="170"/>
+      <c r="O38" s="170"/>
+      <c r="P38" s="170"/>
       <c r="Q38" s="111"/>
       <c r="R38" s="16"/>
       <c r="S38" s="16"/>
@@ -28637,18 +28697,18 @@
       <c r="H39" s="61"/>
       <c r="I39" s="39"/>
       <c r="J39" s="189" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K39" s="116" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L39" s="72">
         <v>0.14583333333333334</v>
       </c>
       <c r="M39" s="39"/>
-      <c r="N39" s="172"/>
-      <c r="O39" s="172"/>
-      <c r="P39" s="172"/>
+      <c r="N39" s="170"/>
+      <c r="O39" s="170"/>
+      <c r="P39" s="170"/>
       <c r="Q39" s="124"/>
       <c r="R39" s="16"/>
       <c r="S39" s="16"/>
@@ -28698,15 +28758,15 @@
       <c r="I40" s="39"/>
       <c r="J40" s="190"/>
       <c r="K40" s="113" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L40" s="83">
         <v>0.3666666666666667</v>
       </c>
       <c r="M40" s="39"/>
-      <c r="N40" s="172"/>
-      <c r="O40" s="172"/>
-      <c r="P40" s="172"/>
+      <c r="N40" s="170"/>
+      <c r="O40" s="170"/>
+      <c r="P40" s="170"/>
       <c r="Q40" s="124"/>
       <c r="R40" s="16"/>
       <c r="S40" s="16"/>
@@ -28755,15 +28815,15 @@
       <c r="I41" s="39"/>
       <c r="J41" s="190"/>
       <c r="K41" s="112" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L41" s="75">
         <v>0.53333333333333333</v>
       </c>
       <c r="M41" s="39"/>
-      <c r="N41" s="172"/>
-      <c r="O41" s="172"/>
-      <c r="P41" s="172"/>
+      <c r="N41" s="170"/>
+      <c r="O41" s="170"/>
+      <c r="P41" s="170"/>
       <c r="Q41" s="124"/>
       <c r="R41" s="16"/>
       <c r="S41" s="16"/>
@@ -28813,7 +28873,7 @@
       <c r="I42" s="39"/>
       <c r="J42" s="190"/>
       <c r="K42" s="114" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L42" s="60">
         <v>0.11388888888888889</v>
@@ -28871,7 +28931,7 @@
       <c r="I43" s="39"/>
       <c r="J43" s="190"/>
       <c r="K43" s="112" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L43" s="75">
         <v>0.22083333333333333</v>
@@ -28929,7 +28989,7 @@
       <c r="I44" s="39"/>
       <c r="J44" s="190"/>
       <c r="K44" s="113" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L44" s="83">
         <v>0.87916666666666676</v>
@@ -28987,7 +29047,7 @@
       <c r="I45" s="39"/>
       <c r="J45" s="191"/>
       <c r="K45" s="115" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L45" s="110">
         <v>4.4444444444444446E-2</v>
@@ -29044,10 +29104,10 @@
       <c r="H46" s="62"/>
       <c r="I46" s="39"/>
       <c r="J46" s="186" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K46" s="119" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L46" s="106">
         <v>4.9999999999999996E-2</v>
@@ -29105,7 +29165,7 @@
       <c r="I47" s="39"/>
       <c r="J47" s="187"/>
       <c r="K47" s="80" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L47" s="82">
         <v>0.1875</v>
@@ -29163,7 +29223,7 @@
       <c r="I48" s="39"/>
       <c r="J48" s="187"/>
       <c r="K48" s="101" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L48" s="83">
         <v>0.3923611111111111</v>
@@ -29221,7 +29281,7 @@
       <c r="I49" s="39"/>
       <c r="J49" s="188"/>
       <c r="K49" s="120" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L49" s="110">
         <v>0.17222222222222225</v>
@@ -29278,10 +29338,10 @@
       <c r="H50" s="39"/>
       <c r="I50" s="39"/>
       <c r="J50" s="186" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K50" s="121" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L50" s="106">
         <v>8.5416666666666655E-2</v>
@@ -29339,7 +29399,7 @@
       <c r="I51" s="39"/>
       <c r="J51" s="187"/>
       <c r="K51" s="122" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L51" s="82">
         <v>0.16666666666666666</v>
@@ -29397,7 +29457,7 @@
       <c r="I52" s="39"/>
       <c r="J52" s="187"/>
       <c r="K52" s="114" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L52" s="83">
         <v>0.75</v>
@@ -29455,7 +29515,7 @@
       <c r="I53" s="39"/>
       <c r="J53" s="188"/>
       <c r="K53" s="115" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L53" s="110">
         <v>6.5277777777777782E-2</v>
@@ -29512,10 +29572,10 @@
       <c r="H54" s="39"/>
       <c r="I54" s="39"/>
       <c r="J54" s="186" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K54" s="121" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L54" s="106">
         <v>0.20416666666666669</v>
@@ -29573,7 +29633,7 @@
       <c r="I55" s="39"/>
       <c r="J55" s="187"/>
       <c r="K55" s="122" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L55" s="82">
         <v>0.25</v>
@@ -29689,7 +29749,7 @@
       <c r="I57" s="39"/>
       <c r="J57" s="188"/>
       <c r="K57" s="115" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L57" s="110">
         <v>3.8194444444444441E-2</v>
@@ -29746,10 +29806,10 @@
       <c r="H58" s="39"/>
       <c r="I58" s="39"/>
       <c r="J58" s="186" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K58" s="121" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L58" s="106">
         <v>0.25486111111111109</v>
@@ -29807,7 +29867,7 @@
       <c r="I59" s="39"/>
       <c r="J59" s="187"/>
       <c r="K59" s="122" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L59" s="82">
         <v>0.11944444444444445</v>
@@ -29865,7 +29925,7 @@
       <c r="I60" s="39"/>
       <c r="J60" s="187"/>
       <c r="K60" s="114" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L60" s="83">
         <v>0.19097222222222221</v>
@@ -29923,7 +29983,7 @@
       <c r="I61" s="39"/>
       <c r="J61" s="187"/>
       <c r="K61" s="122" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L61" s="82">
         <v>0.18611111111111112</v>
@@ -30039,7 +30099,7 @@
       <c r="I63" s="39"/>
       <c r="J63" s="188"/>
       <c r="K63" s="115" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L63" s="110">
         <v>3.888888888888889E-2</v>
@@ -32905,7 +32965,7 @@
       <c r="I116" s="39"/>
       <c r="J116" s="117"/>
       <c r="K116" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L116" s="111"/>
       <c r="M116" s="39"/>
@@ -32961,7 +33021,7 @@
       <c r="I117" s="39"/>
       <c r="J117" s="117"/>
       <c r="K117" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L117" s="111"/>
       <c r="M117" s="39"/>
@@ -33132,7 +33192,7 @@
         <v>77</v>
       </c>
       <c r="P120" s="56" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q120" s="39"/>
       <c r="R120" s="39"/>
@@ -34009,7 +34069,7 @@
       <c r="I135" s="39"/>
       <c r="J135" s="117"/>
       <c r="K135" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L135" s="16"/>
       <c r="M135" s="39"/>
@@ -34070,7 +34130,7 @@
       <c r="I136" s="39"/>
       <c r="J136" s="117"/>
       <c r="K136" s="16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L136" s="16"/>
       <c r="M136" s="39"/>
@@ -34784,7 +34844,7 @@
       <c r="M148" s="39"/>
       <c r="N148" s="39"/>
       <c r="O148" s="41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P148" s="42">
         <f>SUM(P121:P147)</f>
@@ -35786,6 +35846,12 @@
     <sortCondition ref="K33"/>
   </sortState>
   <mergeCells count="18">
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="N39:P39"/>
     <mergeCell ref="J58:J63"/>
     <mergeCell ref="J54:J57"/>
     <mergeCell ref="J50:J53"/>
@@ -35798,12 +35864,6 @@
     <mergeCell ref="J32:J38"/>
     <mergeCell ref="J27:J31"/>
     <mergeCell ref="J14:J19"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="N39:P39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -35878,7 +35938,7 @@
         <v>77</v>
       </c>
       <c r="E2" s="86" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F2" s="86" t="s">
         <v>12</v>
@@ -35890,15 +35950,15 @@
         <v>20</v>
       </c>
       <c r="I2" s="6"/>
-      <c r="J2" s="170" t="s">
-        <v>284</v>
+      <c r="J2" s="171" t="s">
+        <v>283</v>
       </c>
       <c r="K2" s="192"/>
       <c r="L2" s="136"/>
       <c r="M2" s="192" t="s">
-        <v>285</v>
-      </c>
-      <c r="N2" s="171"/>
+        <v>284</v>
+      </c>
+      <c r="N2" s="172"/>
       <c r="O2" s="39"/>
       <c r="P2" s="39"/>
       <c r="Q2" s="39"/>
@@ -35915,26 +35975,26 @@
         <v>1</v>
       </c>
       <c r="C3" s="73" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D3" s="73">
         <v>2019</v>
       </c>
       <c r="E3" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F3" s="74" t="s">
+        <v>258</v>
+      </c>
+      <c r="G3" s="74" t="s">
         <v>259</v>
-      </c>
-      <c r="G3" s="74" t="s">
-        <v>260</v>
       </c>
       <c r="H3" s="75">
         <v>0.80694444444444446</v>
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="122" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K3" s="132">
         <v>4.5833333333333337E-2</v>
@@ -35962,33 +36022,33 @@
         <v>2</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D4" s="54">
         <v>2020</v>
       </c>
       <c r="E4" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F4" s="69" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G4" s="69" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H4" s="60">
         <v>0.17083333333333331</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="113" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K4" s="133">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="L4" s="137"/>
       <c r="M4" s="101" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N4" s="60">
         <v>5.9722222222222225E-2</v>
@@ -36009,19 +36069,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="73" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D5" s="73">
         <v>2020</v>
       </c>
       <c r="E5" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F5" s="74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G5" s="74" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H5" s="75">
         <v>0.33749999999999997</v>
@@ -36035,7 +36095,7 @@
       </c>
       <c r="L5" s="137"/>
       <c r="M5" s="73" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N5" s="75">
         <v>0.19791666666666666</v>
@@ -36056,33 +36116,33 @@
         <v>4</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D6" s="54">
         <v>2012</v>
       </c>
       <c r="E6" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G6" s="69" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H6" s="60">
         <v>0.15</v>
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="113" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K6" s="133">
         <v>6.5972222222222224E-2</v>
       </c>
       <c r="L6" s="137"/>
       <c r="M6" s="54" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N6" s="60">
         <v>5.9027777777777783E-2</v>
@@ -36103,26 +36163,26 @@
         <v>5</v>
       </c>
       <c r="C7" s="73" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D7" s="73">
         <v>2021</v>
       </c>
       <c r="E7" s="152" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F7" s="74" t="s">
+        <v>270</v>
+      </c>
+      <c r="G7" s="74" t="s">
         <v>271</v>
-      </c>
-      <c r="G7" s="74" t="s">
-        <v>272</v>
       </c>
       <c r="H7" s="75">
         <v>2.7097222222222221</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="135" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K7" s="134">
         <v>0.1763888888888889</v>
@@ -36146,19 +36206,19 @@
         <v>6</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D8" s="54">
         <v>2022</v>
       </c>
       <c r="E8" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F8" s="69" t="s">
+        <v>275</v>
+      </c>
+      <c r="G8" s="69" t="s">
         <v>276</v>
-      </c>
-      <c r="G8" s="69" t="s">
-        <v>277</v>
       </c>
       <c r="H8" s="60">
         <v>0.32083333333333336</v>
@@ -36180,33 +36240,33 @@
         <v>7</v>
       </c>
       <c r="C9" s="73" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D9" s="73">
         <v>2019</v>
       </c>
       <c r="E9" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F9" s="74" t="s">
+        <v>278</v>
+      </c>
+      <c r="G9" s="74" t="s">
         <v>279</v>
-      </c>
-      <c r="G9" s="74" t="s">
-        <v>280</v>
       </c>
       <c r="H9" s="75">
         <v>0.20416666666666669</v>
       </c>
       <c r="I9" s="6"/>
-      <c r="J9" s="170" t="s">
-        <v>286</v>
+      <c r="J9" s="171" t="s">
+        <v>285</v>
       </c>
       <c r="K9" s="192"/>
       <c r="L9" s="136"/>
       <c r="M9" s="192" t="s">
-        <v>287</v>
-      </c>
-      <c r="N9" s="171"/>
+        <v>286</v>
+      </c>
+      <c r="N9" s="172"/>
       <c r="O9" s="39"/>
       <c r="P9" s="39"/>
       <c r="Q9" s="39"/>
@@ -36223,16 +36283,16 @@
         <v>8</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D10" s="54">
         <v>2000</v>
       </c>
       <c r="E10" s="153" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G10" s="69" t="s">
         <v>13</v>
@@ -36270,19 +36330,19 @@
         <v>9</v>
       </c>
       <c r="C11" s="73" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D11" s="73">
         <v>2019</v>
       </c>
       <c r="E11" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F11" s="74" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G11" s="74" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H11" s="75">
         <v>0.20833333333333334</v>
@@ -36292,7 +36352,7 @@
       <c r="K11" s="133"/>
       <c r="L11" s="137"/>
       <c r="M11" s="101" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="N11" s="60">
         <v>5.0694444444444452E-2</v>
@@ -36313,19 +36373,19 @@
         <v>10</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D12" s="54">
         <v>2019</v>
       </c>
       <c r="E12" s="153" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F12" s="69" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G12" s="69" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H12" s="60">
         <v>1.6291666666666667</v>
@@ -36335,7 +36395,7 @@
       <c r="K12" s="132"/>
       <c r="L12" s="137"/>
       <c r="M12" s="73" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N12" s="75">
         <v>4.8611111111111112E-2</v>
@@ -36356,19 +36416,19 @@
         <v>11</v>
       </c>
       <c r="C13" s="73" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D13" s="73">
         <v>2022</v>
       </c>
       <c r="E13" s="152" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F13" s="74" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G13" s="74" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H13" s="75">
         <v>0.8618055555555556</v>
@@ -36395,33 +36455,33 @@
         <v>12</v>
       </c>
       <c r="C14" s="54" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D14" s="54">
         <v>2011</v>
       </c>
       <c r="E14" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F14" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G14" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H14" s="60">
         <v>0.15208333333333332</v>
       </c>
       <c r="I14" s="6"/>
-      <c r="J14" s="170" t="s">
+      <c r="J14" s="171" t="s">
+        <v>287</v>
+      </c>
+      <c r="K14" s="172"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="171" t="s">
         <v>288</v>
       </c>
-      <c r="K14" s="171"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="170" t="s">
-        <v>289</v>
-      </c>
-      <c r="N14" s="171"/>
+      <c r="N14" s="172"/>
       <c r="O14" s="39"/>
       <c r="P14" s="39"/>
       <c r="Q14" s="39"/>
@@ -36438,16 +36498,16 @@
         <v>13</v>
       </c>
       <c r="C15" s="73" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D15" s="73">
         <v>1999</v>
       </c>
       <c r="E15" s="152" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F15" s="74" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G15" s="74" t="s">
         <v>102</v>
@@ -36464,7 +36524,7 @@
       </c>
       <c r="L15" s="137"/>
       <c r="M15" s="131" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N15" s="72">
         <v>0.66319444444444442</v>
@@ -36485,33 +36545,33 @@
         <v>14</v>
       </c>
       <c r="C16" s="54" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D16" s="54">
         <v>2022</v>
       </c>
       <c r="E16" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F16" s="69" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G16" s="69" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H16" s="60">
         <v>7.013888888888889E-2</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="113" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K16" s="133">
         <v>5.8333333333333327E-2</v>
       </c>
       <c r="L16" s="137"/>
       <c r="M16" s="101" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N16" s="60">
         <v>0.3520833333333333</v>
@@ -36532,13 +36592,13 @@
         <v>15</v>
       </c>
       <c r="C17" s="73" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D17" s="73">
         <v>2019</v>
       </c>
       <c r="E17" s="152" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F17" s="74" t="s">
         <v>102</v>
@@ -36551,14 +36611,14 @@
       </c>
       <c r="I17" s="6"/>
       <c r="J17" s="112" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K17" s="132">
         <v>0.35138888888888892</v>
       </c>
       <c r="L17" s="137"/>
       <c r="M17" s="73" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N17" s="75">
         <v>7.6388888888888895E-2</v>
@@ -36579,33 +36639,33 @@
         <v>16</v>
       </c>
       <c r="C18" s="54" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D18" s="54">
         <v>2022</v>
       </c>
       <c r="E18" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F18" s="69" t="s">
         <v>51</v>
       </c>
       <c r="G18" s="69" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H18" s="60">
         <v>0.38819444444444445</v>
       </c>
       <c r="I18" s="6"/>
       <c r="J18" s="113" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K18" s="133">
         <v>4.5138888888888888E-2</v>
       </c>
       <c r="L18" s="137"/>
       <c r="M18" s="54" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N18" s="60">
         <v>0.59791666666666665</v>
@@ -36626,16 +36686,16 @@
         <v>17</v>
       </c>
       <c r="C19" s="73" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D19" s="73">
         <v>2022</v>
       </c>
       <c r="E19" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F19" s="74" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G19" s="74" t="s">
         <v>13</v>
@@ -36645,14 +36705,14 @@
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="135" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K19" s="134">
         <v>0.12361111111111112</v>
       </c>
       <c r="L19" s="137"/>
       <c r="M19" s="134" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N19" s="77">
         <v>0.11944444444444445</v>
@@ -36673,19 +36733,19 @@
         <v>18</v>
       </c>
       <c r="C20" s="54" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D20" s="54">
         <v>2003</v>
       </c>
       <c r="E20" s="153" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F20" s="69" t="s">
         <v>54</v>
       </c>
       <c r="G20" s="69" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H20" s="60">
         <v>0.28472222222222221</v>
@@ -36707,45 +36767,45 @@
         <v>19</v>
       </c>
       <c r="C21" s="73" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D21" s="73">
         <v>2005</v>
       </c>
       <c r="E21" s="152" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F21" s="74" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G21" s="74" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H21" s="75">
         <v>0.35138888888888892</v>
       </c>
       <c r="I21" s="6"/>
-      <c r="J21" s="170" t="s">
+      <c r="J21" s="171" t="s">
+        <v>289</v>
+      </c>
+      <c r="K21" s="172"/>
+      <c r="L21" s="136"/>
+      <c r="M21" s="171" t="s">
         <v>290</v>
       </c>
-      <c r="K21" s="171"/>
-      <c r="L21" s="136"/>
-      <c r="M21" s="170" t="s">
-        <v>291</v>
-      </c>
-      <c r="N21" s="171"/>
+      <c r="N21" s="172"/>
       <c r="O21" s="39"/>
       <c r="P21" s="89" t="s">
         <v>31</v>
       </c>
       <c r="Q21" s="91" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R21" s="91" t="s">
-        <v>121</v>
+        <v>676</v>
       </c>
       <c r="S21" s="92" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="T21" s="39"/>
       <c r="U21" s="88" t="s">
@@ -36760,33 +36820,33 @@
         <v>20</v>
       </c>
       <c r="C22" s="54" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D22" s="54">
         <v>2011</v>
       </c>
       <c r="E22" s="153" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F22" s="69" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G22" s="69" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H22" s="60">
         <v>1.0513888888888889</v>
       </c>
       <c r="I22" s="6"/>
       <c r="J22" s="122" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K22" s="132">
         <v>6.3888888888888884E-2</v>
       </c>
       <c r="L22" s="137"/>
       <c r="M22" s="131" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N22" s="72">
         <v>0.4597222222222222</v>
@@ -36808,7 +36868,7 @@
       </c>
       <c r="T22" s="39"/>
       <c r="U22" s="104" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="V22" s="39"/>
       <c r="W22" s="39"/>
@@ -36819,16 +36879,16 @@
         <v>21</v>
       </c>
       <c r="C23" s="73" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D23" s="73">
         <v>1994</v>
       </c>
       <c r="E23" s="152" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F23" s="74" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G23" s="74" t="s">
         <v>13</v>
@@ -36838,7 +36898,7 @@
       </c>
       <c r="I23" s="6"/>
       <c r="J23" s="113" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K23" s="133">
         <v>0.3</v>
@@ -36867,7 +36927,7 @@
       </c>
       <c r="T23" s="39"/>
       <c r="U23" s="98" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V23" s="39"/>
       <c r="W23" s="39"/>
@@ -36878,19 +36938,19 @@
         <v>22</v>
       </c>
       <c r="C24" s="54" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D24" s="54">
         <v>2021</v>
       </c>
       <c r="E24" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F24" s="69" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G24" s="69" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H24" s="60">
         <v>7.9166666666666663E-2</v>
@@ -36904,7 +36964,7 @@
       </c>
       <c r="L24" s="137"/>
       <c r="M24" s="73" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N24" s="75">
         <v>9.1666666666666674E-2</v>
@@ -36937,33 +36997,33 @@
         <v>23</v>
       </c>
       <c r="C25" s="73" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D25" s="73">
         <v>2022</v>
       </c>
       <c r="E25" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F25" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G25" s="74" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H25" s="75">
         <v>1.625</v>
       </c>
       <c r="I25" s="39"/>
       <c r="J25" s="113" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K25" s="60">
         <v>0.80138888888888893</v>
       </c>
       <c r="L25" s="137"/>
       <c r="M25" s="113" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N25" s="60">
         <v>0.64722222222222225</v>
@@ -36985,7 +37045,7 @@
       </c>
       <c r="T25" s="39"/>
       <c r="U25" s="98" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="V25" s="39"/>
       <c r="W25" s="39"/>
@@ -36996,19 +37056,19 @@
         <v>24</v>
       </c>
       <c r="C26" s="54" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D26" s="54">
         <v>2022</v>
       </c>
       <c r="E26" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F26" s="69" t="s">
         <v>88</v>
       </c>
       <c r="G26" s="69" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H26" s="60">
         <v>0.40416666666666662</v>
@@ -37018,7 +37078,7 @@
       <c r="K26" s="77"/>
       <c r="L26" s="61"/>
       <c r="M26" s="139" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N26" s="77">
         <v>0.13125000000000001</v>
@@ -37040,7 +37100,7 @@
       </c>
       <c r="T26" s="39"/>
       <c r="U26" s="99" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="V26" s="39"/>
       <c r="W26" s="39"/>
@@ -37051,16 +37111,16 @@
         <v>25</v>
       </c>
       <c r="C27" s="73" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D27" s="73">
         <v>2015</v>
       </c>
       <c r="E27" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F27" s="74" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G27" s="74" t="s">
         <v>13</v>
@@ -37086,7 +37146,7 @@
       </c>
       <c r="T27" s="39"/>
       <c r="U27" s="98" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="V27" s="39"/>
       <c r="W27" s="39"/>
@@ -37097,33 +37157,33 @@
         <v>26</v>
       </c>
       <c r="C28" s="54" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D28" s="54">
         <v>2022</v>
       </c>
       <c r="E28" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F28" s="69" t="s">
         <v>93</v>
       </c>
       <c r="G28" s="69" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H28" s="60">
         <v>0.11805555555555557</v>
       </c>
       <c r="I28" s="39"/>
-      <c r="J28" s="170" t="s">
+      <c r="J28" s="171" t="s">
+        <v>291</v>
+      </c>
+      <c r="K28" s="172"/>
+      <c r="L28" s="136"/>
+      <c r="M28" s="171" t="s">
         <v>292</v>
       </c>
-      <c r="K28" s="171"/>
-      <c r="L28" s="136"/>
-      <c r="M28" s="170" t="s">
-        <v>293</v>
-      </c>
-      <c r="N28" s="171"/>
+      <c r="N28" s="172"/>
       <c r="O28" s="39"/>
       <c r="P28" s="93" t="s">
         <v>38</v>
@@ -37141,7 +37201,7 @@
       </c>
       <c r="T28" s="39"/>
       <c r="U28" s="100" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="V28" s="39"/>
       <c r="W28" s="39"/>
@@ -37152,33 +37212,33 @@
         <v>27</v>
       </c>
       <c r="C29" s="73" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D29" s="73">
         <v>2021</v>
       </c>
       <c r="E29" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F29" s="74" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G29" s="74" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H29" s="75">
         <v>0.22013888888888888</v>
       </c>
       <c r="I29" s="39"/>
       <c r="J29" s="122" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K29" s="132">
         <v>0.19791666666666666</v>
       </c>
       <c r="L29" s="137"/>
       <c r="M29" s="141" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N29" s="72">
         <v>0.30486111111111108</v>
@@ -37200,7 +37260,7 @@
       </c>
       <c r="T29" s="39"/>
       <c r="U29" s="98" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V29" s="39"/>
       <c r="W29" s="39"/>
@@ -37211,33 +37271,33 @@
         <v>28</v>
       </c>
       <c r="C30" s="54" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D30" s="54">
         <v>2022</v>
       </c>
       <c r="E30" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F30" s="69" t="s">
         <v>105</v>
       </c>
       <c r="G30" s="69" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H30" s="60">
         <v>0.77777777777777779</v>
       </c>
       <c r="I30" s="39"/>
       <c r="J30" s="113" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K30" s="133">
         <v>0.28750000000000003</v>
       </c>
       <c r="L30" s="140"/>
       <c r="M30" s="142" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N30" s="60">
         <v>0.20833333333333334</v>
@@ -37259,7 +37319,7 @@
       </c>
       <c r="T30" s="39"/>
       <c r="U30" s="100" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="V30" s="39"/>
       <c r="W30" s="39"/>
@@ -37270,19 +37330,19 @@
         <v>29</v>
       </c>
       <c r="C31" s="73" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D31" s="73">
         <v>2022</v>
       </c>
       <c r="E31" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F31" s="74" t="s">
+        <v>365</v>
+      </c>
+      <c r="G31" s="74" t="s">
         <v>366</v>
-      </c>
-      <c r="G31" s="74" t="s">
-        <v>367</v>
       </c>
       <c r="H31" s="75">
         <v>0.45833333333333331</v>
@@ -37296,7 +37356,7 @@
       </c>
       <c r="L31" s="137"/>
       <c r="M31" s="80" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N31" s="75">
         <v>0.21666666666666667</v>
@@ -37318,7 +37378,7 @@
       </c>
       <c r="T31" s="39"/>
       <c r="U31" s="98" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="V31" s="39"/>
       <c r="W31" s="39"/>
@@ -37329,33 +37389,33 @@
         <v>30</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D32" s="11">
         <v>2022</v>
       </c>
       <c r="E32" s="154" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H32" s="102">
         <v>0.96180555555555547</v>
       </c>
       <c r="I32" s="39"/>
       <c r="J32" s="113" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K32" s="133">
         <v>0.1875</v>
       </c>
       <c r="L32" s="137"/>
       <c r="M32" s="54" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="N32" s="60">
         <v>0.26944444444444443</v>
@@ -37377,7 +37437,7 @@
       </c>
       <c r="T32" s="39"/>
       <c r="U32" s="99" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="V32" s="39"/>
       <c r="W32" s="39"/>
@@ -37393,14 +37453,14 @@
       <c r="H33" s="61"/>
       <c r="I33" s="39"/>
       <c r="J33" s="135" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K33" s="134">
         <v>0.29375000000000001</v>
       </c>
       <c r="L33" s="137"/>
       <c r="M33" s="135" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N33" s="77">
         <v>0.77361111111111114</v>
@@ -37421,10 +37481,10 @@
         <v>3.5965277777777778</v>
       </c>
       <c r="T33" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="U33" s="128" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="V33" s="39"/>
       <c r="W33" s="39"/>
@@ -37470,15 +37530,15 @@
       <c r="G35" s="30"/>
       <c r="H35" s="61"/>
       <c r="I35" s="39"/>
-      <c r="J35" s="170" t="s">
+      <c r="J35" s="171" t="s">
+        <v>293</v>
+      </c>
+      <c r="K35" s="172"/>
+      <c r="L35" s="136"/>
+      <c r="M35" s="171" t="s">
         <v>294</v>
       </c>
-      <c r="K35" s="171"/>
-      <c r="L35" s="136"/>
-      <c r="M35" s="170" t="s">
-        <v>295</v>
-      </c>
-      <c r="N35" s="171"/>
+      <c r="N35" s="172"/>
       <c r="O35" s="39"/>
       <c r="P35" s="39"/>
       <c r="Q35" s="39"/>
@@ -37507,15 +37567,15 @@
       </c>
       <c r="L36" s="137"/>
       <c r="M36" s="131" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N36" s="72">
         <v>4.9305555555555554E-2</v>
       </c>
       <c r="O36" s="39"/>
-      <c r="P36" s="172"/>
-      <c r="Q36" s="172"/>
-      <c r="R36" s="172"/>
+      <c r="P36" s="170"/>
+      <c r="Q36" s="170"/>
+      <c r="R36" s="170"/>
       <c r="S36" s="111"/>
       <c r="T36" s="16"/>
       <c r="U36" s="16"/>
@@ -37533,14 +37593,14 @@
       <c r="H37" s="61"/>
       <c r="I37" s="39"/>
       <c r="J37" s="113" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K37" s="133">
         <v>6.3194444444444442E-2</v>
       </c>
       <c r="L37" s="137"/>
       <c r="M37" s="101" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N37" s="60">
         <v>0.18472222222222223</v>
@@ -37566,22 +37626,22 @@
       <c r="H38" s="61"/>
       <c r="I38" s="39"/>
       <c r="J38" s="112" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K38" s="132">
         <v>0.61597222222222225</v>
       </c>
       <c r="L38" s="137"/>
       <c r="M38" s="73" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N38" s="75">
         <v>0.21249999999999999</v>
       </c>
       <c r="O38" s="39"/>
-      <c r="P38" s="172"/>
-      <c r="Q38" s="172"/>
-      <c r="R38" s="172"/>
+      <c r="P38" s="170"/>
+      <c r="Q38" s="170"/>
+      <c r="R38" s="170"/>
       <c r="S38" s="111"/>
       <c r="T38" s="16"/>
       <c r="U38" s="16"/>
@@ -37599,22 +37659,22 @@
       <c r="H39" s="61"/>
       <c r="I39" s="39"/>
       <c r="J39" s="113" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K39" s="133">
         <v>1.3187499999999999</v>
       </c>
       <c r="L39" s="137"/>
       <c r="M39" s="54" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="N39" s="60">
         <v>0.26527777777777778</v>
       </c>
       <c r="O39" s="39"/>
-      <c r="P39" s="172"/>
-      <c r="Q39" s="172"/>
-      <c r="R39" s="172"/>
+      <c r="P39" s="170"/>
+      <c r="Q39" s="170"/>
+      <c r="R39" s="170"/>
       <c r="S39" s="124"/>
       <c r="T39" s="16"/>
       <c r="U39" s="16"/>
@@ -37632,22 +37692,22 @@
       <c r="H40" s="62"/>
       <c r="I40" s="39"/>
       <c r="J40" s="112" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K40" s="132">
         <v>0.75694444444444453</v>
       </c>
       <c r="L40" s="137"/>
       <c r="M40" s="132" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N40" s="75">
         <v>0.75347222222222221</v>
       </c>
       <c r="O40" s="39"/>
-      <c r="P40" s="172"/>
-      <c r="Q40" s="172"/>
-      <c r="R40" s="172"/>
+      <c r="P40" s="170"/>
+      <c r="Q40" s="170"/>
+      <c r="R40" s="170"/>
       <c r="S40" s="124"/>
       <c r="T40" s="16"/>
       <c r="U40" s="16"/>
@@ -37667,15 +37727,15 @@
       <c r="J41" s="14"/>
       <c r="K41" s="102"/>
       <c r="M41" s="14" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="N41" s="102">
         <v>1.0513888888888889</v>
       </c>
       <c r="O41" s="39"/>
-      <c r="P41" s="172"/>
-      <c r="Q41" s="172"/>
-      <c r="R41" s="172"/>
+      <c r="P41" s="170"/>
+      <c r="Q41" s="170"/>
+      <c r="R41" s="170"/>
       <c r="S41" s="124"/>
       <c r="T41" s="16"/>
       <c r="U41" s="16"/>
@@ -39538,7 +39598,7 @@
       <c r="H116" s="62"/>
       <c r="I116" s="39"/>
       <c r="J116" s="129" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K116" s="111"/>
       <c r="L116" s="111"/>
@@ -39565,7 +39625,7 @@
       <c r="H117" s="62"/>
       <c r="I117" s="39"/>
       <c r="J117" s="129" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K117" s="111"/>
       <c r="L117" s="111"/>
@@ -39652,7 +39712,7 @@
         <v>77</v>
       </c>
       <c r="R120" s="56" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S120" s="39"/>
       <c r="T120" s="39"/>
@@ -40548,7 +40608,7 @@
       <c r="O150" s="39"/>
       <c r="P150" s="39"/>
       <c r="Q150" s="41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R150" s="42">
         <f>SUM(R121:R149)</f>
@@ -40640,6 +40700,12 @@
     <sortCondition ref="J9"/>
   </sortState>
   <mergeCells count="18">
+    <mergeCell ref="P41:R41"/>
+    <mergeCell ref="P36:R36"/>
+    <mergeCell ref="P37:R37"/>
+    <mergeCell ref="P38:R38"/>
+    <mergeCell ref="P39:R39"/>
+    <mergeCell ref="P40:R40"/>
     <mergeCell ref="M35:N35"/>
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="M21:N21"/>
@@ -40652,12 +40718,6 @@
     <mergeCell ref="M14:N14"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="J35:K35"/>
-    <mergeCell ref="P41:R41"/>
-    <mergeCell ref="P36:R36"/>
-    <mergeCell ref="P37:R37"/>
-    <mergeCell ref="P38:R38"/>
-    <mergeCell ref="P39:R39"/>
-    <mergeCell ref="P40:R40"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J116" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
@@ -40733,7 +40793,7 @@
         <v>77</v>
       </c>
       <c r="E2" s="86" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F2" s="86" t="s">
         <v>12</v>
@@ -40745,15 +40805,15 @@
         <v>20</v>
       </c>
       <c r="I2" s="6"/>
-      <c r="J2" s="170" t="s">
-        <v>284</v>
+      <c r="J2" s="171" t="s">
+        <v>283</v>
       </c>
       <c r="K2" s="192"/>
       <c r="L2" s="136"/>
       <c r="M2" s="192" t="s">
-        <v>285</v>
-      </c>
-      <c r="N2" s="171"/>
+        <v>284</v>
+      </c>
+      <c r="N2" s="172"/>
       <c r="O2" s="39"/>
       <c r="P2" s="39"/>
       <c r="Q2" s="39"/>
@@ -40770,16 +40830,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="73" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D3" s="73">
         <v>2017</v>
       </c>
       <c r="E3" s="152" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F3" s="74" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G3" s="74" t="s">
         <v>13</v>
@@ -40789,14 +40849,14 @@
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="122" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K3" s="132">
         <v>0.24652777777777779</v>
       </c>
       <c r="L3" s="137"/>
       <c r="M3" s="131" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N3" s="72">
         <v>0.24305555555555555</v>
@@ -40817,33 +40877,33 @@
         <v>2</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D4" s="54">
         <v>2001</v>
       </c>
       <c r="E4" s="153" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F4" s="69" t="s">
+        <v>378</v>
+      </c>
+      <c r="G4" s="69" t="s">
         <v>379</v>
-      </c>
-      <c r="G4" s="69" t="s">
-        <v>380</v>
       </c>
       <c r="H4" s="60">
         <v>0.25555555555555559</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="113" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K4" s="133">
         <v>0.22361111111111109</v>
       </c>
       <c r="L4" s="137"/>
       <c r="M4" s="101" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N4" s="60">
         <v>1.1048611111111111</v>
@@ -40864,33 +40924,33 @@
         <v>3</v>
       </c>
       <c r="C5" s="73" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D5" s="73">
         <v>2018</v>
       </c>
       <c r="E5" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F5" s="74" t="s">
+        <v>382</v>
+      </c>
+      <c r="G5" s="74" t="s">
         <v>383</v>
-      </c>
-      <c r="G5" s="74" t="s">
-        <v>384</v>
       </c>
       <c r="H5" s="75">
         <v>0.5708333333333333</v>
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="135" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K5" s="77">
         <v>0.1875</v>
       </c>
       <c r="L5" s="137"/>
       <c r="M5" s="112" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N5" s="75">
         <v>9.9999999999999992E-2</v>
@@ -40911,26 +40971,26 @@
         <v>4</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D6" s="54">
         <v>2023</v>
       </c>
       <c r="E6" s="153" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F6" s="69" t="s">
+        <v>386</v>
+      </c>
+      <c r="G6" s="69" t="s">
         <v>387</v>
-      </c>
-      <c r="G6" s="69" t="s">
-        <v>388</v>
       </c>
       <c r="H6" s="60">
         <v>0.71388888888888891</v>
       </c>
       <c r="I6" s="6"/>
       <c r="M6" s="114" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N6" s="60">
         <v>2.9861111111111113E-2</v>
@@ -40951,26 +41011,26 @@
         <v>5</v>
       </c>
       <c r="C7" s="73" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D7" s="73">
         <v>2020</v>
       </c>
       <c r="E7" s="152" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F7" s="74" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G7" s="74" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H7" s="75">
         <v>0.80555555555555547</v>
       </c>
       <c r="I7" s="6"/>
       <c r="M7" s="112" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N7" s="75">
         <v>0.13125000000000001</v>
@@ -40991,26 +41051,26 @@
         <v>6</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D8" s="54">
         <v>2021</v>
       </c>
       <c r="E8" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G8" s="69" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H8" s="60">
         <v>8.5416666666666655E-2</v>
       </c>
       <c r="I8" s="6"/>
       <c r="M8" s="143" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="N8" s="102">
         <v>0.53819444444444442</v>
@@ -41031,19 +41091,19 @@
         <v>7</v>
       </c>
       <c r="C9" s="73" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D9" s="73">
         <v>2020</v>
       </c>
       <c r="E9" s="152" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F9" s="74" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G9" s="74" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H9" s="75">
         <v>0.15972222222222224</v>
@@ -41065,33 +41125,33 @@
         <v>8</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D10" s="54">
         <v>2020</v>
       </c>
       <c r="E10" s="153" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F10" s="69" t="s">
+        <v>394</v>
+      </c>
+      <c r="G10" s="69" t="s">
         <v>395</v>
-      </c>
-      <c r="G10" s="69" t="s">
-        <v>396</v>
       </c>
       <c r="H10" s="60">
         <v>1.1847222222222222</v>
       </c>
       <c r="I10" s="6"/>
-      <c r="J10" s="170" t="s">
+      <c r="J10" s="171" t="s">
+        <v>285</v>
+      </c>
+      <c r="K10" s="172"/>
+      <c r="L10" s="136"/>
+      <c r="M10" s="171" t="s">
         <v>286</v>
       </c>
-      <c r="K10" s="171"/>
-      <c r="L10" s="136"/>
-      <c r="M10" s="170" t="s">
-        <v>287</v>
-      </c>
-      <c r="N10" s="171"/>
+      <c r="N10" s="172"/>
       <c r="O10" s="39"/>
       <c r="P10" s="39"/>
       <c r="Q10" s="39"/>
@@ -41108,33 +41168,33 @@
         <v>9</v>
       </c>
       <c r="C11" s="73" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D11" s="73">
         <v>2020</v>
       </c>
       <c r="E11" s="152" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F11" s="74" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G11" s="74" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H11" s="75">
         <v>0.5444444444444444</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="122" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K11" s="132">
         <v>4.7222222222222221E-2</v>
       </c>
       <c r="L11" s="137"/>
       <c r="M11" s="131" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N11" s="72">
         <v>0.41944444444444445</v>
@@ -41155,33 +41215,33 @@
         <v>10</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D12" s="54">
         <v>2018</v>
       </c>
       <c r="E12" s="153" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F12" s="69" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G12" s="69" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H12" s="60">
         <v>0.30138888888888887</v>
       </c>
       <c r="I12" s="6"/>
       <c r="J12" s="113" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K12" s="133">
         <v>8.819444444444445E-2</v>
       </c>
       <c r="L12" s="137"/>
       <c r="M12" s="101" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N12" s="60">
         <v>0.27361111111111108</v>
@@ -41202,33 +41262,33 @@
         <v>11</v>
       </c>
       <c r="C13" s="73" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D13" s="73">
         <v>1997</v>
       </c>
       <c r="E13" s="152" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F13" s="74" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G13" s="74" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H13" s="75">
         <v>0.64166666666666672</v>
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="112" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K13" s="132">
         <v>0.32291666666666669</v>
       </c>
       <c r="L13" s="137"/>
       <c r="M13" s="73" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N13" s="75">
         <v>0.14444444444444446</v>
@@ -41249,33 +41309,33 @@
         <v>12</v>
       </c>
       <c r="C14" s="54" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D14" s="54">
         <v>1993</v>
       </c>
       <c r="E14" s="153" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F14" s="69" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G14" s="69" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H14" s="60">
         <v>0.21319444444444444</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="113" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K14" s="60">
         <v>0.16180555555555556</v>
       </c>
       <c r="L14" s="61"/>
       <c r="M14" s="143" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N14" s="102">
         <v>5.347222222222222E-2</v>
@@ -41296,26 +41356,26 @@
         <v>13</v>
       </c>
       <c r="C15" s="73" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D15" s="73">
         <v>2016</v>
       </c>
       <c r="E15" s="152" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F15" s="74" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G15" s="74" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H15" s="75">
         <v>0.59791666666666665</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="135" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K15" s="77">
         <v>3.3333333333333333E-2</v>
@@ -41336,16 +41396,16 @@
         <v>14</v>
       </c>
       <c r="C16" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D16" s="54">
         <v>1997</v>
       </c>
       <c r="E16" s="153" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F16" s="69" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G16" s="69" t="s">
         <v>13</v>
@@ -41370,33 +41430,33 @@
         <v>15</v>
       </c>
       <c r="C17" s="73" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D17" s="73">
         <v>2023</v>
       </c>
       <c r="E17" s="152" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F17" s="74" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G17" s="74" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H17" s="75">
         <v>6.063194444444445</v>
       </c>
       <c r="I17" s="6"/>
-      <c r="J17" s="170" t="s">
+      <c r="J17" s="171" t="s">
+        <v>287</v>
+      </c>
+      <c r="K17" s="172"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="171" t="s">
         <v>288</v>
       </c>
-      <c r="K17" s="171"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="170" t="s">
-        <v>289</v>
-      </c>
-      <c r="N17" s="171"/>
+      <c r="N17" s="172"/>
       <c r="O17" s="39"/>
       <c r="P17" s="39"/>
       <c r="Q17" s="39"/>
@@ -41413,33 +41473,33 @@
         <v>16</v>
       </c>
       <c r="C18" s="54" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D18" s="54">
         <v>2023</v>
       </c>
       <c r="E18" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F18" s="69" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G18" s="69" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H18" s="60">
         <v>0.49652777777777773</v>
       </c>
       <c r="I18" s="6"/>
       <c r="J18" s="122" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K18" s="132">
         <v>0.3125</v>
       </c>
       <c r="L18" s="137"/>
       <c r="M18" s="131" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N18" s="72">
         <v>0.27777777777777779</v>
@@ -41460,33 +41520,33 @@
         <v>17</v>
       </c>
       <c r="C19" s="73" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D19" s="73">
         <v>2020</v>
       </c>
       <c r="E19" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F19" s="74" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G19" s="74" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H19" s="75">
         <v>9.375E-2</v>
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="113" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K19" s="133">
         <v>0.13333333333333333</v>
       </c>
       <c r="L19" s="137"/>
       <c r="M19" s="101" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N19" s="60">
         <v>0.1125</v>
@@ -41507,16 +41567,16 @@
         <v>18</v>
       </c>
       <c r="C20" s="54" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D20" s="54">
         <v>2021</v>
       </c>
       <c r="E20" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F20" s="69" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G20" s="69">
         <v>45123</v>
@@ -41526,14 +41586,14 @@
       </c>
       <c r="I20" s="6"/>
       <c r="J20" s="135" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K20" s="77">
         <v>3.2638888888888891E-2</v>
       </c>
       <c r="L20" s="137"/>
       <c r="M20" s="135" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N20" s="77">
         <v>0.15</v>
@@ -41554,19 +41614,19 @@
         <v>19</v>
       </c>
       <c r="C21" s="73" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D21" s="73">
         <v>2023</v>
       </c>
       <c r="E21" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F21" s="74" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G21" s="74" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H21" s="75">
         <v>0.51388888888888895</v>
@@ -41577,13 +41637,13 @@
         <v>31</v>
       </c>
       <c r="Q21" s="91" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R21" s="91" t="s">
-        <v>121</v>
+        <v>676</v>
       </c>
       <c r="S21" s="92" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="T21" s="39"/>
       <c r="U21" s="88" t="s">
@@ -41600,33 +41660,33 @@
         <v>20</v>
       </c>
       <c r="C22" s="54" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D22" s="54">
         <v>2011</v>
       </c>
       <c r="E22" s="153" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F22" s="69" t="s">
+        <v>427</v>
+      </c>
+      <c r="G22" s="69" t="s">
         <v>428</v>
-      </c>
-      <c r="G22" s="69" t="s">
-        <v>429</v>
       </c>
       <c r="H22" s="60">
         <v>0.50555555555555554</v>
       </c>
       <c r="I22" s="6"/>
-      <c r="J22" s="170" t="s">
+      <c r="J22" s="171" t="s">
+        <v>289</v>
+      </c>
+      <c r="K22" s="172"/>
+      <c r="L22" s="136"/>
+      <c r="M22" s="171" t="s">
         <v>290</v>
       </c>
-      <c r="K22" s="171"/>
-      <c r="L22" s="136"/>
-      <c r="M22" s="170" t="s">
-        <v>291</v>
-      </c>
-      <c r="N22" s="171"/>
+      <c r="N22" s="172"/>
       <c r="O22" s="39"/>
       <c r="P22" s="63" t="s">
         <v>32</v>
@@ -41644,7 +41704,7 @@
       </c>
       <c r="T22" s="39"/>
       <c r="U22" s="104" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="V22" s="146"/>
       <c r="W22" s="147"/>
@@ -41658,33 +41718,33 @@
         <v>21</v>
       </c>
       <c r="C23" s="73" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D23" s="73">
         <v>2021</v>
       </c>
       <c r="E23" s="152" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F23" s="74" t="s">
+        <v>431</v>
+      </c>
+      <c r="G23" s="74" t="s">
         <v>432</v>
-      </c>
-      <c r="G23" s="74" t="s">
-        <v>433</v>
       </c>
       <c r="H23" s="75">
         <v>0.45277777777777778</v>
       </c>
       <c r="I23" s="6"/>
       <c r="J23" s="122" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K23" s="132">
         <v>0.3611111111111111</v>
       </c>
       <c r="L23" s="137"/>
       <c r="M23" s="131" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N23" s="72">
         <v>1.1909722222222221</v>
@@ -41707,7 +41767,7 @@
       </c>
       <c r="T23" s="39"/>
       <c r="U23" s="105" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="V23" s="146"/>
       <c r="W23" s="147"/>
@@ -41721,33 +41781,33 @@
         <v>22</v>
       </c>
       <c r="C24" s="54" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D24" s="54">
         <v>2013</v>
       </c>
       <c r="E24" s="153" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F24" s="69" t="s">
         <v>73</v>
       </c>
       <c r="G24" s="69" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H24" s="60">
         <v>1.1722222222222223</v>
       </c>
       <c r="I24" s="39"/>
       <c r="J24" s="113" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K24" s="133">
         <v>4.7916666666666663E-2</v>
       </c>
       <c r="L24" s="137"/>
       <c r="M24" s="101" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N24" s="60">
         <v>0.52777777777777779</v>
@@ -41770,7 +41830,7 @@
       </c>
       <c r="T24" s="39"/>
       <c r="U24" s="100" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="V24" s="146"/>
       <c r="W24" s="147">
@@ -41786,26 +41846,26 @@
         <v>23</v>
       </c>
       <c r="C25" s="73" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D25" s="73">
         <v>2009</v>
       </c>
       <c r="E25" s="152" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F25" s="74" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G25" s="74" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H25" s="75">
         <v>1.4138888888888888</v>
       </c>
       <c r="I25" s="39"/>
       <c r="J25" s="112" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="K25" s="75">
         <v>0.10416666666666667</v>
@@ -41831,7 +41891,7 @@
       </c>
       <c r="T25" s="39"/>
       <c r="U25" s="105" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="V25" s="146"/>
       <c r="W25" s="147">
@@ -41847,16 +41907,16 @@
         <v>24</v>
       </c>
       <c r="C26" s="54" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D26" s="54">
         <v>1999</v>
       </c>
       <c r="E26" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F26" s="69" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G26" s="69" t="s">
         <v>13</v>
@@ -41866,7 +41926,7 @@
       </c>
       <c r="I26" s="39"/>
       <c r="J26" s="14" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K26" s="102">
         <v>6.1111111111111116E-2</v>
@@ -41889,7 +41949,7 @@
       </c>
       <c r="T26" s="39"/>
       <c r="U26" s="99" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="V26" s="146"/>
       <c r="W26" s="147">
@@ -41907,16 +41967,16 @@
         <v>25</v>
       </c>
       <c r="C27" s="73" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D27" s="73">
         <v>2023</v>
       </c>
       <c r="E27" s="152" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F27" s="74" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G27" s="74" t="s">
         <v>99</v>
@@ -41943,7 +42003,7 @@
       </c>
       <c r="T27" s="39"/>
       <c r="U27" s="98" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="V27" s="146"/>
       <c r="W27" s="147">
@@ -41959,33 +42019,33 @@
         <v>26</v>
       </c>
       <c r="C28" s="54" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D28" s="54">
         <v>2023</v>
       </c>
       <c r="E28" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F28" s="69" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G28" s="69" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H28" s="60">
         <v>2.6388888888888889E-2</v>
       </c>
       <c r="I28" s="39"/>
-      <c r="J28" s="170" t="s">
+      <c r="J28" s="171" t="s">
+        <v>291</v>
+      </c>
+      <c r="K28" s="172"/>
+      <c r="L28" s="136"/>
+      <c r="M28" s="171" t="s">
         <v>292</v>
       </c>
-      <c r="K28" s="171"/>
-      <c r="L28" s="136"/>
-      <c r="M28" s="170" t="s">
-        <v>293</v>
-      </c>
-      <c r="N28" s="171"/>
+      <c r="N28" s="172"/>
       <c r="O28" s="39"/>
       <c r="P28" s="93" t="s">
         <v>38</v>
@@ -42004,7 +42064,7 @@
       </c>
       <c r="T28" s="39"/>
       <c r="U28" s="99" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="V28" s="146"/>
       <c r="W28" s="147">
@@ -42020,16 +42080,16 @@
         <v>27</v>
       </c>
       <c r="C29" s="73" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D29" s="73">
         <v>2023</v>
       </c>
       <c r="E29" s="152" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F29" s="74" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G29" s="74">
         <v>45224</v>
@@ -42039,14 +42099,14 @@
       </c>
       <c r="I29" s="39"/>
       <c r="J29" s="122" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K29" s="132">
         <v>0.90208333333333324</v>
       </c>
       <c r="L29" s="137"/>
       <c r="M29" s="141" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N29" s="72">
         <v>0.36041666666666666</v>
@@ -42069,7 +42129,7 @@
       </c>
       <c r="T29" s="39"/>
       <c r="U29" s="105" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="V29" s="146"/>
       <c r="W29" s="111">
@@ -42085,33 +42145,33 @@
         <v>28</v>
       </c>
       <c r="C30" s="54" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D30" s="54">
         <v>2023</v>
       </c>
       <c r="E30" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F30" s="69" t="s">
+        <v>456</v>
+      </c>
+      <c r="G30" s="69" t="s">
         <v>457</v>
-      </c>
-      <c r="G30" s="69" t="s">
-        <v>458</v>
       </c>
       <c r="H30" s="60">
         <v>0.16527777777777777</v>
       </c>
       <c r="I30" s="39"/>
       <c r="J30" s="113" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K30" s="133">
         <v>0.23541666666666669</v>
       </c>
       <c r="L30" s="140"/>
       <c r="M30" s="142" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N30" s="60">
         <v>0.44861111111111113</v>
@@ -42134,7 +42194,7 @@
       </c>
       <c r="T30" s="39"/>
       <c r="U30" s="99" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="V30" s="146"/>
       <c r="W30" s="147">
@@ -42152,33 +42212,33 @@
         <v>29</v>
       </c>
       <c r="C31" s="73" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D31" s="73">
         <v>2021</v>
       </c>
       <c r="E31" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F31" s="74" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G31" s="74" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H31" s="75">
         <v>4.9999999999999996E-2</v>
       </c>
       <c r="I31" s="39"/>
       <c r="J31" s="112" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K31" s="75">
         <v>7.1527777777777787E-2</v>
       </c>
       <c r="L31" s="137"/>
       <c r="M31" s="115" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N31" s="77">
         <v>3.0555555555555555E-2</v>
@@ -42201,7 +42261,7 @@
       </c>
       <c r="T31" s="39"/>
       <c r="U31" s="105" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="V31" s="146"/>
       <c r="W31" s="147">
@@ -42217,26 +42277,26 @@
         <v>30</v>
       </c>
       <c r="C32" s="54" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D32" s="54">
         <v>2023</v>
       </c>
       <c r="E32" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F32" s="69" t="s">
+        <v>462</v>
+      </c>
+      <c r="G32" s="69" t="s">
         <v>463</v>
-      </c>
-      <c r="G32" s="69" t="s">
-        <v>464</v>
       </c>
       <c r="H32" s="60">
         <v>0.19652777777777777</v>
       </c>
       <c r="I32" s="39"/>
       <c r="J32" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K32" s="102">
         <v>4.0972222222222222E-2</v>
@@ -42259,7 +42319,7 @@
       </c>
       <c r="T32" s="39"/>
       <c r="U32" s="99" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="V32" s="146"/>
       <c r="W32" s="147">
@@ -42277,19 +42337,19 @@
         <v>31</v>
       </c>
       <c r="C33" s="73" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D33" s="73">
         <v>2012</v>
       </c>
       <c r="E33" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F33" s="74" t="s">
+        <v>466</v>
+      </c>
+      <c r="G33" s="74" t="s">
         <v>467</v>
-      </c>
-      <c r="G33" s="74" t="s">
-        <v>468</v>
       </c>
       <c r="H33" s="75">
         <v>0.25347222222222221</v>
@@ -42312,10 +42372,10 @@
         <v>2.2263888888888888</v>
       </c>
       <c r="T33" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="U33" s="128" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="V33" s="39"/>
       <c r="W33" s="147">
@@ -42333,33 +42393,33 @@
         <v>32</v>
       </c>
       <c r="C34" s="54" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D34" s="54">
         <v>2022</v>
       </c>
       <c r="E34" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F34" s="69" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G34" s="69" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H34" s="60">
         <v>0.14722222222222223</v>
       </c>
       <c r="I34" s="39"/>
-      <c r="J34" s="170" t="s">
+      <c r="J34" s="171" t="s">
+        <v>293</v>
+      </c>
+      <c r="K34" s="172"/>
+      <c r="L34" s="136"/>
+      <c r="M34" s="171" t="s">
         <v>294</v>
       </c>
-      <c r="K34" s="171"/>
-      <c r="L34" s="136"/>
-      <c r="M34" s="170" t="s">
-        <v>295</v>
-      </c>
-      <c r="N34" s="171"/>
+      <c r="N34" s="172"/>
       <c r="O34" s="39"/>
       <c r="P34" s="125" t="s">
         <v>77</v>
@@ -42387,16 +42447,16 @@
         <v>33</v>
       </c>
       <c r="C35" s="73" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D35" s="73">
         <v>2016</v>
       </c>
       <c r="E35" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F35" s="74" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G35" s="74">
         <v>45266</v>
@@ -42406,14 +42466,14 @@
       </c>
       <c r="I35" s="39"/>
       <c r="J35" s="122" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K35" s="132">
         <v>0.35902777777777778</v>
       </c>
       <c r="L35" s="137"/>
       <c r="M35" s="131" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="N35" s="72">
         <v>0.48958333333333331</v>
@@ -42434,41 +42494,41 @@
         <v>34</v>
       </c>
       <c r="C36" s="54" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D36" s="54">
         <v>2011</v>
       </c>
       <c r="E36" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F36" s="69" t="s">
+        <v>474</v>
+      </c>
+      <c r="G36" s="69" t="s">
         <v>475</v>
-      </c>
-      <c r="G36" s="69" t="s">
-        <v>476</v>
       </c>
       <c r="H36" s="60">
         <v>0.2986111111111111</v>
       </c>
       <c r="I36" s="39"/>
       <c r="J36" s="113" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K36" s="133">
         <v>0.6958333333333333</v>
       </c>
       <c r="L36" s="137"/>
       <c r="M36" s="101" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="N36" s="60">
         <v>0.36944444444444446</v>
       </c>
       <c r="O36" s="39"/>
-      <c r="P36" s="172"/>
-      <c r="Q36" s="172"/>
-      <c r="R36" s="172"/>
+      <c r="P36" s="170"/>
+      <c r="Q36" s="170"/>
+      <c r="R36" s="170"/>
       <c r="S36" s="111"/>
       <c r="T36" s="16"/>
       <c r="U36" s="16"/>
@@ -42481,13 +42541,13 @@
         <v>35</v>
       </c>
       <c r="C37" s="73" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D37" s="73">
         <v>2021</v>
       </c>
       <c r="E37" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F37" s="74" t="s">
         <v>114</v>
@@ -42500,22 +42560,22 @@
       </c>
       <c r="I37" s="39"/>
       <c r="J37" s="135" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K37" s="77">
         <v>4.7222222222222221E-2</v>
       </c>
       <c r="L37" s="137"/>
       <c r="M37" s="135" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N37" s="77">
         <v>7.9166666666666663E-2</v>
       </c>
       <c r="O37" s="39"/>
       <c r="P37" s="175"/>
-      <c r="Q37" s="172"/>
-      <c r="R37" s="172"/>
+      <c r="Q37" s="170"/>
+      <c r="R37" s="170"/>
       <c r="S37" s="111"/>
       <c r="T37" s="16"/>
       <c r="U37" s="16"/>
@@ -42528,28 +42588,28 @@
         <v>36</v>
       </c>
       <c r="C38" s="54" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D38" s="54">
         <v>2016</v>
       </c>
       <c r="E38" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F38" s="69" t="s">
         <v>117</v>
       </c>
       <c r="G38" s="69" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H38" s="60">
         <v>0.88750000000000007</v>
       </c>
       <c r="I38" s="39"/>
       <c r="O38" s="39"/>
-      <c r="P38" s="172"/>
-      <c r="Q38" s="172"/>
-      <c r="R38" s="172"/>
+      <c r="P38" s="170"/>
+      <c r="Q38" s="170"/>
+      <c r="R38" s="170"/>
       <c r="S38" s="111"/>
       <c r="T38" s="16"/>
       <c r="U38" s="16"/>
@@ -42567,9 +42627,9 @@
       <c r="H39" s="138"/>
       <c r="I39" s="39"/>
       <c r="O39" s="39"/>
-      <c r="P39" s="172"/>
-      <c r="Q39" s="172"/>
-      <c r="R39" s="172"/>
+      <c r="P39" s="170"/>
+      <c r="Q39" s="170"/>
+      <c r="R39" s="170"/>
       <c r="S39" s="124"/>
       <c r="T39" s="16"/>
       <c r="U39" s="16"/>
@@ -42587,9 +42647,9 @@
       <c r="H40" s="61"/>
       <c r="I40" s="39"/>
       <c r="O40" s="39"/>
-      <c r="P40" s="172"/>
-      <c r="Q40" s="172"/>
-      <c r="R40" s="172"/>
+      <c r="P40" s="170"/>
+      <c r="Q40" s="170"/>
+      <c r="R40" s="170"/>
       <c r="S40" s="124"/>
       <c r="T40" s="16"/>
       <c r="U40" s="16"/>
@@ -42607,9 +42667,9 @@
       <c r="H41" s="61"/>
       <c r="I41" s="39"/>
       <c r="O41" s="39"/>
-      <c r="P41" s="172"/>
-      <c r="Q41" s="172"/>
-      <c r="R41" s="172"/>
+      <c r="P41" s="170"/>
+      <c r="Q41" s="170"/>
+      <c r="R41" s="170"/>
       <c r="S41" s="124"/>
       <c r="T41" s="16"/>
       <c r="U41" s="16"/>
@@ -44452,7 +44512,7 @@
       <c r="H116" s="62"/>
       <c r="I116" s="39"/>
       <c r="J116" s="129" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K116" s="111"/>
       <c r="L116" s="111"/>
@@ -44479,7 +44539,7 @@
       <c r="H117" s="62"/>
       <c r="I117" s="39"/>
       <c r="J117" s="129" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K117" s="111"/>
       <c r="L117" s="111"/>
@@ -44491,7 +44551,7 @@
         <v>77</v>
       </c>
       <c r="R117" s="56" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S117" s="39"/>
       <c r="T117" s="39"/>
@@ -45472,7 +45532,7 @@
       <c r="O150" s="39"/>
       <c r="P150" s="39"/>
       <c r="Q150" s="41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R150" s="42">
         <f>SUM(R119:R149)</f>
@@ -45561,24 +45621,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M17:N17"/>
     <mergeCell ref="P41:R41"/>
     <mergeCell ref="P36:R36"/>
     <mergeCell ref="P37:R37"/>
     <mergeCell ref="P38:R38"/>
     <mergeCell ref="P39:R39"/>
     <mergeCell ref="P40:R40"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="J22:K22"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <hyperlinks>
@@ -45660,7 +45720,7 @@
         <v>77</v>
       </c>
       <c r="E2" s="86" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F2" s="86" t="s">
         <v>12</v>
@@ -45672,15 +45732,15 @@
         <v>20</v>
       </c>
       <c r="I2" s="6"/>
-      <c r="J2" s="170" t="s">
+      <c r="J2" s="171" t="s">
+        <v>283</v>
+      </c>
+      <c r="K2" s="172"/>
+      <c r="L2" s="136"/>
+      <c r="M2" s="171" t="s">
         <v>284</v>
       </c>
-      <c r="K2" s="171"/>
-      <c r="L2" s="136"/>
-      <c r="M2" s="170" t="s">
-        <v>285</v>
-      </c>
-      <c r="N2" s="171"/>
+      <c r="N2" s="172"/>
       <c r="O2" s="39"/>
       <c r="P2" s="39"/>
       <c r="Q2" s="39"/>
@@ -45697,33 +45757,33 @@
         <v>1</v>
       </c>
       <c r="C3" s="73" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D3" s="73">
         <v>2016</v>
       </c>
       <c r="E3" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F3" s="74" t="s">
+        <v>480</v>
+      </c>
+      <c r="G3" s="74" t="s">
         <v>481</v>
-      </c>
-      <c r="G3" s="74" t="s">
-        <v>482</v>
       </c>
       <c r="H3" s="75">
         <v>0.88750000000000007</v>
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="122" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K3" s="132">
         <v>0.28750000000000003</v>
       </c>
       <c r="L3" s="137"/>
       <c r="M3" s="131" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N3" s="72">
         <v>0.60833333333333328</v>
@@ -45744,33 +45804,33 @@
         <v>2</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D4" s="54">
         <v>2023</v>
       </c>
       <c r="E4" s="153" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F4" s="69" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G4" s="69" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H4" s="60">
         <v>0.64722222222222225</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="113" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K4" s="133">
         <v>0.12847222222222224</v>
       </c>
       <c r="L4" s="137"/>
       <c r="M4" s="101" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N4" s="60">
         <v>0.36249999999999999</v>
@@ -45791,19 +45851,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="73" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D5" s="73">
         <v>2021</v>
       </c>
       <c r="E5" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F5" s="74" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G5" s="74" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H5" s="75">
         <v>0.48194444444444445</v>
@@ -45813,7 +45873,7 @@
       <c r="K5" s="138"/>
       <c r="L5" s="163"/>
       <c r="M5" s="135" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="N5" s="77">
         <v>3.6805555555555557E-2</v>
@@ -45834,19 +45894,19 @@
         <v>4</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D6" s="54">
         <v>2020</v>
       </c>
       <c r="E6" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G6" s="69" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H6" s="60">
         <v>0.60972222222222217</v>
@@ -45868,33 +45928,33 @@
         <v>5</v>
       </c>
       <c r="C7" s="73" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D7" s="73">
         <v>2024</v>
       </c>
       <c r="E7" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F7" s="74" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G7" s="74" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H7" s="75">
         <v>0.33749999999999997</v>
       </c>
       <c r="I7" s="6"/>
-      <c r="J7" s="170" t="s">
+      <c r="J7" s="171" t="s">
+        <v>285</v>
+      </c>
+      <c r="K7" s="172"/>
+      <c r="L7" s="136"/>
+      <c r="M7" s="171" t="s">
         <v>286</v>
       </c>
-      <c r="K7" s="171"/>
-      <c r="L7" s="136"/>
-      <c r="M7" s="170" t="s">
-        <v>287</v>
-      </c>
-      <c r="N7" s="171"/>
+      <c r="N7" s="172"/>
       <c r="O7" s="39"/>
       <c r="P7" s="39"/>
       <c r="Q7" s="39"/>
@@ -45911,33 +45971,33 @@
         <v>6</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D8" s="54">
         <v>2024</v>
       </c>
       <c r="E8" s="153" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G8" s="69" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H8" s="60">
         <v>0.59027777777777779</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="122" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K8" s="132">
         <v>1.0229166666666667</v>
       </c>
       <c r="L8" s="137"/>
       <c r="M8" s="131" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N8" s="72">
         <v>0.40486111111111112</v>
@@ -45958,19 +46018,19 @@
         <v>7</v>
       </c>
       <c r="C9" s="73" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D9" s="73">
         <v>2023</v>
       </c>
       <c r="E9" s="152" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F9" s="74" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G9" s="74" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H9" s="75">
         <f>SUM(W24,X23)</f>
@@ -45978,14 +46038,14 @@
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="113" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K9" s="133">
         <v>6.458333333333334E-2</v>
       </c>
       <c r="L9" s="137"/>
       <c r="M9" s="101" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="N9" s="60">
         <v>2.7083333333333334E-2</v>
@@ -46006,19 +46066,19 @@
         <v>8</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D10" s="54">
         <v>2006</v>
       </c>
       <c r="E10" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G10" s="69" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H10" s="60">
         <v>1.3131944444444446</v>
@@ -46028,7 +46088,7 @@
       <c r="K10" s="138"/>
       <c r="L10" s="163"/>
       <c r="M10" s="135" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="N10" s="77">
         <v>5.6944444444444443E-2</v>
@@ -46049,19 +46109,19 @@
         <v>9</v>
       </c>
       <c r="C11" s="73" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D11" s="73">
         <v>2024</v>
       </c>
       <c r="E11" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F11" s="74" t="s">
+        <v>503</v>
+      </c>
+      <c r="G11" s="74" t="s">
         <v>504</v>
-      </c>
-      <c r="G11" s="74" t="s">
-        <v>505</v>
       </c>
       <c r="H11" s="75">
         <v>0.13541666666666666</v>
@@ -46083,33 +46143,33 @@
         <v>10</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D12" s="54">
         <v>1998</v>
       </c>
       <c r="E12" s="153" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F12" s="69" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G12" s="69" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H12" s="60">
         <v>0.48819444444444443</v>
       </c>
       <c r="I12" s="6"/>
-      <c r="J12" s="170" t="s">
+      <c r="J12" s="171" t="s">
+        <v>287</v>
+      </c>
+      <c r="K12" s="172"/>
+      <c r="L12" s="136"/>
+      <c r="M12" s="171" t="s">
         <v>288</v>
       </c>
-      <c r="K12" s="171"/>
-      <c r="L12" s="136"/>
-      <c r="M12" s="170" t="s">
-        <v>289</v>
-      </c>
-      <c r="N12" s="171"/>
+      <c r="N12" s="172"/>
       <c r="O12" s="39"/>
       <c r="P12" s="39"/>
       <c r="Q12" s="39"/>
@@ -46126,33 +46186,33 @@
         <v>11</v>
       </c>
       <c r="C13" s="73" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D13" s="73">
         <v>2018</v>
       </c>
       <c r="E13" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F13" s="74" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G13" s="74" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H13" s="75">
         <v>0.4548611111111111</v>
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="122" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K13" s="132">
         <v>0.18472222222222223</v>
       </c>
       <c r="L13" s="137"/>
       <c r="M13" s="131" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N13" s="72">
         <v>3.9583333333333331E-2</v>
@@ -46173,33 +46233,33 @@
         <v>12</v>
       </c>
       <c r="C14" s="54" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D14" s="54">
         <v>2024</v>
       </c>
       <c r="E14" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F14" s="69" t="s">
         <v>49</v>
       </c>
       <c r="G14" s="69" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H14" s="60">
         <v>0.54583333333333328</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="113" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K14" s="133">
         <v>6.0416666666666667E-2</v>
       </c>
       <c r="L14" s="137"/>
       <c r="M14" s="142" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N14" s="164">
         <v>0.18958333333333333</v>
@@ -46220,33 +46280,33 @@
         <v>13</v>
       </c>
       <c r="C15" s="73" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D15" s="73">
         <v>2024</v>
       </c>
       <c r="E15" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F15" s="74" t="s">
         <v>54</v>
       </c>
       <c r="G15" s="74" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H15" s="75">
         <v>0.46250000000000002</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="135" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K15" s="77">
         <v>4.583333333333333E-2</v>
       </c>
       <c r="L15" s="137"/>
       <c r="M15" s="80" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="N15" s="75">
         <v>4.0972222222222222E-2</v>
@@ -46267,26 +46327,26 @@
         <v>14</v>
       </c>
       <c r="C16" s="54" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D16" s="54">
         <v>2015</v>
       </c>
       <c r="E16" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F16" s="69" t="s">
         <v>58</v>
       </c>
       <c r="G16" s="69" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H16" s="60">
         <v>0.29166666666666669</v>
       </c>
       <c r="I16" s="6"/>
       <c r="M16" s="14" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="N16" s="102">
         <v>7.9166666666666663E-2</v>
@@ -46307,19 +46367,19 @@
         <v>15</v>
       </c>
       <c r="C17" s="73" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D17" s="73">
         <v>2017</v>
       </c>
       <c r="E17" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F17" s="74" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G17" s="74" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H17" s="75">
         <v>4.4444444444444446E-2</v>
@@ -46341,33 +46401,33 @@
         <v>16</v>
       </c>
       <c r="C18" s="54" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D18" s="54">
         <v>2024</v>
       </c>
       <c r="E18" s="153" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F18" s="69" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G18" s="69" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H18" s="60">
         <v>2.6659722222222224</v>
       </c>
       <c r="I18" s="6"/>
-      <c r="J18" s="170" t="s">
+      <c r="J18" s="171" t="s">
+        <v>289</v>
+      </c>
+      <c r="K18" s="172"/>
+      <c r="L18" s="136"/>
+      <c r="M18" s="171" t="s">
         <v>290</v>
       </c>
-      <c r="K18" s="171"/>
-      <c r="L18" s="136"/>
-      <c r="M18" s="170" t="s">
-        <v>291</v>
-      </c>
-      <c r="N18" s="171"/>
+      <c r="N18" s="172"/>
       <c r="O18" s="39"/>
       <c r="P18" s="39"/>
       <c r="Q18" s="39"/>
@@ -46384,33 +46444,33 @@
         <v>17</v>
       </c>
       <c r="C19" s="73" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D19" s="73">
         <v>2002</v>
       </c>
       <c r="E19" s="152" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F19" s="74" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G19" s="74" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H19" s="75">
         <v>0.68055555555555558</v>
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="122" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K19" s="132">
         <v>0.23194444444444445</v>
       </c>
       <c r="L19" s="137"/>
       <c r="M19" s="131" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="N19" s="72">
         <v>0.21666666666666667</v>
@@ -46431,33 +46491,33 @@
         <v>18</v>
       </c>
       <c r="C20" s="54" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D20" s="54">
         <v>2024</v>
       </c>
       <c r="E20" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F20" s="69" t="s">
         <v>73</v>
       </c>
       <c r="G20" s="69" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H20" s="60">
         <v>0.83194444444444449</v>
       </c>
       <c r="I20" s="6"/>
       <c r="J20" s="113" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K20" s="133">
         <v>4.791666666666667E-2</v>
       </c>
       <c r="L20" s="137"/>
       <c r="M20" s="101" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="N20" s="60">
         <v>0.11944444444444445</v>
@@ -46478,19 +46538,19 @@
         <v>19</v>
       </c>
       <c r="C21" s="73" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D21" s="73">
         <v>2016</v>
       </c>
       <c r="E21" s="152" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F21" s="74" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G21" s="74" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H21" s="75">
         <v>0.42222222222222222</v>
@@ -46500,7 +46560,7 @@
       <c r="K21" s="138"/>
       <c r="L21" s="163"/>
       <c r="M21" s="135" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="N21" s="77">
         <v>2.7777777777777776E-2</v>
@@ -46510,13 +46570,13 @@
         <v>31</v>
       </c>
       <c r="Q21" s="91" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R21" s="91" t="s">
-        <v>121</v>
+        <v>676</v>
       </c>
       <c r="S21" s="92" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="T21" s="39"/>
       <c r="U21" s="88" t="s">
@@ -46533,22 +46593,22 @@
         <v>20</v>
       </c>
       <c r="C22" s="54" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D22" s="54">
         <v>2024</v>
       </c>
       <c r="E22" s="153" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F22" s="69" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G22" s="69" t="s">
+        <v>534</v>
+      </c>
+      <c r="H22" s="60" t="s">
         <v>535</v>
-      </c>
-      <c r="H22" s="60" t="s">
-        <v>536</v>
       </c>
       <c r="I22" s="6"/>
       <c r="O22" s="39"/>
@@ -46569,7 +46629,7 @@
       </c>
       <c r="T22" s="39"/>
       <c r="U22" s="104" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V22" s="146"/>
       <c r="W22" s="147">
@@ -46586,33 +46646,33 @@
         <v>21</v>
       </c>
       <c r="C23" s="73" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D23" s="73">
         <v>2004</v>
       </c>
       <c r="E23" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F23" s="74" t="s">
+        <v>536</v>
+      </c>
+      <c r="G23" s="74" t="s">
         <v>537</v>
-      </c>
-      <c r="G23" s="74" t="s">
-        <v>538</v>
       </c>
       <c r="H23" s="75">
         <v>1.8131944444444446</v>
       </c>
       <c r="I23" s="6"/>
-      <c r="J23" s="170" t="s">
+      <c r="J23" s="171" t="s">
+        <v>291</v>
+      </c>
+      <c r="K23" s="172"/>
+      <c r="L23" s="136"/>
+      <c r="M23" s="171" t="s">
         <v>292</v>
       </c>
-      <c r="K23" s="171"/>
-      <c r="L23" s="136"/>
-      <c r="M23" s="170" t="s">
-        <v>293</v>
-      </c>
-      <c r="N23" s="171"/>
+      <c r="N23" s="172"/>
       <c r="O23" s="39"/>
       <c r="P23" s="94" t="s">
         <v>33</v>
@@ -46631,7 +46691,7 @@
       </c>
       <c r="T23" s="39"/>
       <c r="U23" s="98" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="V23" s="146"/>
       <c r="W23" s="147">
@@ -46648,33 +46708,33 @@
         <v>22</v>
       </c>
       <c r="C24" s="54" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D24" s="54">
         <v>2006</v>
       </c>
       <c r="E24" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F24" s="69" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G24" s="69" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H24" s="60">
         <v>2.8166666666666664</v>
       </c>
       <c r="I24" s="39"/>
       <c r="J24" s="122" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="K24" s="132">
         <v>0.11180555555555556</v>
       </c>
       <c r="L24" s="137"/>
       <c r="M24" s="131" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="N24" s="72">
         <v>6.6666666666666666E-2</v>
@@ -46697,7 +46757,7 @@
       </c>
       <c r="T24" s="39"/>
       <c r="U24" s="99" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="V24" s="146"/>
       <c r="W24" s="147">
@@ -46712,33 +46772,33 @@
         <v>23</v>
       </c>
       <c r="C25" s="80" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D25" s="80">
         <v>2007</v>
       </c>
       <c r="E25" s="165" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F25" s="80" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G25" s="80" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H25" s="82">
         <v>1.85</v>
       </c>
       <c r="I25" s="39"/>
       <c r="J25" s="113" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K25" s="133">
         <v>7.5694444444444439E-2</v>
       </c>
       <c r="L25" s="137"/>
       <c r="M25" s="101" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N25" s="60">
         <v>4.9305555555555554E-2</v>
@@ -46761,7 +46821,7 @@
       </c>
       <c r="T25" s="39"/>
       <c r="U25" s="98" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="V25" s="146"/>
       <c r="W25" s="147">
@@ -46776,19 +46836,19 @@
         <v>24</v>
       </c>
       <c r="C26" s="54" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D26" s="54">
         <v>2024</v>
       </c>
       <c r="E26" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F26" s="69" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G26" s="69" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H26" s="60">
         <v>0.1</v>
@@ -46802,7 +46862,7 @@
       </c>
       <c r="L26" s="137"/>
       <c r="M26" s="135" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="N26" s="77">
         <v>0.51944444444444449</v>
@@ -46825,7 +46885,7 @@
       </c>
       <c r="T26" s="39"/>
       <c r="U26" s="99" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="V26" s="146"/>
       <c r="W26" s="147">
@@ -46840,26 +46900,26 @@
         <v>25</v>
       </c>
       <c r="C27" s="73" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D27" s="73">
         <v>2024</v>
       </c>
       <c r="E27" s="152" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F27" s="74" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G27" s="74" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H27" s="75">
         <v>1.0965277777777778</v>
       </c>
       <c r="I27" s="39"/>
       <c r="J27" s="14" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K27" s="102">
         <v>0.25208333333333333</v>
@@ -46882,7 +46942,7 @@
       </c>
       <c r="T27" s="39"/>
       <c r="U27" s="98" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="V27" s="146"/>
       <c r="W27" s="147">
@@ -46897,19 +46957,19 @@
         <v>26</v>
       </c>
       <c r="C28" s="54" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D28" s="54">
         <v>2022</v>
       </c>
       <c r="E28" s="153" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F28" s="69" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G28" s="69" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H28" s="60">
         <v>2.1729166666666666</v>
@@ -46933,7 +46993,7 @@
       </c>
       <c r="T28" s="39"/>
       <c r="U28" s="99" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="V28" s="146"/>
       <c r="W28" s="147">
@@ -46950,33 +47010,33 @@
         <v>27</v>
       </c>
       <c r="C29" s="73" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D29" s="73">
         <v>2024</v>
       </c>
       <c r="E29" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F29" s="74" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G29" s="74" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H29" s="75">
         <v>0.11527777777777778</v>
       </c>
       <c r="I29" s="39"/>
-      <c r="J29" s="170" t="s">
+      <c r="J29" s="171" t="s">
+        <v>293</v>
+      </c>
+      <c r="K29" s="172"/>
+      <c r="L29" s="136"/>
+      <c r="M29" s="171" t="s">
         <v>294</v>
       </c>
-      <c r="K29" s="171"/>
-      <c r="L29" s="136"/>
-      <c r="M29" s="170" t="s">
-        <v>295</v>
-      </c>
-      <c r="N29" s="171"/>
+      <c r="N29" s="172"/>
       <c r="O29" s="39"/>
       <c r="P29" s="94" t="s">
         <v>39</v>
@@ -46995,7 +47055,7 @@
       </c>
       <c r="T29" s="39"/>
       <c r="U29" s="98" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="V29" s="146"/>
       <c r="W29" s="111">
@@ -47012,33 +47072,33 @@
         <v>28</v>
       </c>
       <c r="C30" s="54" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D30" s="54">
         <v>2024</v>
       </c>
       <c r="E30" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F30" s="69" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G30" s="69" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H30" s="60">
         <v>0.63194444444444442</v>
       </c>
       <c r="I30" s="39"/>
       <c r="J30" s="122" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K30" s="132">
         <v>0.18472222222222223</v>
       </c>
       <c r="L30" s="137"/>
       <c r="M30" s="122" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="N30" s="72">
         <v>0.17847222222222223</v>
@@ -47061,7 +47121,7 @@
       </c>
       <c r="T30" s="39"/>
       <c r="U30" s="99" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="V30" s="146"/>
       <c r="W30" s="147">
@@ -47078,33 +47138,33 @@
         <v>29</v>
       </c>
       <c r="C31" s="73" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D31" s="73">
         <v>2022</v>
       </c>
       <c r="E31" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F31" s="74" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G31" s="74" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H31" s="75">
         <v>0.39861111111111114</v>
       </c>
       <c r="I31" s="39"/>
       <c r="J31" s="113" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K31" s="133">
         <v>0.47083333333333333</v>
       </c>
       <c r="L31" s="137"/>
       <c r="M31" s="101" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="N31" s="60">
         <v>5.1388888888888887E-2</v>
@@ -47127,7 +47187,7 @@
       </c>
       <c r="T31" s="39"/>
       <c r="U31" s="98" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="V31" s="146"/>
       <c r="W31" s="147">
@@ -47149,14 +47209,14 @@
       <c r="H32" s="138"/>
       <c r="I32" s="39"/>
       <c r="J32" s="112" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K32" s="75">
         <v>5.0694444444444445E-2</v>
       </c>
       <c r="L32" s="137"/>
       <c r="M32" s="112" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="N32" s="75">
         <v>1.3708333333333333</v>
@@ -47179,7 +47239,7 @@
       </c>
       <c r="T32" s="39"/>
       <c r="U32" s="99" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="V32" s="146"/>
       <c r="W32" s="147">
@@ -47201,13 +47261,13 @@
       <c r="H33" s="61"/>
       <c r="I33" s="39"/>
       <c r="J33" s="14" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K33" s="102">
         <v>0.2298611111111111</v>
       </c>
       <c r="M33" s="114" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N33" s="60">
         <v>2.7777777777777776E-2</v>
@@ -47229,10 +47289,10 @@
         <v>4.8763888888888891</v>
       </c>
       <c r="T33" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="U33" s="166" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="V33" s="39"/>
       <c r="W33" s="147">
@@ -47251,7 +47311,7 @@
       <c r="H34" s="61"/>
       <c r="I34" s="39"/>
       <c r="M34" s="135" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="N34" s="77">
         <v>0.15</v>
@@ -47308,9 +47368,9 @@
       <c r="H36" s="61"/>
       <c r="I36" s="39"/>
       <c r="O36" s="39"/>
-      <c r="P36" s="172"/>
-      <c r="Q36" s="172"/>
-      <c r="R36" s="172"/>
+      <c r="P36" s="170"/>
+      <c r="Q36" s="170"/>
+      <c r="R36" s="170"/>
       <c r="S36" s="111"/>
       <c r="T36" s="16"/>
       <c r="U36" s="16"/>
@@ -47329,8 +47389,8 @@
       <c r="I37" s="39"/>
       <c r="O37" s="39"/>
       <c r="P37" s="175"/>
-      <c r="Q37" s="172"/>
-      <c r="R37" s="172"/>
+      <c r="Q37" s="170"/>
+      <c r="R37" s="170"/>
       <c r="S37" s="111"/>
       <c r="T37" s="16"/>
       <c r="U37" s="16"/>
@@ -47348,9 +47408,9 @@
       <c r="H38" s="61"/>
       <c r="I38" s="39"/>
       <c r="O38" s="39"/>
-      <c r="P38" s="172"/>
-      <c r="Q38" s="172"/>
-      <c r="R38" s="172"/>
+      <c r="P38" s="170"/>
+      <c r="Q38" s="170"/>
+      <c r="R38" s="170"/>
       <c r="S38" s="111"/>
       <c r="T38" s="16"/>
       <c r="U38" s="16"/>
@@ -47368,9 +47428,9 @@
       <c r="H39" s="61"/>
       <c r="I39" s="39"/>
       <c r="O39" s="39"/>
-      <c r="P39" s="172"/>
-      <c r="Q39" s="172"/>
-      <c r="R39" s="172"/>
+      <c r="P39" s="170"/>
+      <c r="Q39" s="170"/>
+      <c r="R39" s="170"/>
       <c r="S39" s="124"/>
       <c r="T39" s="16"/>
       <c r="U39" s="16"/>
@@ -47388,9 +47448,9 @@
       <c r="H40" s="62"/>
       <c r="I40" s="39"/>
       <c r="O40" s="39"/>
-      <c r="P40" s="172"/>
-      <c r="Q40" s="172"/>
-      <c r="R40" s="172"/>
+      <c r="P40" s="170"/>
+      <c r="Q40" s="170"/>
+      <c r="R40" s="170"/>
       <c r="S40" s="124"/>
       <c r="T40" s="16"/>
       <c r="U40" s="16"/>
@@ -47408,9 +47468,9 @@
       <c r="H41" s="61"/>
       <c r="I41" s="39"/>
       <c r="O41" s="39"/>
-      <c r="P41" s="172"/>
-      <c r="Q41" s="172"/>
-      <c r="R41" s="172"/>
+      <c r="P41" s="170"/>
+      <c r="Q41" s="170"/>
+      <c r="R41" s="170"/>
       <c r="S41" s="124"/>
       <c r="T41" s="16"/>
       <c r="U41" s="16"/>
@@ -49253,7 +49313,7 @@
       <c r="H116" s="62"/>
       <c r="I116" s="39"/>
       <c r="J116" s="129" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K116" s="111"/>
       <c r="L116" s="111"/>
@@ -49265,7 +49325,7 @@
         <v>77</v>
       </c>
       <c r="R116" s="56" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S116" s="39"/>
       <c r="T116" s="39"/>
@@ -49284,7 +49344,7 @@
       <c r="H117" s="62"/>
       <c r="I117" s="39"/>
       <c r="J117" s="129" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K117" s="111"/>
       <c r="L117" s="111"/>
@@ -50276,7 +50336,7 @@
       <c r="O150" s="39"/>
       <c r="P150" s="39"/>
       <c r="Q150" s="41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R150" s="42">
         <f>SUM(R118:R149)</f>
@@ -50365,11 +50425,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="P37:R37"/>
-    <mergeCell ref="P41:R41"/>
-    <mergeCell ref="P39:R39"/>
-    <mergeCell ref="P40:R40"/>
-    <mergeCell ref="P38:R38"/>
     <mergeCell ref="J23:K23"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="M2:N2"/>
@@ -50383,6 +50438,11 @@
     <mergeCell ref="M23:N23"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="J29:K29"/>
+    <mergeCell ref="P37:R37"/>
+    <mergeCell ref="P41:R41"/>
+    <mergeCell ref="P39:R39"/>
+    <mergeCell ref="P40:R40"/>
+    <mergeCell ref="P38:R38"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <hyperlinks>
@@ -50464,7 +50524,7 @@
         <v>77</v>
       </c>
       <c r="E2" s="86" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F2" s="86" t="s">
         <v>12</v>
@@ -50476,15 +50536,15 @@
         <v>20</v>
       </c>
       <c r="I2" s="6"/>
-      <c r="J2" s="170" t="s">
+      <c r="J2" s="171" t="s">
+        <v>283</v>
+      </c>
+      <c r="K2" s="172"/>
+      <c r="L2" s="136"/>
+      <c r="M2" s="171" t="s">
         <v>284</v>
       </c>
-      <c r="K2" s="171"/>
-      <c r="L2" s="136"/>
-      <c r="M2" s="170" t="s">
-        <v>285</v>
-      </c>
-      <c r="N2" s="171"/>
+      <c r="N2" s="172"/>
       <c r="O2" s="39"/>
       <c r="P2" s="39"/>
       <c r="Q2" s="39"/>
@@ -50501,33 +50561,33 @@
         <v>1</v>
       </c>
       <c r="C3" s="73" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D3" s="73">
         <v>2024</v>
       </c>
       <c r="E3" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F3" s="74" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G3" s="74" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H3" s="75">
         <v>0.81666666666666665</v>
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="168" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="K3" s="72">
         <v>7.2916666666666671E-2</v>
       </c>
       <c r="L3" s="137"/>
       <c r="M3" s="131" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N3" s="72">
         <v>2.1527777777777778E-2</v>
@@ -50548,33 +50608,33 @@
         <v>2</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D4" s="54">
         <v>2020</v>
       </c>
       <c r="E4" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F4" s="69" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G4" s="69" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H4" s="60">
         <v>0.1388888888888889</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="114" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="K4" s="60">
         <v>0.76875000000000004</v>
       </c>
       <c r="L4" s="137"/>
       <c r="M4" s="101" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="N4" s="60">
         <v>0.27430555555555558</v>
@@ -50595,16 +50655,16 @@
         <v>3</v>
       </c>
       <c r="C5" s="73" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D5" s="73">
         <v>2011</v>
       </c>
       <c r="E5" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F5" s="74" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G5" s="74" t="s">
         <v>13</v>
@@ -50614,14 +50674,14 @@
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="135" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K5" s="77">
         <v>0.11666666666666667</v>
       </c>
       <c r="L5" s="163"/>
       <c r="M5" s="135" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="N5" s="77">
         <v>2.7083333333333334E-2</v>
@@ -50642,19 +50702,19 @@
         <v>4</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D6" s="54">
         <v>2022</v>
       </c>
       <c r="E6" s="153" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G6" s="69" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H6" s="60">
         <v>1.0118055555555556</v>
@@ -50676,33 +50736,33 @@
         <v>5</v>
       </c>
       <c r="C7" s="73" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D7" s="73">
         <v>1998</v>
       </c>
       <c r="E7" s="152" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F7" s="74" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G7" s="74" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H7" s="75">
         <v>2.5249999999999999</v>
       </c>
       <c r="I7" s="6"/>
-      <c r="J7" s="170" t="s">
+      <c r="J7" s="171" t="s">
+        <v>285</v>
+      </c>
+      <c r="K7" s="172"/>
+      <c r="L7" s="136"/>
+      <c r="M7" s="171" t="s">
         <v>286</v>
       </c>
-      <c r="K7" s="171"/>
-      <c r="L7" s="136"/>
-      <c r="M7" s="170" t="s">
-        <v>287</v>
-      </c>
-      <c r="N7" s="171"/>
+      <c r="N7" s="172"/>
       <c r="O7" s="39"/>
       <c r="P7" s="39"/>
       <c r="Q7" s="39"/>
@@ -50719,33 +50779,33 @@
         <v>6</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D8" s="54">
         <v>2023</v>
       </c>
       <c r="E8" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G8" s="69" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H8" s="60">
         <v>0.35416666666666669</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="168" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K8" s="72">
         <v>0.61250000000000004</v>
       </c>
       <c r="L8" s="137"/>
       <c r="M8" s="131" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="N8" s="72">
         <v>0.47986111111111113</v>
@@ -50766,19 +50826,19 @@
         <v>7</v>
       </c>
       <c r="C9" s="73" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D9" s="73">
         <v>2025</v>
       </c>
       <c r="E9" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F9" s="74" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G9" s="74" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H9" s="75">
         <v>0.1125</v>
@@ -50788,7 +50848,7 @@
       <c r="K9" s="60"/>
       <c r="L9" s="137"/>
       <c r="M9" s="101" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N9" s="60">
         <v>0.43680555555555556</v>
@@ -50809,19 +50869,19 @@
         <v>8</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D10" s="54">
         <v>2008</v>
       </c>
       <c r="E10" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G10" s="69" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H10" s="60">
         <v>0.97291666666666665</v>
@@ -50848,16 +50908,16 @@
         <v>9</v>
       </c>
       <c r="C11" s="73" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D11" s="73">
         <v>2004</v>
       </c>
       <c r="E11" s="152" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F11" s="74" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G11" s="74">
         <v>45768</v>
@@ -50882,33 +50942,33 @@
         <v>10</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D12" s="54">
         <v>2024</v>
       </c>
       <c r="E12" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F12" s="69" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G12" s="69" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H12" s="60">
         <v>1.8055555555555554E-2</v>
       </c>
       <c r="I12" s="6"/>
-      <c r="J12" s="170" t="s">
+      <c r="J12" s="171" t="s">
+        <v>287</v>
+      </c>
+      <c r="K12" s="172"/>
+      <c r="L12" s="136"/>
+      <c r="M12" s="171" t="s">
         <v>288</v>
       </c>
-      <c r="K12" s="171"/>
-      <c r="L12" s="136"/>
-      <c r="M12" s="170" t="s">
-        <v>289</v>
-      </c>
-      <c r="N12" s="171"/>
+      <c r="N12" s="172"/>
       <c r="O12" s="39"/>
       <c r="P12" s="39"/>
       <c r="Q12" s="39"/>
@@ -50925,33 +50985,33 @@
         <v>11</v>
       </c>
       <c r="C13" s="73" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D13" s="73">
         <v>2025</v>
       </c>
       <c r="E13" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F13" s="74" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G13" s="74" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H13" s="75">
         <v>2.1256944444444446</v>
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="168" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="K13" s="72">
         <v>0.65694444444444444</v>
       </c>
       <c r="L13" s="137"/>
       <c r="M13" s="131" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="N13" s="72">
         <v>0.22638888888888889</v>
@@ -50972,33 +51032,33 @@
         <v>12</v>
       </c>
       <c r="C14" s="54" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D14" s="54">
         <v>2011</v>
       </c>
       <c r="E14" s="153" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F14" s="69" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G14" s="69" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H14" s="60">
         <v>0.57361111111111107</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="114" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K14" s="60">
         <v>0.27291666666666664</v>
       </c>
       <c r="L14" s="137"/>
       <c r="M14" s="101" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="N14" s="60">
         <v>0.12916666666666668</v>
@@ -51019,19 +51079,19 @@
         <v>13</v>
       </c>
       <c r="C15" s="73" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D15" s="73">
         <v>2007</v>
       </c>
       <c r="E15" s="152" t="s">
+        <v>591</v>
+      </c>
+      <c r="F15" s="74" t="s">
         <v>592</v>
       </c>
-      <c r="F15" s="74" t="s">
-        <v>593</v>
-      </c>
       <c r="G15" s="74" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H15" s="75">
         <v>0.67569444444444449</v>
@@ -51041,7 +51101,7 @@
       <c r="K15" s="77"/>
       <c r="L15" s="163"/>
       <c r="M15" s="135" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N15" s="77">
         <v>9.4444444444444442E-2</v>
@@ -51062,16 +51122,16 @@
         <v>14</v>
       </c>
       <c r="C16" s="54" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D16" s="54">
         <v>1999</v>
       </c>
       <c r="E16" s="153" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F16" s="69" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G16" s="69" t="s">
         <v>51</v>
@@ -51097,33 +51157,33 @@
         <v>15</v>
       </c>
       <c r="C17" s="73" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D17" s="73">
         <v>2025</v>
       </c>
       <c r="E17" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F17" s="74" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G17" s="74" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H17" s="75">
         <v>0.30902777777777779</v>
       </c>
       <c r="I17" s="6"/>
-      <c r="J17" s="170" t="s">
+      <c r="J17" s="171" t="s">
+        <v>289</v>
+      </c>
+      <c r="K17" s="172"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="171" t="s">
         <v>290</v>
       </c>
-      <c r="K17" s="171"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="170" t="s">
-        <v>291</v>
-      </c>
-      <c r="N17" s="171"/>
+      <c r="N17" s="172"/>
       <c r="O17" s="39"/>
       <c r="P17" s="39"/>
       <c r="Q17" s="39"/>
@@ -51140,16 +51200,16 @@
         <v>16</v>
       </c>
       <c r="C18" s="54" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D18" s="54">
         <v>2025</v>
       </c>
       <c r="E18" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F18" s="69" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G18" s="69" t="s">
         <v>102</v>
@@ -51159,14 +51219,14 @@
       </c>
       <c r="I18" s="6"/>
       <c r="J18" s="168" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="K18" s="72">
         <v>0.79513888888888884</v>
       </c>
       <c r="L18" s="137"/>
       <c r="M18" s="168" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="N18" s="72">
         <v>0.65</v>
@@ -51187,33 +51247,33 @@
         <v>17</v>
       </c>
       <c r="C19" s="73" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D19" s="73">
         <v>2025</v>
       </c>
       <c r="E19" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F19" s="74" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G19" s="74" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H19" s="75">
         <v>1.3368055555555556</v>
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="114" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K19" s="60">
         <v>0.28749999999999998</v>
       </c>
       <c r="L19" s="137"/>
       <c r="M19" s="114" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="N19" s="60">
         <v>0.27500000000000002</v>
@@ -51234,19 +51294,19 @@
         <v>18</v>
       </c>
       <c r="C20" s="54" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D20" s="54">
         <v>2024</v>
       </c>
       <c r="E20" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F20" s="69" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G20" s="69" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H20" s="60">
         <v>0.2</v>
@@ -51273,19 +51333,19 @@
         <v>19</v>
       </c>
       <c r="C21" s="73" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D21" s="73">
         <v>2023</v>
       </c>
       <c r="E21" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F21" s="74" t="s">
         <v>54</v>
       </c>
       <c r="G21" s="74" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H21" s="75">
         <v>0.5</v>
@@ -51301,13 +51361,13 @@
         <v>31</v>
       </c>
       <c r="Q21" s="91" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R21" s="91" t="s">
-        <v>121</v>
+        <v>676</v>
       </c>
       <c r="S21" s="92" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="T21" s="39"/>
       <c r="U21" s="88" t="s">
@@ -51324,16 +51384,16 @@
         <v>20</v>
       </c>
       <c r="C22" s="54" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D22" s="54">
         <v>2017</v>
       </c>
       <c r="E22" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F22" s="69" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G22" s="69">
         <v>45847</v>
@@ -51343,13 +51403,13 @@
         <v>2.0166666666666666</v>
       </c>
       <c r="I22" s="6"/>
-      <c r="J22" s="170" t="s">
-        <v>292</v>
-      </c>
-      <c r="K22" s="171"/>
+      <c r="J22" s="171" t="s">
+        <v>291</v>
+      </c>
+      <c r="K22" s="172"/>
       <c r="L22" s="136"/>
       <c r="M22" s="173" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N22" s="174"/>
       <c r="O22" s="39"/>
@@ -51370,7 +51430,7 @@
       </c>
       <c r="T22" s="39"/>
       <c r="U22" s="104" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="V22" s="146"/>
       <c r="W22" s="147">
@@ -51385,33 +51445,33 @@
         <v>21</v>
       </c>
       <c r="C23" s="73" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D23" s="73">
         <v>2006</v>
       </c>
       <c r="E23" s="152" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F23" s="74" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G23" s="74" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H23" s="75">
         <v>0.5229166666666667</v>
       </c>
       <c r="I23" s="6"/>
       <c r="J23" s="168" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="K23" s="72">
         <v>0.81319444444444444</v>
       </c>
       <c r="L23" s="140"/>
       <c r="M23" s="121" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="N23" s="59">
         <v>0.38611111111111113</v>
@@ -51434,7 +51494,7 @@
       </c>
       <c r="T23" s="39"/>
       <c r="U23" s="98" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="V23" s="146"/>
       <c r="W23" s="147">
@@ -51449,16 +51509,16 @@
         <v>22</v>
       </c>
       <c r="C24" s="54" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D24" s="54">
         <v>2008</v>
       </c>
       <c r="E24" s="153" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F24" s="69" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G24" s="69" t="s">
         <v>60</v>
@@ -51494,7 +51554,7 @@
       </c>
       <c r="T24" s="39"/>
       <c r="U24" s="99" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="V24" s="146"/>
       <c r="W24" s="147">
@@ -51511,19 +51571,19 @@
         <v>23</v>
       </c>
       <c r="C25" s="73" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D25" s="73">
         <v>2025</v>
       </c>
       <c r="E25" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F25" s="74" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G25" s="74" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H25" s="75">
         <v>9.0277777777777769E-3</v>
@@ -51533,7 +51593,7 @@
       <c r="K25" s="77"/>
       <c r="L25" s="163"/>
       <c r="M25" s="101" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="N25" s="60">
         <v>0.12708333333333333</v>
@@ -51556,7 +51616,7 @@
       </c>
       <c r="T25" s="39"/>
       <c r="U25" s="98" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="V25" s="146"/>
       <c r="W25" s="147">
@@ -51575,16 +51635,16 @@
         <v>24</v>
       </c>
       <c r="C26" s="54" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D26" s="54">
         <v>2007</v>
       </c>
       <c r="E26" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F26" s="69" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G26" s="69" t="s">
         <v>65</v>
@@ -51594,7 +51654,7 @@
       </c>
       <c r="I26" s="39"/>
       <c r="M26" s="169" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N26" s="75">
         <v>7.9861111111111105E-2</v>
@@ -51617,7 +51677,7 @@
       </c>
       <c r="T26" s="39"/>
       <c r="U26" s="100" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="V26" s="146"/>
       <c r="W26" s="147">
@@ -51636,26 +51696,26 @@
         <v>25</v>
       </c>
       <c r="C27" s="73" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D27" s="73">
         <v>2010</v>
       </c>
       <c r="E27" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F27" s="74" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G27" s="74" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H27" s="75">
         <v>2.3708333333333331</v>
       </c>
       <c r="I27" s="39"/>
       <c r="M27" s="14" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="N27" s="102">
         <v>4.1666666666666664E-2</v>
@@ -51678,7 +51738,7 @@
       </c>
       <c r="T27" s="39"/>
       <c r="U27" s="98" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="V27" s="146"/>
       <c r="W27" s="147">
@@ -51695,19 +51755,19 @@
         <v>26</v>
       </c>
       <c r="C28" s="54" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D28" s="54">
         <v>2025</v>
       </c>
       <c r="E28" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F28" s="69" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G28" s="69" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H28" s="60">
         <v>2.2124999999999999</v>
@@ -51731,7 +51791,7 @@
       </c>
       <c r="T28" s="39"/>
       <c r="U28" s="99" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="V28" s="146"/>
       <c r="W28" s="147">
@@ -51748,16 +51808,16 @@
         <v>27</v>
       </c>
       <c r="C29" s="73" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D29" s="73">
         <v>2025</v>
       </c>
       <c r="E29" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F29" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G29" s="74" t="s">
         <v>82</v>
@@ -51766,15 +51826,15 @@
         <v>0.35</v>
       </c>
       <c r="I29" s="39"/>
-      <c r="J29" s="170" t="s">
+      <c r="J29" s="171" t="s">
+        <v>293</v>
+      </c>
+      <c r="K29" s="172"/>
+      <c r="L29" s="136"/>
+      <c r="M29" s="171" t="s">
         <v>294</v>
       </c>
-      <c r="K29" s="171"/>
-      <c r="L29" s="136"/>
-      <c r="M29" s="170" t="s">
-        <v>295</v>
-      </c>
-      <c r="N29" s="171"/>
+      <c r="N29" s="172"/>
       <c r="O29" s="39"/>
       <c r="P29" s="94" t="s">
         <v>39</v>
@@ -51793,7 +51853,7 @@
       </c>
       <c r="T29" s="39"/>
       <c r="U29" s="98" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="V29" s="146"/>
       <c r="W29" s="111">
@@ -51810,33 +51870,33 @@
         <v>28</v>
       </c>
       <c r="C30" s="54" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D30" s="54">
         <v>2025</v>
       </c>
       <c r="E30" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F30" s="69" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G30" s="69" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H30" s="60">
         <v>2.2833333333333332</v>
       </c>
       <c r="I30" s="39"/>
       <c r="J30" s="168" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="K30" s="72">
         <v>0.58750000000000002</v>
       </c>
       <c r="L30" s="137"/>
       <c r="M30" s="131" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="N30" s="72">
         <v>0.19166666666666668</v>
@@ -51859,7 +51919,7 @@
       </c>
       <c r="T30" s="39"/>
       <c r="U30" s="99" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="V30" s="146"/>
       <c r="W30" s="147">
@@ -51876,33 +51936,33 @@
         <v>29</v>
       </c>
       <c r="C31" s="73" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D31" s="73">
         <v>2010</v>
       </c>
       <c r="E31" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F31" s="74" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G31" s="74" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H31" s="75">
         <v>0.54166666666666663</v>
       </c>
       <c r="I31" s="39"/>
       <c r="J31" s="114" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K31" s="60">
         <v>0.33402777777777776</v>
       </c>
       <c r="L31" s="137"/>
       <c r="M31" s="101" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="N31" s="60">
         <v>7.013888888888889E-2</v>
@@ -51925,7 +51985,7 @@
       </c>
       <c r="T31" s="39"/>
       <c r="U31" s="98" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="V31" s="146"/>
       <c r="W31" s="147">
@@ -51942,19 +52002,19 @@
         <v>30</v>
       </c>
       <c r="C32" s="54" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D32" s="54">
         <v>2007</v>
       </c>
       <c r="E32" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F32" s="69" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G32" s="69" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H32" s="60">
         <v>0.39513888888888887</v>
@@ -51983,7 +52043,7 @@
       </c>
       <c r="T32" s="39"/>
       <c r="U32" s="99" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="V32" s="146"/>
       <c r="W32" s="147">
@@ -52000,19 +52060,19 @@
         <v>31</v>
       </c>
       <c r="C33" s="73" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D33" s="73">
         <v>2025</v>
       </c>
       <c r="E33" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F33" s="74" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G33" s="74" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H33" s="75">
         <v>2.4</v>
@@ -52039,10 +52099,10 @@
         <v>3.1520833333333331</v>
       </c>
       <c r="T33" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="U33" s="128" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="V33" s="39"/>
       <c r="W33" s="147">
@@ -52058,19 +52118,19 @@
         <v>32</v>
       </c>
       <c r="C34" s="54" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D34" s="54">
         <v>2013</v>
       </c>
       <c r="E34" s="153" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F34" s="69" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G34" s="69" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H34" s="60">
         <v>0.50138888888888888</v>
@@ -52105,13 +52165,13 @@
         <v>33</v>
       </c>
       <c r="C35" s="73" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D35" s="73">
         <v>2024</v>
       </c>
       <c r="E35" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F35" s="74" t="s">
         <v>105</v>
@@ -52139,28 +52199,28 @@
         <v>34</v>
       </c>
       <c r="C36" s="54" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D36" s="54">
         <v>2018</v>
       </c>
       <c r="E36" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F36" s="69" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G36" s="69" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H36" s="60">
         <v>0.21944444444444444</v>
       </c>
       <c r="I36" s="39"/>
       <c r="O36" s="39"/>
-      <c r="P36" s="172"/>
-      <c r="Q36" s="172"/>
-      <c r="R36" s="172"/>
+      <c r="P36" s="170"/>
+      <c r="Q36" s="170"/>
+      <c r="R36" s="170"/>
       <c r="S36" s="111"/>
       <c r="T36" s="16"/>
       <c r="U36" s="16"/>
@@ -52173,16 +52233,16 @@
         <v>35</v>
       </c>
       <c r="C37" s="73" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D37" s="73">
         <v>2002</v>
       </c>
       <c r="E37" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F37" s="74" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G37" s="74" t="s">
         <v>108</v>
@@ -52193,8 +52253,8 @@
       <c r="I37" s="39"/>
       <c r="O37" s="39"/>
       <c r="P37" s="175"/>
-      <c r="Q37" s="172"/>
-      <c r="R37" s="172"/>
+      <c r="Q37" s="170"/>
+      <c r="R37" s="170"/>
       <c r="S37" s="111"/>
       <c r="T37" s="16"/>
       <c r="U37" s="16"/>
@@ -52207,13 +52267,13 @@
         <v>36</v>
       </c>
       <c r="C38" s="54" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D38" s="54">
         <v>1999</v>
       </c>
       <c r="E38" s="153" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F38" s="69" t="s">
         <v>111</v>
@@ -52226,9 +52286,9 @@
       </c>
       <c r="I38" s="39"/>
       <c r="O38" s="39"/>
-      <c r="P38" s="172"/>
-      <c r="Q38" s="172"/>
-      <c r="R38" s="172"/>
+      <c r="P38" s="170"/>
+      <c r="Q38" s="170"/>
+      <c r="R38" s="170"/>
       <c r="S38" s="111"/>
       <c r="T38" s="16"/>
       <c r="U38" s="16"/>
@@ -52241,28 +52301,28 @@
         <v>37</v>
       </c>
       <c r="C39" s="73" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D39" s="73">
         <v>2003</v>
       </c>
       <c r="E39" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F39" s="74" t="s">
         <v>117</v>
       </c>
       <c r="G39" s="74" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H39" s="75">
         <v>0.22083333333333333</v>
       </c>
       <c r="I39" s="39"/>
       <c r="O39" s="39"/>
-      <c r="P39" s="172"/>
-      <c r="Q39" s="172"/>
-      <c r="R39" s="172"/>
+      <c r="P39" s="170"/>
+      <c r="Q39" s="170"/>
+      <c r="R39" s="170"/>
       <c r="S39" s="124"/>
       <c r="T39" s="16"/>
       <c r="U39" s="16"/>
@@ -52275,28 +52335,28 @@
         <v>38</v>
       </c>
       <c r="C40" s="54" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D40" s="54">
         <v>2025</v>
       </c>
       <c r="E40" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F40" s="69" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G40" s="69" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H40" s="60">
         <v>0.79166666666666663</v>
       </c>
       <c r="I40" s="39"/>
       <c r="O40" s="39"/>
-      <c r="P40" s="172"/>
-      <c r="Q40" s="172"/>
-      <c r="R40" s="172"/>
+      <c r="P40" s="170"/>
+      <c r="Q40" s="170"/>
+      <c r="R40" s="170"/>
       <c r="S40" s="124"/>
       <c r="T40" s="16"/>
       <c r="U40" s="16"/>
@@ -52309,28 +52369,28 @@
         <v>39</v>
       </c>
       <c r="C41" s="73" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D41" s="73">
         <v>2025</v>
       </c>
       <c r="E41" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F41" s="74" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G41" s="74" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H41" s="75">
         <v>0.8125</v>
       </c>
       <c r="I41" s="39"/>
       <c r="O41" s="39"/>
-      <c r="P41" s="172"/>
-      <c r="Q41" s="172"/>
-      <c r="R41" s="172"/>
+      <c r="P41" s="170"/>
+      <c r="Q41" s="170"/>
+      <c r="R41" s="170"/>
       <c r="S41" s="124"/>
       <c r="T41" s="16"/>
       <c r="U41" s="16"/>
@@ -54183,7 +54243,7 @@
         <v>77</v>
       </c>
       <c r="R116" s="56" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S116" s="39"/>
       <c r="T116" s="39"/>
@@ -55199,7 +55259,7 @@
       <c r="O150" s="39"/>
       <c r="P150" s="39"/>
       <c r="Q150" s="41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R150" s="42">
         <f>SUM(R117:R149)</f>
@@ -55288,14 +55348,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="M12:N12"/>
     <mergeCell ref="J22:K22"/>
     <mergeCell ref="M22:N22"/>
     <mergeCell ref="J29:K29"/>
@@ -55306,6 +55358,14 @@
     <mergeCell ref="P38:R38"/>
     <mergeCell ref="P39:R39"/>
     <mergeCell ref="P40:R40"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="M12:N12"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55383,7 +55443,7 @@
         <v>77</v>
       </c>
       <c r="E2" s="86" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F2" s="86" t="s">
         <v>12</v>
@@ -55395,15 +55455,15 @@
         <v>20</v>
       </c>
       <c r="I2" s="6"/>
-      <c r="J2" s="170" t="s">
+      <c r="J2" s="171" t="s">
+        <v>283</v>
+      </c>
+      <c r="K2" s="172"/>
+      <c r="L2" s="136"/>
+      <c r="M2" s="171" t="s">
         <v>284</v>
       </c>
-      <c r="K2" s="171"/>
-      <c r="L2" s="136"/>
-      <c r="M2" s="170" t="s">
-        <v>285</v>
-      </c>
-      <c r="N2" s="171"/>
+      <c r="N2" s="172"/>
       <c r="O2" s="39"/>
       <c r="P2" s="39"/>
       <c r="Q2" s="39"/>
@@ -55420,33 +55480,33 @@
         <v>1</v>
       </c>
       <c r="C3" s="73" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D3" s="73">
         <v>2025</v>
       </c>
       <c r="E3" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F3" s="74" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G3" s="74" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H3" s="75">
         <v>0.8125</v>
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="168" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K3" s="72">
         <v>6.5972222222222224E-2</v>
       </c>
       <c r="L3" s="137"/>
       <c r="M3" s="112" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="N3" s="72">
         <v>0.17986111111111111</v>
@@ -55467,26 +55527,26 @@
         <v>2</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D4" s="54">
         <v>2013</v>
       </c>
       <c r="E4" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F4" s="69" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G4" s="69" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H4" s="60">
         <v>0.25694444444444442</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="114" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K4" s="60">
         <v>0.11874999999999999</v>
@@ -55510,19 +55570,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="73" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D5" s="73">
         <v>2013</v>
       </c>
       <c r="E5" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F5" s="74" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G5" s="74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H5" s="75">
         <v>0.39166666666666666</v>
@@ -55549,19 +55609,19 @@
         <v>4</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D6" s="54">
         <v>2005</v>
       </c>
       <c r="E6" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F6" s="69" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G6" s="69" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H6" s="60">
         <v>0.52500000000000002</v>
@@ -55583,33 +55643,33 @@
         <v>5</v>
       </c>
       <c r="C7" s="73" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D7" s="73">
         <v>2005</v>
       </c>
       <c r="E7" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F7" s="74" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G7" s="74" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H7" s="75">
         <v>0.88194444444444442</v>
       </c>
       <c r="I7" s="6"/>
-      <c r="J7" s="170" t="s">
+      <c r="J7" s="171" t="s">
+        <v>285</v>
+      </c>
+      <c r="K7" s="172"/>
+      <c r="L7" s="136"/>
+      <c r="M7" s="171" t="s">
         <v>286</v>
       </c>
-      <c r="K7" s="171"/>
-      <c r="L7" s="136"/>
-      <c r="M7" s="170" t="s">
-        <v>287</v>
-      </c>
-      <c r="N7" s="171"/>
+      <c r="N7" s="172"/>
       <c r="O7" s="39"/>
       <c r="P7" s="39"/>
       <c r="Q7" s="39"/>
@@ -55626,29 +55686,37 @@
         <v>6</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D8" s="54">
         <v>2011</v>
       </c>
       <c r="E8" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F8" s="69" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G8" s="69" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H8" s="60">
         <v>2.9958333333333331</v>
       </c>
       <c r="I8" s="6"/>
-      <c r="J8" s="168"/>
-      <c r="K8" s="72"/>
+      <c r="J8" s="168" t="s">
+        <v>666</v>
+      </c>
+      <c r="K8" s="72">
+        <v>2.2041666666666666</v>
+      </c>
       <c r="L8" s="137"/>
-      <c r="M8" s="131"/>
-      <c r="N8" s="72"/>
+      <c r="M8" s="131" t="s">
+        <v>464</v>
+      </c>
+      <c r="N8" s="72">
+        <v>0.24305555555555555</v>
+      </c>
       <c r="O8" s="39"/>
       <c r="P8" s="39"/>
       <c r="Q8" s="39"/>
@@ -55665,19 +55733,19 @@
         <v>7</v>
       </c>
       <c r="C9" s="73" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D9" s="73">
         <v>2013</v>
       </c>
       <c r="E9" s="152" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F9" s="74" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G9" s="74" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H9" s="75">
         <v>0.74513888888888891</v>
@@ -55686,8 +55754,12 @@
       <c r="J9" s="114"/>
       <c r="K9" s="60"/>
       <c r="L9" s="137"/>
-      <c r="M9" s="101"/>
-      <c r="N9" s="60"/>
+      <c r="M9" s="101" t="s">
+        <v>360</v>
+      </c>
+      <c r="N9" s="60">
+        <v>1.7041666666666666</v>
+      </c>
       <c r="O9" s="39"/>
       <c r="P9" s="39"/>
       <c r="Q9" s="39"/>
@@ -55704,19 +55776,23 @@
         <v>8</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D10" s="54">
         <v>1997</v>
       </c>
       <c r="E10" s="153" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F10" s="69" t="s">
-        <v>384</v>
-      </c>
-      <c r="G10" s="69"/>
-      <c r="H10" s="60"/>
+        <v>383</v>
+      </c>
+      <c r="G10" s="69" t="s">
+        <v>665</v>
+      </c>
+      <c r="H10" s="60">
+        <v>1.9319444444444445</v>
+      </c>
       <c r="I10" s="6"/>
       <c r="J10" s="135"/>
       <c r="K10" s="77"/>
@@ -55745,13 +55821,17 @@
         <v>2026</v>
       </c>
       <c r="E11" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F11" s="74" t="s">
-        <v>664</v>
-      </c>
-      <c r="G11" s="74"/>
-      <c r="H11" s="75"/>
+        <v>661</v>
+      </c>
+      <c r="G11" s="74" t="s">
+        <v>662</v>
+      </c>
+      <c r="H11" s="75">
+        <v>0.23749999999999999</v>
+      </c>
       <c r="I11" s="6"/>
       <c r="O11" s="39"/>
       <c r="P11" s="39"/>
@@ -55768,22 +55848,34 @@
       <c r="B12" s="78">
         <v>10</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="153"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="60"/>
+      <c r="C12" s="54" t="s">
+        <v>667</v>
+      </c>
+      <c r="D12" s="54">
+        <v>2025</v>
+      </c>
+      <c r="E12" s="153" t="s">
+        <v>439</v>
+      </c>
+      <c r="F12" s="69" t="s">
+        <v>395</v>
+      </c>
+      <c r="G12" s="69" t="s">
+        <v>668</v>
+      </c>
+      <c r="H12" s="60">
+        <v>0.26250000000000001</v>
+      </c>
       <c r="I12" s="6"/>
-      <c r="J12" s="170" t="s">
+      <c r="J12" s="171" t="s">
+        <v>287</v>
+      </c>
+      <c r="K12" s="172"/>
+      <c r="L12" s="136"/>
+      <c r="M12" s="171" t="s">
         <v>288</v>
       </c>
-      <c r="K12" s="171"/>
-      <c r="L12" s="136"/>
-      <c r="M12" s="170" t="s">
-        <v>289</v>
-      </c>
-      <c r="N12" s="171"/>
+      <c r="N12" s="172"/>
       <c r="O12" s="39"/>
       <c r="P12" s="39"/>
       <c r="Q12" s="39"/>
@@ -55799,14 +55891,28 @@
       <c r="B13" s="70">
         <v>11</v>
       </c>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="152"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="75"/>
+      <c r="C13" s="73" t="s">
+        <v>669</v>
+      </c>
+      <c r="D13" s="73">
+        <v>2025</v>
+      </c>
+      <c r="E13" s="152" t="s">
+        <v>439</v>
+      </c>
+      <c r="F13" s="74" t="s">
+        <v>668</v>
+      </c>
+      <c r="G13" s="74" t="s">
+        <v>298</v>
+      </c>
+      <c r="H13" s="75">
+        <v>1.0791666666666666</v>
+      </c>
       <c r="I13" s="6"/>
-      <c r="J13" s="168"/>
+      <c r="J13" s="168" t="s">
+        <v>666</v>
+      </c>
       <c r="K13" s="72"/>
       <c r="L13" s="137"/>
       <c r="M13" s="131"/>
@@ -55826,12 +55932,24 @@
       <c r="B14" s="78">
         <v>12</v>
       </c>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="153"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="60"/>
+      <c r="C14" s="54" t="s">
+        <v>671</v>
+      </c>
+      <c r="D14" s="54">
+        <v>1999</v>
+      </c>
+      <c r="E14" s="153" t="s">
+        <v>439</v>
+      </c>
+      <c r="F14" s="69" t="s">
+        <v>672</v>
+      </c>
+      <c r="G14" s="69" t="s">
+        <v>673</v>
+      </c>
+      <c r="H14" s="60">
+        <v>0.27430555555555558</v>
+      </c>
       <c r="I14" s="6"/>
       <c r="J14" s="114"/>
       <c r="K14" s="60"/>
@@ -55853,12 +55971,24 @@
       <c r="B15" s="70">
         <v>13</v>
       </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="152"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="75"/>
+      <c r="C15" s="73" t="s">
+        <v>674</v>
+      </c>
+      <c r="D15" s="73">
+        <v>2017</v>
+      </c>
+      <c r="E15" s="152" t="s">
+        <v>439</v>
+      </c>
+      <c r="F15" s="74" t="s">
+        <v>673</v>
+      </c>
+      <c r="G15" s="74">
+        <v>46146</v>
+      </c>
+      <c r="H15" s="75">
+        <v>1.2333333333333334</v>
+      </c>
       <c r="I15" s="6"/>
       <c r="J15" s="135"/>
       <c r="K15" s="77"/>
@@ -55880,10 +56010,18 @@
       <c r="B16" s="78">
         <v>14</v>
       </c>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="153"/>
-      <c r="F16" s="69"/>
+      <c r="C16" s="54" t="s">
+        <v>678</v>
+      </c>
+      <c r="D16" s="54">
+        <v>2021</v>
+      </c>
+      <c r="E16" s="153" t="s">
+        <v>439</v>
+      </c>
+      <c r="F16" s="69" t="s">
+        <v>679</v>
+      </c>
       <c r="G16" s="69"/>
       <c r="H16" s="60"/>
       <c r="I16" s="6"/>
@@ -55909,15 +56047,15 @@
       <c r="G17" s="74"/>
       <c r="H17" s="75"/>
       <c r="I17" s="6"/>
-      <c r="J17" s="170" t="s">
+      <c r="J17" s="171" t="s">
+        <v>289</v>
+      </c>
+      <c r="K17" s="172"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="171" t="s">
         <v>290</v>
       </c>
-      <c r="K17" s="171"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="170" t="s">
-        <v>291</v>
-      </c>
-      <c r="N17" s="171"/>
+      <c r="N17" s="172"/>
       <c r="O17" s="39"/>
       <c r="P17" s="39"/>
       <c r="Q17" s="39"/>
@@ -56031,13 +56169,13 @@
         <v>31</v>
       </c>
       <c r="Q21" s="91" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R21" s="91" t="s">
-        <v>121</v>
+        <v>676</v>
       </c>
       <c r="S21" s="92" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="T21" s="39"/>
       <c r="U21" s="88" t="s">
@@ -56060,13 +56198,13 @@
       <c r="G22" s="69"/>
       <c r="H22" s="60"/>
       <c r="I22" s="6"/>
-      <c r="J22" s="170" t="s">
-        <v>292</v>
-      </c>
-      <c r="K22" s="171"/>
+      <c r="J22" s="171" t="s">
+        <v>291</v>
+      </c>
+      <c r="K22" s="172"/>
       <c r="L22" s="136"/>
       <c r="M22" s="173" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N22" s="174"/>
       <c r="O22" s="39"/>
@@ -56087,7 +56225,7 @@
       </c>
       <c r="T22" s="39"/>
       <c r="U22" s="104" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="V22" s="146"/>
       <c r="W22" s="147">
@@ -56131,7 +56269,7 @@
       </c>
       <c r="T23" s="39"/>
       <c r="U23" s="98" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="V23" s="146"/>
       <c r="W23" s="147">
@@ -56163,15 +56301,32 @@
       <c r="P24" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="Q24" s="81"/>
-      <c r="R24" s="81"/>
-      <c r="S24" s="97"/>
+      <c r="Q24" s="81">
+        <f>SUM(H12,W24:Y24)</f>
+        <v>2.1541666666666668</v>
+      </c>
+      <c r="R24" s="81">
+        <f>SUM(K8)</f>
+        <v>2.2041666666666666</v>
+      </c>
+      <c r="S24" s="97">
+        <f>SUM(Q24:R24)</f>
+        <v>4.3583333333333334</v>
+      </c>
       <c r="T24" s="39"/>
-      <c r="U24" s="99"/>
+      <c r="U24" s="99" t="s">
+        <v>670</v>
+      </c>
       <c r="V24" s="146"/>
-      <c r="W24" s="147"/>
-      <c r="X24" s="147"/>
-      <c r="Y24" s="147"/>
+      <c r="W24" s="147">
+        <v>0.1763888888888889</v>
+      </c>
+      <c r="X24" s="149">
+        <v>1.4652777777777777</v>
+      </c>
+      <c r="Y24" s="147">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="25" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="39"/>
@@ -56192,14 +56347,29 @@
       <c r="P25" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="Q25" s="64"/>
-      <c r="R25" s="64"/>
-      <c r="S25" s="90"/>
+      <c r="Q25" s="64">
+        <f>SUM(W25:X25,H14)</f>
+        <v>2.0465277777777775</v>
+      </c>
+      <c r="R25" s="64">
+        <f>SUM(N8:N9)</f>
+        <v>1.9472222222222222</v>
+      </c>
+      <c r="S25" s="90">
+        <f>SUM(Q25:R25)</f>
+        <v>3.9937499999999995</v>
+      </c>
       <c r="T25" s="39"/>
-      <c r="U25" s="98"/>
+      <c r="U25" s="98" t="s">
+        <v>675</v>
+      </c>
       <c r="V25" s="146"/>
-      <c r="W25" s="147"/>
-      <c r="X25" s="147"/>
+      <c r="W25" s="147">
+        <v>0.82916666666666672</v>
+      </c>
+      <c r="X25" s="147">
+        <v>0.94305555555555554</v>
+      </c>
       <c r="Y25" s="147"/>
     </row>
     <row r="26" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -56216,13 +56386,20 @@
       <c r="P26" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="Q26" s="81"/>
+      <c r="Q26" s="81">
+        <f>SUM(W26:Y26)</f>
+        <v>0.2902777777777778</v>
+      </c>
       <c r="R26" s="81"/>
       <c r="S26" s="97"/>
       <c r="T26" s="39"/>
-      <c r="U26" s="100"/>
+      <c r="U26" s="99" t="s">
+        <v>677</v>
+      </c>
       <c r="V26" s="146"/>
-      <c r="W26" s="147"/>
+      <c r="W26" s="147">
+        <v>0.2902777777777778</v>
+      </c>
       <c r="X26" s="147"/>
       <c r="Y26" s="147"/>
     </row>
@@ -56236,15 +56413,15 @@
       <c r="G27" s="30"/>
       <c r="H27" s="61"/>
       <c r="I27" s="39"/>
-      <c r="J27" s="170" t="s">
+      <c r="J27" s="171" t="s">
+        <v>293</v>
+      </c>
+      <c r="K27" s="172"/>
+      <c r="L27" s="136"/>
+      <c r="M27" s="171" t="s">
         <v>294</v>
       </c>
-      <c r="K27" s="171"/>
-      <c r="L27" s="136"/>
-      <c r="M27" s="170" t="s">
-        <v>295</v>
-      </c>
-      <c r="N27" s="171"/>
+      <c r="N27" s="172"/>
       <c r="O27" s="39"/>
       <c r="P27" s="94" t="s">
         <v>37</v>
@@ -56416,7 +56593,7 @@
       <c r="R33" s="64"/>
       <c r="S33" s="90"/>
       <c r="T33" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="U33" s="128"/>
       <c r="V33" s="39"/>
@@ -56441,15 +56618,15 @@
       </c>
       <c r="Q34" s="126">
         <f>SUM(Q22:Q33)</f>
-        <v>6.3118055555555559</v>
+        <v>10.802777777777779</v>
       </c>
       <c r="R34" s="126">
         <f>SUM(R22:R33)</f>
-        <v>0.36458333333333337</v>
+        <v>4.5159722222222225</v>
       </c>
       <c r="S34" s="127">
         <f>SUM(S22:S33)</f>
-        <v>6.6763888888888889</v>
+        <v>15.02847222222222</v>
       </c>
       <c r="T34" s="39"/>
       <c r="U34" s="39"/>
@@ -56487,9 +56664,9 @@
       <c r="H36" s="61"/>
       <c r="I36" s="39"/>
       <c r="O36" s="39"/>
-      <c r="P36" s="172"/>
-      <c r="Q36" s="172"/>
-      <c r="R36" s="172"/>
+      <c r="P36" s="170"/>
+      <c r="Q36" s="170"/>
+      <c r="R36" s="170"/>
       <c r="S36" s="111"/>
       <c r="T36" s="16"/>
       <c r="U36" s="16"/>
@@ -56508,8 +56685,8 @@
       <c r="I37" s="39"/>
       <c r="O37" s="39"/>
       <c r="P37" s="175"/>
-      <c r="Q37" s="172"/>
-      <c r="R37" s="172"/>
+      <c r="Q37" s="170"/>
+      <c r="R37" s="170"/>
       <c r="S37" s="111"/>
       <c r="T37" s="16"/>
       <c r="U37" s="16"/>
@@ -56527,9 +56704,9 @@
       <c r="H38" s="61"/>
       <c r="I38" s="39"/>
       <c r="O38" s="39"/>
-      <c r="P38" s="172"/>
-      <c r="Q38" s="172"/>
-      <c r="R38" s="172"/>
+      <c r="P38" s="170"/>
+      <c r="Q38" s="170"/>
+      <c r="R38" s="170"/>
       <c r="S38" s="111"/>
       <c r="T38" s="16"/>
       <c r="U38" s="16"/>
@@ -56547,9 +56724,9 @@
       <c r="H39" s="61"/>
       <c r="I39" s="39"/>
       <c r="O39" s="39"/>
-      <c r="P39" s="172"/>
-      <c r="Q39" s="172"/>
-      <c r="R39" s="172"/>
+      <c r="P39" s="170"/>
+      <c r="Q39" s="170"/>
+      <c r="R39" s="170"/>
       <c r="S39" s="124"/>
       <c r="T39" s="16"/>
       <c r="U39" s="16"/>
@@ -56567,9 +56744,9 @@
       <c r="H40" s="61"/>
       <c r="I40" s="39"/>
       <c r="O40" s="39"/>
-      <c r="P40" s="172"/>
-      <c r="Q40" s="172"/>
-      <c r="R40" s="172"/>
+      <c r="P40" s="170"/>
+      <c r="Q40" s="170"/>
+      <c r="R40" s="170"/>
       <c r="S40" s="124"/>
       <c r="T40" s="16"/>
       <c r="U40" s="16"/>
@@ -56587,9 +56764,9 @@
       <c r="H41" s="61"/>
       <c r="I41" s="39"/>
       <c r="O41" s="39"/>
-      <c r="P41" s="172"/>
-      <c r="Q41" s="172"/>
-      <c r="R41" s="172"/>
+      <c r="P41" s="170"/>
+      <c r="Q41" s="170"/>
+      <c r="R41" s="170"/>
       <c r="S41" s="124"/>
       <c r="T41" s="16"/>
       <c r="U41" s="16"/>
@@ -58442,7 +58619,7 @@
         <v>77</v>
       </c>
       <c r="R116" s="56" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S116" s="39"/>
       <c r="T116" s="39"/>
@@ -58472,7 +58649,7 @@
       </c>
       <c r="R117" s="44">
         <f>COUNTIF(D1:D57,Q117)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S117" s="39"/>
       <c r="T117" s="39"/>
@@ -58592,7 +58769,7 @@
       </c>
       <c r="R121" s="145">
         <f>COUNTIF(D3:D59,Q121)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S121" s="39"/>
       <c r="T121" s="39"/>
@@ -58712,7 +58889,7 @@
       </c>
       <c r="R125" s="46">
         <f>COUNTIF(D3:D59,Q125)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S125" s="39"/>
       <c r="T125" s="39"/>
@@ -59252,7 +59429,7 @@
       </c>
       <c r="R143" s="46">
         <f>COUNTIF(D3:D59,Q143)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S143" s="39"/>
       <c r="T143" s="39"/>
@@ -59458,11 +59635,11 @@
       <c r="O150" s="39"/>
       <c r="P150" s="39"/>
       <c r="Q150" s="41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R150" s="42">
         <f>SUM(R117:R149)</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="S150" s="39"/>
       <c r="T150" s="39"/>
@@ -59547,6 +59724,12 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="M12:N12"/>
     <mergeCell ref="P41:R41"/>
     <mergeCell ref="J17:K17"/>
     <mergeCell ref="M17:N17"/>
@@ -59559,12 +59742,6 @@
     <mergeCell ref="P40:R40"/>
     <mergeCell ref="J27:K27"/>
     <mergeCell ref="M27:N27"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="M12:N12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
